--- a/ThirdLibs/pandas_df9_test_xlsx.xlsx
+++ b/ThirdLibs/pandas_df9_test_xlsx.xlsx
@@ -444,7 +444,7 @@
         <v>36526</v>
       </c>
       <c r="B2" t="n">
-        <v>0.583615642630077</v>
+        <v>-0.9030715111748</v>
       </c>
     </row>
     <row r="3">
@@ -452,7 +452,7 @@
         <v>36527</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6317275618434102</v>
+        <v>-0.06137371051808792</v>
       </c>
     </row>
     <row r="4">
@@ -460,7 +460,7 @@
         <v>36528</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.690571476495911</v>
+        <v>0.9178082537989496</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         <v>36529</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7910742435256264</v>
+        <v>-0.7354051611719306</v>
       </c>
     </row>
     <row r="6">
@@ -476,7 +476,7 @@
         <v>36530</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5579287502280889</v>
+        <v>-0.5613627220191015</v>
       </c>
     </row>
     <row r="7">
@@ -484,7 +484,7 @@
         <v>36531</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.7344775624260637</v>
+        <v>0.737090448199259</v>
       </c>
     </row>
     <row r="8">
@@ -492,7 +492,7 @@
         <v>36532</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.08655844676753219</v>
+        <v>1.357511014806152</v>
       </c>
     </row>
     <row r="9">
@@ -500,7 +500,7 @@
         <v>36533</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8693972338888454</v>
+        <v>-0.2979789346693378</v>
       </c>
     </row>
     <row r="10">
@@ -508,7 +508,7 @@
         <v>36534</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.8130622308934203</v>
+        <v>-0.7899197666034672</v>
       </c>
     </row>
     <row r="11">
@@ -516,7 +516,7 @@
         <v>36535</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.5375637142553162</v>
+        <v>0.3976608869246535</v>
       </c>
     </row>
     <row r="12">
@@ -524,7 +524,7 @@
         <v>36536</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3360170523026056</v>
+        <v>-0.2830864968959515</v>
       </c>
     </row>
     <row r="13">
@@ -532,7 +532,7 @@
         <v>36537</v>
       </c>
       <c r="B13" t="n">
-        <v>1.023731005533951</v>
+        <v>0.598639600180747</v>
       </c>
     </row>
     <row r="14">
@@ -540,7 +540,7 @@
         <v>36538</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7252692223305108</v>
+        <v>-0.6489242820008231</v>
       </c>
     </row>
     <row r="15">
@@ -548,7 +548,7 @@
         <v>36539</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4751117885034393</v>
+        <v>0.7707989051569716</v>
       </c>
     </row>
     <row r="16">
@@ -556,7 +556,7 @@
         <v>36540</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6448206795078826</v>
+        <v>-0.07989583266538997</v>
       </c>
     </row>
     <row r="17">
@@ -564,7 +564,7 @@
         <v>36541</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.134514709771326</v>
+        <v>0.09073497041044089</v>
       </c>
     </row>
     <row r="18">
@@ -572,7 +572,7 @@
         <v>36542</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.3495539212695105</v>
+        <v>0.3469857904124792</v>
       </c>
     </row>
     <row r="19">
@@ -580,7 +580,7 @@
         <v>36543</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.9753750317304831</v>
+        <v>-0.4909401850929245</v>
       </c>
     </row>
     <row r="20">
@@ -588,7 +588,7 @@
         <v>36544</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.6253578957175397</v>
+        <v>-0.07586293267169547</v>
       </c>
     </row>
     <row r="21">
@@ -596,7 +596,7 @@
         <v>36545</v>
       </c>
       <c r="B21" t="n">
-        <v>1.101735365911809</v>
+        <v>-1.872123615565154</v>
       </c>
     </row>
     <row r="22">
@@ -604,7 +604,7 @@
         <v>36546</v>
       </c>
       <c r="B22" t="n">
-        <v>2.115745571049162</v>
+        <v>0.1874346384757426</v>
       </c>
     </row>
     <row r="23">
@@ -612,7 +612,7 @@
         <v>36547</v>
       </c>
       <c r="B23" t="n">
-        <v>1.343670288868992</v>
+        <v>-1.857227675862331</v>
       </c>
     </row>
     <row r="24">
@@ -620,7 +620,7 @@
         <v>36548</v>
       </c>
       <c r="B24" t="n">
-        <v>1.411545539335902</v>
+        <v>-1.743603212748021</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>36549</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.854594232458049</v>
+        <v>0.2769761842888659</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +636,7 @@
         <v>36550</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.2916616779655208</v>
+        <v>-0.7042621478443625</v>
       </c>
     </row>
     <row r="27">
@@ -644,7 +644,7 @@
         <v>36551</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2081237741510459</v>
+        <v>-0.89093330688765</v>
       </c>
     </row>
     <row r="28">
@@ -652,7 +652,7 @@
         <v>36552</v>
       </c>
       <c r="B28" t="n">
-        <v>1.636369708843543</v>
+        <v>-0.8504545252846444</v>
       </c>
     </row>
     <row r="29">
@@ -660,7 +660,7 @@
         <v>36553</v>
       </c>
       <c r="B29" t="n">
-        <v>1.08154674630949</v>
+        <v>1.306535502297844</v>
       </c>
     </row>
     <row r="30">
@@ -668,7 +668,7 @@
         <v>36554</v>
       </c>
       <c r="B30" t="n">
-        <v>1.161898025192728</v>
+        <v>0.8582145651045189</v>
       </c>
     </row>
     <row r="31">
@@ -676,7 +676,7 @@
         <v>36555</v>
       </c>
       <c r="B31" t="n">
-        <v>0.6335537451919439</v>
+        <v>0.784091687156253</v>
       </c>
     </row>
     <row r="32">
@@ -684,7 +684,7 @@
         <v>36556</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.2703858076903927</v>
+        <v>1.639488211891701</v>
       </c>
     </row>
     <row r="33">
@@ -692,7 +692,7 @@
         <v>36557</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.463409011559412</v>
+        <v>-0.5755389028220665</v>
       </c>
     </row>
     <row r="34">
@@ -700,7 +700,7 @@
         <v>36558</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1244454936766377</v>
+        <v>1.288819908231768</v>
       </c>
     </row>
     <row r="35">
@@ -708,7 +708,7 @@
         <v>36559</v>
       </c>
       <c r="B35" t="n">
-        <v>1.012359450058236</v>
+        <v>0.1023242897977027</v>
       </c>
     </row>
     <row r="36">
@@ -716,7 +716,7 @@
         <v>36560</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5928053861298469</v>
+        <v>-1.1637950998677</v>
       </c>
     </row>
     <row r="37">
@@ -724,7 +724,7 @@
         <v>36561</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.7287311690068377</v>
+        <v>0.9993006636518834</v>
       </c>
     </row>
     <row r="38">
@@ -732,7 +732,7 @@
         <v>36562</v>
       </c>
       <c r="B38" t="n">
-        <v>2.236158198643784</v>
+        <v>0.4988061980823115</v>
       </c>
     </row>
     <row r="39">
@@ -740,7 +740,7 @@
         <v>36563</v>
       </c>
       <c r="B39" t="n">
-        <v>1.448278638379306</v>
+        <v>-1.332958999541962</v>
       </c>
     </row>
     <row r="40">
@@ -748,7 +748,7 @@
         <v>36564</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0150315882848604</v>
+        <v>1.419757882872955</v>
       </c>
     </row>
     <row r="41">
@@ -756,7 +756,7 @@
         <v>36565</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.13418346586322</v>
+        <v>-0.9548571499495366</v>
       </c>
     </row>
     <row r="42">
@@ -764,7 +764,7 @@
         <v>36566</v>
       </c>
       <c r="B42" t="n">
-        <v>1.752569727410761</v>
+        <v>-0.7415074956619589</v>
       </c>
     </row>
     <row r="43">
@@ -772,7 +772,7 @@
         <v>36567</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.2588576110937003</v>
+        <v>-1.023304852584799</v>
       </c>
     </row>
     <row r="44">
@@ -780,7 +780,7 @@
         <v>36568</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.9018675132231649</v>
+        <v>0.780162669570087</v>
       </c>
     </row>
     <row r="45">
@@ -788,7 +788,7 @@
         <v>36569</v>
       </c>
       <c r="B45" t="n">
-        <v>1.349783427234366</v>
+        <v>0.6182296934475909</v>
       </c>
     </row>
     <row r="46">
@@ -796,7 +796,7 @@
         <v>36570</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.8245859788553862</v>
+        <v>-0.6169332362525101</v>
       </c>
     </row>
     <row r="47">
@@ -804,7 +804,7 @@
         <v>36571</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.1914435611358112</v>
+        <v>-0.1594371630002585</v>
       </c>
     </row>
     <row r="48">
@@ -812,7 +812,7 @@
         <v>36572</v>
       </c>
       <c r="B48" t="n">
-        <v>-2.535722679824263</v>
+        <v>-0.2080509461574617</v>
       </c>
     </row>
     <row r="49">
@@ -820,7 +820,7 @@
         <v>36573</v>
       </c>
       <c r="B49" t="n">
-        <v>0.09955354772411912</v>
+        <v>-0.9134495852075981</v>
       </c>
     </row>
     <row r="50">
@@ -828,7 +828,7 @@
         <v>36574</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.2059453230467568</v>
+        <v>-0.3914875327878212</v>
       </c>
     </row>
     <row r="51">
@@ -836,7 +836,7 @@
         <v>36575</v>
       </c>
       <c r="B51" t="n">
-        <v>-2.493377674606796</v>
+        <v>1.337160458773752</v>
       </c>
     </row>
     <row r="52">
@@ -844,7 +844,7 @@
         <v>36576</v>
       </c>
       <c r="B52" t="n">
-        <v>-2.406425574521157</v>
+        <v>0.7607028285493489</v>
       </c>
     </row>
     <row r="53">
@@ -852,7 +852,7 @@
         <v>36577</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1423561721674574</v>
+        <v>-0.9132780482314354</v>
       </c>
     </row>
     <row r="54">
@@ -860,7 +860,7 @@
         <v>36578</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.7360812609499395</v>
+        <v>0.6893483981955753</v>
       </c>
     </row>
     <row r="55">
@@ -868,7 +868,7 @@
         <v>36579</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.5955716482934508</v>
+        <v>-0.2888776167241791</v>
       </c>
     </row>
     <row r="56">
@@ -876,7 +876,7 @@
         <v>36580</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.06592020995802669</v>
+        <v>1.289222906502264</v>
       </c>
     </row>
     <row r="57">
@@ -884,7 +884,7 @@
         <v>36581</v>
       </c>
       <c r="B57" t="n">
-        <v>1.012825422068722</v>
+        <v>0.8612543416489559</v>
       </c>
     </row>
     <row r="58">
@@ -892,7 +892,7 @@
         <v>36582</v>
       </c>
       <c r="B58" t="n">
-        <v>-1.799541624977967</v>
+        <v>-0.3976368715851372</v>
       </c>
     </row>
     <row r="59">
@@ -900,7 +900,7 @@
         <v>36583</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.214606465298795</v>
+        <v>0.5216734295802294</v>
       </c>
     </row>
     <row r="60">
@@ -908,7 +908,7 @@
         <v>36584</v>
       </c>
       <c r="B60" t="n">
-        <v>0.8838158128985097</v>
+        <v>-0.6895418688640121</v>
       </c>
     </row>
     <row r="61">
@@ -916,7 +916,7 @@
         <v>36585</v>
       </c>
       <c r="B61" t="n">
-        <v>0.677075100363021</v>
+        <v>-0.5268299135332237</v>
       </c>
     </row>
     <row r="62">
@@ -924,7 +924,7 @@
         <v>36586</v>
       </c>
       <c r="B62" t="n">
-        <v>0.397796802755609</v>
+        <v>1.183575267475868</v>
       </c>
     </row>
     <row r="63">
@@ -932,7 +932,7 @@
         <v>36587</v>
       </c>
       <c r="B63" t="n">
-        <v>-2.121362755851405</v>
+        <v>0.4386528813631055</v>
       </c>
     </row>
     <row r="64">
@@ -940,7 +940,7 @@
         <v>36588</v>
       </c>
       <c r="B64" t="n">
-        <v>1.330109941716636</v>
+        <v>-0.1341464080028734</v>
       </c>
     </row>
     <row r="65">
@@ -948,7 +948,7 @@
         <v>36589</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.672619839396428</v>
+        <v>1.291906003572662</v>
       </c>
     </row>
     <row r="66">
@@ -956,7 +956,7 @@
         <v>36590</v>
       </c>
       <c r="B66" t="n">
-        <v>-1.109926477420428</v>
+        <v>0.671574690334363</v>
       </c>
     </row>
     <row r="67">
@@ -964,7 +964,7 @@
         <v>36591</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.3967403611093963</v>
+        <v>-0.103809396649247</v>
       </c>
     </row>
     <row r="68">
@@ -972,7 +972,7 @@
         <v>36592</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.9932029953292569</v>
+        <v>-0.7163274070893856</v>
       </c>
     </row>
     <row r="69">
@@ -980,7 +980,7 @@
         <v>36593</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.9110782618229365</v>
+        <v>-1.31163607029712</v>
       </c>
     </row>
     <row r="70">
@@ -988,7 +988,7 @@
         <v>36594</v>
       </c>
       <c r="B70" t="n">
-        <v>0.5075911074177593</v>
+        <v>-0.2072900162906239</v>
       </c>
     </row>
     <row r="71">
@@ -996,7 +996,7 @@
         <v>36595</v>
       </c>
       <c r="B71" t="n">
-        <v>0.2342850092605754</v>
+        <v>-0.198677387448814</v>
       </c>
     </row>
     <row r="72">
@@ -1004,7 +1004,7 @@
         <v>36596</v>
       </c>
       <c r="B72" t="n">
-        <v>0.9016324200856203</v>
+        <v>-0.8380056159769591</v>
       </c>
     </row>
     <row r="73">
@@ -1012,7 +1012,7 @@
         <v>36597</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.3848778246812692</v>
+        <v>-0.05324982831074831</v>
       </c>
     </row>
     <row r="74">
@@ -1020,7 +1020,7 @@
         <v>36598</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.4635668881310407</v>
+        <v>1.67145437851402</v>
       </c>
     </row>
     <row r="75">
@@ -1028,7 +1028,7 @@
         <v>36599</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.7036162668324506</v>
+        <v>0.312699847008944</v>
       </c>
     </row>
     <row r="76">
@@ -1036,7 +1036,7 @@
         <v>36600</v>
       </c>
       <c r="B76" t="n">
-        <v>0.04181785161922458</v>
+        <v>-0.08755041734458206</v>
       </c>
     </row>
     <row r="77">
@@ -1044,7 +1044,7 @@
         <v>36601</v>
       </c>
       <c r="B77" t="n">
-        <v>0.03823910408179908</v>
+        <v>0.955495664812169</v>
       </c>
     </row>
     <row r="78">
@@ -1052,7 +1052,7 @@
         <v>36602</v>
       </c>
       <c r="B78" t="n">
-        <v>0.7330558373121302</v>
+        <v>0.1103125770392815</v>
       </c>
     </row>
     <row r="79">
@@ -1060,7 +1060,7 @@
         <v>36603</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.8566155356961108</v>
+        <v>1.959420695153594</v>
       </c>
     </row>
     <row r="80">
@@ -1068,7 +1068,7 @@
         <v>36604</v>
       </c>
       <c r="B80" t="n">
-        <v>0.2897945279508145</v>
+        <v>-1.770130203729383</v>
       </c>
     </row>
     <row r="81">
@@ -1076,7 +1076,7 @@
         <v>36605</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3063108047893926</v>
+        <v>-1.387868552717573</v>
       </c>
     </row>
     <row r="82">
@@ -1084,7 +1084,7 @@
         <v>36606</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.9668300697072327</v>
+        <v>-1.01651730867131</v>
       </c>
     </row>
     <row r="83">
@@ -1092,7 +1092,7 @@
         <v>36607</v>
       </c>
       <c r="B83" t="n">
-        <v>-0.06421301946402412</v>
+        <v>1.429438760677633</v>
       </c>
     </row>
     <row r="84">
@@ -1100,7 +1100,7 @@
         <v>36608</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.2027053304047762</v>
+        <v>0.9119237367899042</v>
       </c>
     </row>
     <row r="85">
@@ -1108,7 +1108,7 @@
         <v>36609</v>
       </c>
       <c r="B85" t="n">
-        <v>0.5783176672619706</v>
+        <v>-1.324507177926327</v>
       </c>
     </row>
     <row r="86">
@@ -1116,7 +1116,7 @@
         <v>36610</v>
       </c>
       <c r="B86" t="n">
-        <v>1.185570054396711</v>
+        <v>-0.9876169517072697</v>
       </c>
     </row>
     <row r="87">
@@ -1124,7 +1124,7 @@
         <v>36611</v>
       </c>
       <c r="B87" t="n">
-        <v>1.190227007532266</v>
+        <v>0.3642291759802385</v>
       </c>
     </row>
     <row r="88">
@@ -1132,7 +1132,7 @@
         <v>36612</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.357150459205437</v>
+        <v>-0.479138310192465</v>
       </c>
     </row>
     <row r="89">
@@ -1140,7 +1140,7 @@
         <v>36613</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.704650077484131</v>
+        <v>0.6887774168196971</v>
       </c>
     </row>
     <row r="90">
@@ -1148,7 +1148,7 @@
         <v>36614</v>
       </c>
       <c r="B90" t="n">
-        <v>0.4086780209260575</v>
+        <v>0.1171936828167742</v>
       </c>
     </row>
     <row r="91">
@@ -1156,7 +1156,7 @@
         <v>36615</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.6851170102582218</v>
+        <v>0.2565303570225252</v>
       </c>
     </row>
     <row r="92">
@@ -1164,7 +1164,7 @@
         <v>36616</v>
       </c>
       <c r="B92" t="n">
-        <v>1.267849654357442</v>
+        <v>-0.5255390962096641</v>
       </c>
     </row>
     <row r="93">
@@ -1172,7 +1172,7 @@
         <v>36617</v>
       </c>
       <c r="B93" t="n">
-        <v>1.036261880127686</v>
+        <v>0.1517163427911615</v>
       </c>
     </row>
     <row r="94">
@@ -1180,7 +1180,7 @@
         <v>36618</v>
       </c>
       <c r="B94" t="n">
-        <v>1.082534572411711</v>
+        <v>1.185045396063237</v>
       </c>
     </row>
     <row r="95">
@@ -1188,7 +1188,7 @@
         <v>36619</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.8002821019606625</v>
+        <v>1.504697237868434</v>
       </c>
     </row>
     <row r="96">
@@ -1196,7 +1196,7 @@
         <v>36620</v>
       </c>
       <c r="B96" t="n">
-        <v>0.5503570515701247</v>
+        <v>-1.944921348219784</v>
       </c>
     </row>
     <row r="97">
@@ -1204,7 +1204,7 @@
         <v>36621</v>
       </c>
       <c r="B97" t="n">
-        <v>0.01461899186092852</v>
+        <v>-0.5280199365691568</v>
       </c>
     </row>
     <row r="98">
@@ -1212,7 +1212,7 @@
         <v>36622</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.7793597778834677</v>
+        <v>-0.8274509178346214</v>
       </c>
     </row>
     <row r="99">
@@ -1220,7 +1220,7 @@
         <v>36623</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.9941135869556654</v>
+        <v>-0.3873173926998476</v>
       </c>
     </row>
     <row r="100">
@@ -1228,7 +1228,7 @@
         <v>36624</v>
       </c>
       <c r="B100" t="n">
-        <v>2.143040449438831</v>
+        <v>-2.198425613807967</v>
       </c>
     </row>
     <row r="101">
@@ -1236,7 +1236,7 @@
         <v>36625</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.8850871849922122</v>
+        <v>0.09534277104342324</v>
       </c>
     </row>
     <row r="102">
@@ -1244,7 +1244,7 @@
         <v>36626</v>
       </c>
       <c r="B102" t="n">
-        <v>0.5096917961637105</v>
+        <v>0.1917788886663704</v>
       </c>
     </row>
     <row r="103">
@@ -1252,7 +1252,7 @@
         <v>36627</v>
       </c>
       <c r="B103" t="n">
-        <v>-1.064266565927884</v>
+        <v>-0.151869542591736</v>
       </c>
     </row>
     <row r="104">
@@ -1260,7 +1260,7 @@
         <v>36628</v>
       </c>
       <c r="B104" t="n">
-        <v>-0.2140725125858285</v>
+        <v>1.361660623363045</v>
       </c>
     </row>
     <row r="105">
@@ -1268,7 +1268,7 @@
         <v>36629</v>
       </c>
       <c r="B105" t="n">
-        <v>-1.268231371944322</v>
+        <v>-0.7782832363735572</v>
       </c>
     </row>
     <row r="106">
@@ -1276,7 +1276,7 @@
         <v>36630</v>
       </c>
       <c r="B106" t="n">
-        <v>-2.082474186709732</v>
+        <v>0.5926282146440149</v>
       </c>
     </row>
     <row r="107">
@@ -1284,7 +1284,7 @@
         <v>36631</v>
       </c>
       <c r="B107" t="n">
-        <v>2.041516045507231</v>
+        <v>-0.1348177635947483</v>
       </c>
     </row>
     <row r="108">
@@ -1292,7 +1292,7 @@
         <v>36632</v>
       </c>
       <c r="B108" t="n">
-        <v>-0.315552521675874</v>
+        <v>0.5846252476918173</v>
       </c>
     </row>
     <row r="109">
@@ -1300,7 +1300,7 @@
         <v>36633</v>
       </c>
       <c r="B109" t="n">
-        <v>1.270417247835826</v>
+        <v>0.6813092685065868</v>
       </c>
     </row>
     <row r="110">
@@ -1308,7 +1308,7 @@
         <v>36634</v>
       </c>
       <c r="B110" t="n">
-        <v>1.464050661798757</v>
+        <v>1.406164010726788</v>
       </c>
     </row>
     <row r="111">
@@ -1316,7 +1316,7 @@
         <v>36635</v>
       </c>
       <c r="B111" t="n">
-        <v>1.501298656885958</v>
+        <v>0.4642307487966723</v>
       </c>
     </row>
     <row r="112">
@@ -1324,7 +1324,7 @@
         <v>36636</v>
       </c>
       <c r="B112" t="n">
-        <v>1.009536000591397</v>
+        <v>0.4528944195573132</v>
       </c>
     </row>
     <row r="113">
@@ -1332,7 +1332,7 @@
         <v>36637</v>
       </c>
       <c r="B113" t="n">
-        <v>1.005172022175294</v>
+        <v>0.1173488532463749</v>
       </c>
     </row>
     <row r="114">
@@ -1340,7 +1340,7 @@
         <v>36638</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.5510237809200514</v>
+        <v>-1.944437703666707</v>
       </c>
     </row>
     <row r="115">
@@ -1348,7 +1348,7 @@
         <v>36639</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.289129950203742</v>
+        <v>-0.4123819898766327</v>
       </c>
     </row>
     <row r="116">
@@ -1356,7 +1356,7 @@
         <v>36640</v>
       </c>
       <c r="B116" t="n">
-        <v>-1.803086804125947</v>
+        <v>-0.433022098017115</v>
       </c>
     </row>
     <row r="117">
@@ -1364,7 +1364,7 @@
         <v>36641</v>
       </c>
       <c r="B117" t="n">
-        <v>0.02525206666419461</v>
+        <v>-0.679946099268391</v>
       </c>
     </row>
     <row r="118">
@@ -1372,7 +1372,7 @@
         <v>36642</v>
       </c>
       <c r="B118" t="n">
-        <v>-0.05348592777913851</v>
+        <v>0.6439240505788242</v>
       </c>
     </row>
     <row r="119">
@@ -1380,7 +1380,7 @@
         <v>36643</v>
       </c>
       <c r="B119" t="n">
-        <v>-1.003640307527889</v>
+        <v>-0.1207465567842172</v>
       </c>
     </row>
     <row r="120">
@@ -1388,7 +1388,7 @@
         <v>36644</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.1089568891987454</v>
+        <v>-0.6364138389533065</v>
       </c>
     </row>
     <row r="121">
@@ -1396,7 +1396,7 @@
         <v>36645</v>
       </c>
       <c r="B121" t="n">
-        <v>0.4647839173232247</v>
+        <v>0.1373097104486949</v>
       </c>
     </row>
     <row r="122">
@@ -1404,7 +1404,7 @@
         <v>36646</v>
       </c>
       <c r="B122" t="n">
-        <v>-0.5797394205781368</v>
+        <v>-1.91775430170954</v>
       </c>
     </row>
     <row r="123">
@@ -1412,7 +1412,7 @@
         <v>36647</v>
       </c>
       <c r="B123" t="n">
-        <v>-0.2077033243853617</v>
+        <v>-0.7639920532258737</v>
       </c>
     </row>
     <row r="124">
@@ -1420,7 +1420,7 @@
         <v>36648</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.1254227309323749</v>
+        <v>-1.962368945031957</v>
       </c>
     </row>
     <row r="125">
@@ -1428,7 +1428,7 @@
         <v>36649</v>
       </c>
       <c r="B125" t="n">
-        <v>-0.8095980061909233</v>
+        <v>0.830850073097815</v>
       </c>
     </row>
     <row r="126">
@@ -1436,7 +1436,7 @@
         <v>36650</v>
       </c>
       <c r="B126" t="n">
-        <v>0.6117777095454059</v>
+        <v>-2.151446332176202</v>
       </c>
     </row>
     <row r="127">
@@ -1444,7 +1444,7 @@
         <v>36651</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.97914278910985</v>
+        <v>-0.9573063077033968</v>
       </c>
     </row>
     <row r="128">
@@ -1452,7 +1452,7 @@
         <v>36652</v>
       </c>
       <c r="B128" t="n">
-        <v>0.02672950174605446</v>
+        <v>-1.645291432843199</v>
       </c>
     </row>
     <row r="129">
@@ -1460,7 +1460,7 @@
         <v>36653</v>
       </c>
       <c r="B129" t="n">
-        <v>-1.448289928448284</v>
+        <v>-0.5464088599779886</v>
       </c>
     </row>
     <row r="130">
@@ -1468,7 +1468,7 @@
         <v>36654</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.7083141231444519</v>
+        <v>-1.444660632102301</v>
       </c>
     </row>
     <row r="131">
@@ -1476,7 +1476,7 @@
         <v>36655</v>
       </c>
       <c r="B131" t="n">
-        <v>2.260590228239972</v>
+        <v>-0.6920785257490079</v>
       </c>
     </row>
     <row r="132">
@@ -1484,7 +1484,7 @@
         <v>36656</v>
       </c>
       <c r="B132" t="n">
-        <v>0.9528865609081412</v>
+        <v>1.029017246558146</v>
       </c>
     </row>
     <row r="133">
@@ -1492,7 +1492,7 @@
         <v>36657</v>
       </c>
       <c r="B133" t="n">
-        <v>0.2718912763980106</v>
+        <v>-1.195803691178134</v>
       </c>
     </row>
     <row r="134">
@@ -1500,7 +1500,7 @@
         <v>36658</v>
       </c>
       <c r="B134" t="n">
-        <v>-1.151951326423238</v>
+        <v>0.03309074091773007</v>
       </c>
     </row>
     <row r="135">
@@ -1508,7 +1508,7 @@
         <v>36659</v>
       </c>
       <c r="B135" t="n">
-        <v>0.07438631967410628</v>
+        <v>-1.067245195183786</v>
       </c>
     </row>
     <row r="136">
@@ -1516,7 +1516,7 @@
         <v>36660</v>
       </c>
       <c r="B136" t="n">
-        <v>0.9143430019637665</v>
+        <v>0.2984228334126001</v>
       </c>
     </row>
     <row r="137">
@@ -1524,7 +1524,7 @@
         <v>36661</v>
       </c>
       <c r="B137" t="n">
-        <v>-1.982090827472893</v>
+        <v>0.1760278904218261</v>
       </c>
     </row>
     <row r="138">
@@ -1532,7 +1532,7 @@
         <v>36662</v>
       </c>
       <c r="B138" t="n">
-        <v>0.141738775161501</v>
+        <v>1.9776896183211</v>
       </c>
     </row>
     <row r="139">
@@ -1540,7 +1540,7 @@
         <v>36663</v>
       </c>
       <c r="B139" t="n">
-        <v>-0.6697314418645267</v>
+        <v>-0.0001745348704289044</v>
       </c>
     </row>
     <row r="140">
@@ -1548,7 +1548,7 @@
         <v>36664</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.7720959042246416</v>
+        <v>-1.320528168396664</v>
       </c>
     </row>
     <row r="141">
@@ -1556,7 +1556,7 @@
         <v>36665</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.3382367177354892</v>
+        <v>-0.2345678937473047</v>
       </c>
     </row>
     <row r="142">
@@ -1564,7 +1564,7 @@
         <v>36666</v>
       </c>
       <c r="B142" t="n">
-        <v>-1.142659748683341</v>
+        <v>1.713500253257435</v>
       </c>
     </row>
     <row r="143">
@@ -1572,7 +1572,7 @@
         <v>36667</v>
       </c>
       <c r="B143" t="n">
-        <v>0.9737925321049923</v>
+        <v>0.6760758959475481</v>
       </c>
     </row>
     <row r="144">
@@ -1580,7 +1580,7 @@
         <v>36668</v>
       </c>
       <c r="B144" t="n">
-        <v>0.9264127898349072</v>
+        <v>0.132657916674885</v>
       </c>
     </row>
     <row r="145">
@@ -1588,7 +1588,7 @@
         <v>36669</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.979477266609477</v>
+        <v>-0.1880525441744051</v>
       </c>
     </row>
     <row r="146">
@@ -1596,7 +1596,7 @@
         <v>36670</v>
       </c>
       <c r="B146" t="n">
-        <v>-0.2101426630051735</v>
+        <v>1.079094934363223</v>
       </c>
     </row>
     <row r="147">
@@ -1604,7 +1604,7 @@
         <v>36671</v>
       </c>
       <c r="B147" t="n">
-        <v>0.08443814306791421</v>
+        <v>0.4863437363366127</v>
       </c>
     </row>
     <row r="148">
@@ -1612,7 +1612,7 @@
         <v>36672</v>
       </c>
       <c r="B148" t="n">
-        <v>0.2334359864568535</v>
+        <v>0.4198586529557582</v>
       </c>
     </row>
     <row r="149">
@@ -1620,7 +1620,7 @@
         <v>36673</v>
       </c>
       <c r="B149" t="n">
-        <v>-0.8828897032789303</v>
+        <v>-0.5452736610949181</v>
       </c>
     </row>
     <row r="150">
@@ -1628,7 +1628,7 @@
         <v>36674</v>
       </c>
       <c r="B150" t="n">
-        <v>0.3900117090675141</v>
+        <v>0.4413823490876329</v>
       </c>
     </row>
     <row r="151">
@@ -1636,7 +1636,7 @@
         <v>36675</v>
       </c>
       <c r="B151" t="n">
-        <v>0.9200426485144695</v>
+        <v>-1.009959192145125</v>
       </c>
     </row>
     <row r="152">
@@ -1644,7 +1644,7 @@
         <v>36676</v>
       </c>
       <c r="B152" t="n">
-        <v>-0.2400467500163591</v>
+        <v>-0.5925092468238695</v>
       </c>
     </row>
     <row r="153">
@@ -1652,7 +1652,7 @@
         <v>36677</v>
       </c>
       <c r="B153" t="n">
-        <v>0.9078433225344634</v>
+        <v>0.1727833828050402</v>
       </c>
     </row>
     <row r="154">
@@ -1660,7 +1660,7 @@
         <v>36678</v>
       </c>
       <c r="B154" t="n">
-        <v>-1.356368154475816</v>
+        <v>0.2945808719901571</v>
       </c>
     </row>
     <row r="155">
@@ -1668,7 +1668,7 @@
         <v>36679</v>
       </c>
       <c r="B155" t="n">
-        <v>-2.689255358028095</v>
+        <v>0.8551430387833605</v>
       </c>
     </row>
     <row r="156">
@@ -1676,7 +1676,7 @@
         <v>36680</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.5867149987033553</v>
+        <v>-0.9201309513261461</v>
       </c>
     </row>
     <row r="157">
@@ -1684,7 +1684,7 @@
         <v>36681</v>
       </c>
       <c r="B157" t="n">
-        <v>-1.678411183108156</v>
+        <v>0.3541854824167904</v>
       </c>
     </row>
     <row r="158">
@@ -1692,7 +1692,7 @@
         <v>36682</v>
       </c>
       <c r="B158" t="n">
-        <v>1.018426850273066</v>
+        <v>-0.4439563133299025</v>
       </c>
     </row>
     <row r="159">
@@ -1700,7 +1700,7 @@
         <v>36683</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.9953072805997091</v>
+        <v>0.4715290241430893</v>
       </c>
     </row>
     <row r="160">
@@ -1708,7 +1708,7 @@
         <v>36684</v>
       </c>
       <c r="B160" t="n">
-        <v>-0.2456442515622606</v>
+        <v>-1.276736530396729</v>
       </c>
     </row>
     <row r="161">
@@ -1716,7 +1716,7 @@
         <v>36685</v>
       </c>
       <c r="B161" t="n">
-        <v>-0.0727001538722004</v>
+        <v>-0.6403942207848471</v>
       </c>
     </row>
     <row r="162">
@@ -1724,7 +1724,7 @@
         <v>36686</v>
       </c>
       <c r="B162" t="n">
-        <v>-0.783078228411524</v>
+        <v>-0.1715229806497905</v>
       </c>
     </row>
     <row r="163">
@@ -1732,7 +1732,7 @@
         <v>36687</v>
       </c>
       <c r="B163" t="n">
-        <v>-0.3847663716870998</v>
+        <v>-1.452812055760873</v>
       </c>
     </row>
     <row r="164">
@@ -1740,7 +1740,7 @@
         <v>36688</v>
       </c>
       <c r="B164" t="n">
-        <v>-0.4802537598322238</v>
+        <v>-0.1960322152493968</v>
       </c>
     </row>
     <row r="165">
@@ -1748,7 +1748,7 @@
         <v>36689</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.3323382201977203</v>
+        <v>1.884039692578262</v>
       </c>
     </row>
     <row r="166">
@@ -1756,7 +1756,7 @@
         <v>36690</v>
       </c>
       <c r="B166" t="n">
-        <v>2.028333337392805</v>
+        <v>0.9436815178960705</v>
       </c>
     </row>
     <row r="167">
@@ -1764,7 +1764,7 @@
         <v>36691</v>
       </c>
       <c r="B167" t="n">
-        <v>-2.989992226370893</v>
+        <v>-1.991383998552025</v>
       </c>
     </row>
     <row r="168">
@@ -1772,7 +1772,7 @@
         <v>36692</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.5812413296993262</v>
+        <v>0.975158035139181</v>
       </c>
     </row>
     <row r="169">
@@ -1780,7 +1780,7 @@
         <v>36693</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.02236640082469089</v>
+        <v>-1.436095424460271</v>
       </c>
     </row>
     <row r="170">
@@ -1788,7 +1788,7 @@
         <v>36694</v>
       </c>
       <c r="B170" t="n">
-        <v>0.9485603125684885</v>
+        <v>1.141535725353881</v>
       </c>
     </row>
     <row r="171">
@@ -1796,7 +1796,7 @@
         <v>36695</v>
       </c>
       <c r="B171" t="n">
-        <v>1.937410003512439</v>
+        <v>0.1194737985376405</v>
       </c>
     </row>
     <row r="172">
@@ -1804,7 +1804,7 @@
         <v>36696</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.9678418520689938</v>
+        <v>-0.5608979217957752</v>
       </c>
     </row>
     <row r="173">
@@ -1812,7 +1812,7 @@
         <v>36697</v>
       </c>
       <c r="B173" t="n">
-        <v>0.1773912566976789</v>
+        <v>-0.1372735776794839</v>
       </c>
     </row>
     <row r="174">
@@ -1820,7 +1820,7 @@
         <v>36698</v>
       </c>
       <c r="B174" t="n">
-        <v>0.3224825759218263</v>
+        <v>0.2821788605805339</v>
       </c>
     </row>
     <row r="175">
@@ -1828,7 +1828,7 @@
         <v>36699</v>
       </c>
       <c r="B175" t="n">
-        <v>0.1535627594620368</v>
+        <v>-0.998190987396398</v>
       </c>
     </row>
     <row r="176">
@@ -1836,7 +1836,7 @@
         <v>36700</v>
       </c>
       <c r="B176" t="n">
-        <v>-0.0617140111854381</v>
+        <v>1.153236074113232</v>
       </c>
     </row>
     <row r="177">
@@ -1844,7 +1844,7 @@
         <v>36701</v>
       </c>
       <c r="B177" t="n">
-        <v>1.619456293608207</v>
+        <v>0.01366677793018739</v>
       </c>
     </row>
     <row r="178">
@@ -1852,7 +1852,7 @@
         <v>36702</v>
       </c>
       <c r="B178" t="n">
-        <v>0.3094945596214949</v>
+        <v>0.6144318990251689</v>
       </c>
     </row>
     <row r="179">
@@ -1860,7 +1860,7 @@
         <v>36703</v>
       </c>
       <c r="B179" t="n">
-        <v>-0.4834097098281273</v>
+        <v>0.5847296097450049</v>
       </c>
     </row>
     <row r="180">
@@ -1868,7 +1868,7 @@
         <v>36704</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.4677290020240864</v>
+        <v>0.6276398721349963</v>
       </c>
     </row>
     <row r="181">
@@ -1876,7 +1876,7 @@
         <v>36705</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.6149248288188803</v>
+        <v>1.161926915802306</v>
       </c>
     </row>
     <row r="182">
@@ -1884,7 +1884,7 @@
         <v>36706</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.03296382081357564</v>
+        <v>0.6980248842072392</v>
       </c>
     </row>
     <row r="183">
@@ -1892,7 +1892,7 @@
         <v>36707</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.07403611169882643</v>
+        <v>-0.5807845838175638</v>
       </c>
     </row>
     <row r="184">
@@ -1900,7 +1900,7 @@
         <v>36708</v>
       </c>
       <c r="B184" t="n">
-        <v>0.8525761605198053</v>
+        <v>0.08700653057507933</v>
       </c>
     </row>
     <row r="185">
@@ -1908,7 +1908,7 @@
         <v>36709</v>
       </c>
       <c r="B185" t="n">
-        <v>-0.4971772885237372</v>
+        <v>1.60100144122429</v>
       </c>
     </row>
     <row r="186">
@@ -1916,7 +1916,7 @@
         <v>36710</v>
       </c>
       <c r="B186" t="n">
-        <v>-0.09779623604637196</v>
+        <v>0.7828388065727109</v>
       </c>
     </row>
     <row r="187">
@@ -1924,7 +1924,7 @@
         <v>36711</v>
       </c>
       <c r="B187" t="n">
-        <v>1.240181271903582</v>
+        <v>1.383547535153879</v>
       </c>
     </row>
     <row r="188">
@@ -1932,7 +1932,7 @@
         <v>36712</v>
       </c>
       <c r="B188" t="n">
-        <v>0.7116992912731439</v>
+        <v>0.6295916778063095</v>
       </c>
     </row>
     <row r="189">
@@ -1940,7 +1940,7 @@
         <v>36713</v>
       </c>
       <c r="B189" t="n">
-        <v>2.357788289915966</v>
+        <v>1.001464119696554</v>
       </c>
     </row>
     <row r="190">
@@ -1948,7 +1948,7 @@
         <v>36714</v>
       </c>
       <c r="B190" t="n">
-        <v>-1.103751559439092</v>
+        <v>0.1836765518438284</v>
       </c>
     </row>
     <row r="191">
@@ -1956,7 +1956,7 @@
         <v>36715</v>
       </c>
       <c r="B191" t="n">
-        <v>0.3696292118047787</v>
+        <v>0.5293725203864303</v>
       </c>
     </row>
     <row r="192">
@@ -1964,7 +1964,7 @@
         <v>36716</v>
       </c>
       <c r="B192" t="n">
-        <v>-1.307585775481253</v>
+        <v>0.7324667702555665</v>
       </c>
     </row>
     <row r="193">
@@ -1972,7 +1972,7 @@
         <v>36717</v>
       </c>
       <c r="B193" t="n">
-        <v>0.4228931412583896</v>
+        <v>-0.2841838602934352</v>
       </c>
     </row>
     <row r="194">
@@ -1980,7 +1980,7 @@
         <v>36718</v>
       </c>
       <c r="B194" t="n">
-        <v>-1.141849150018598</v>
+        <v>0.4422338112344227</v>
       </c>
     </row>
     <row r="195">
@@ -1988,7 +1988,7 @@
         <v>36719</v>
       </c>
       <c r="B195" t="n">
-        <v>0.1849908529570447</v>
+        <v>-1.562322525239719</v>
       </c>
     </row>
     <row r="196">
@@ -1996,7 +1996,7 @@
         <v>36720</v>
       </c>
       <c r="B196" t="n">
-        <v>-1.12561081417574</v>
+        <v>-1.909492877061703</v>
       </c>
     </row>
     <row r="197">
@@ -2004,7 +2004,7 @@
         <v>36721</v>
       </c>
       <c r="B197" t="n">
-        <v>1.338026056116752</v>
+        <v>1.006996733746133</v>
       </c>
     </row>
     <row r="198">
@@ -2012,7 +2012,7 @@
         <v>36722</v>
       </c>
       <c r="B198" t="n">
-        <v>0.7528711701821011</v>
+        <v>0.09018193781874818</v>
       </c>
     </row>
     <row r="199">
@@ -2020,7 +2020,7 @@
         <v>36723</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.3558746700055775</v>
+        <v>-1.304961585397219</v>
       </c>
     </row>
     <row r="200">
@@ -2028,7 +2028,7 @@
         <v>36724</v>
       </c>
       <c r="B200" t="n">
-        <v>0.2812140680373394</v>
+        <v>-1.429244954586068</v>
       </c>
     </row>
     <row r="201">
@@ -2036,7 +2036,7 @@
         <v>36725</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.6424196394379958</v>
+        <v>1.746248698288624</v>
       </c>
     </row>
     <row r="202">
@@ -2044,7 +2044,7 @@
         <v>36726</v>
       </c>
       <c r="B202" t="n">
-        <v>0.08589438855986249</v>
+        <v>0.4407240497722068</v>
       </c>
     </row>
     <row r="203">
@@ -2052,7 +2052,7 @@
         <v>36727</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.2405953654480859</v>
+        <v>-1.548249533666307</v>
       </c>
     </row>
     <row r="204">
@@ -2060,7 +2060,7 @@
         <v>36728</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.1491094668183373</v>
+        <v>0.9677424832503577</v>
       </c>
     </row>
     <row r="205">
@@ -2068,7 +2068,7 @@
         <v>36729</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.05686741739387854</v>
+        <v>-0.4631011680849633</v>
       </c>
     </row>
     <row r="206">
@@ -2076,7 +2076,7 @@
         <v>36730</v>
       </c>
       <c r="B206" t="n">
-        <v>-0.2831738164292967</v>
+        <v>0.6147405770046157</v>
       </c>
     </row>
     <row r="207">
@@ -2084,7 +2084,7 @@
         <v>36731</v>
       </c>
       <c r="B207" t="n">
-        <v>-0.3028454685498765</v>
+        <v>0.3446050850571052</v>
       </c>
     </row>
     <row r="208">
@@ -2092,7 +2092,7 @@
         <v>36732</v>
       </c>
       <c r="B208" t="n">
-        <v>0.1909519200058289</v>
+        <v>0.4675169666038133</v>
       </c>
     </row>
     <row r="209">
@@ -2100,7 +2100,7 @@
         <v>36733</v>
       </c>
       <c r="B209" t="n">
-        <v>2.102407337589044</v>
+        <v>0.912038124878621</v>
       </c>
     </row>
     <row r="210">
@@ -2108,7 +2108,7 @@
         <v>36734</v>
       </c>
       <c r="B210" t="n">
-        <v>-0.9598847284657727</v>
+        <v>1.076988759988665</v>
       </c>
     </row>
     <row r="211">
@@ -2116,7 +2116,7 @@
         <v>36735</v>
       </c>
       <c r="B211" t="n">
-        <v>0.5783827923075795</v>
+        <v>0.5149523765224084</v>
       </c>
     </row>
     <row r="212">
@@ -2124,7 +2124,7 @@
         <v>36736</v>
       </c>
       <c r="B212" t="n">
-        <v>-1.382754615744703</v>
+        <v>1.333237991721308</v>
       </c>
     </row>
     <row r="213">
@@ -2132,7 +2132,7 @@
         <v>36737</v>
       </c>
       <c r="B213" t="n">
-        <v>-1.027042070173965</v>
+        <v>0.7837709675202735</v>
       </c>
     </row>
     <row r="214">
@@ -2140,7 +2140,7 @@
         <v>36738</v>
       </c>
       <c r="B214" t="n">
-        <v>-0.6884874095938187</v>
+        <v>1.927779047994647</v>
       </c>
     </row>
     <row r="215">
@@ -2148,7 +2148,7 @@
         <v>36739</v>
       </c>
       <c r="B215" t="n">
-        <v>0.9901671361808267</v>
+        <v>-2.059773075570155</v>
       </c>
     </row>
     <row r="216">
@@ -2156,7 +2156,7 @@
         <v>36740</v>
       </c>
       <c r="B216" t="n">
-        <v>0.691976146930399</v>
+        <v>0.4720434359640285</v>
       </c>
     </row>
     <row r="217">
@@ -2164,7 +2164,7 @@
         <v>36741</v>
       </c>
       <c r="B217" t="n">
-        <v>-1.266306857328138</v>
+        <v>-0.5087958231627813</v>
       </c>
     </row>
     <row r="218">
@@ -2172,7 +2172,7 @@
         <v>36742</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.430587122845516</v>
+        <v>-0.04757200858091249</v>
       </c>
     </row>
     <row r="219">
@@ -2180,7 +2180,7 @@
         <v>36743</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.500876564585816</v>
+        <v>-0.005897781646790515</v>
       </c>
     </row>
     <row r="220">
@@ -2188,7 +2188,7 @@
         <v>36744</v>
       </c>
       <c r="B220" t="n">
-        <v>0.07342932366598957</v>
+        <v>0.722333593521324</v>
       </c>
     </row>
     <row r="221">
@@ -2196,7 +2196,7 @@
         <v>36745</v>
       </c>
       <c r="B221" t="n">
-        <v>2.226655384606548</v>
+        <v>-0.4637999480967193</v>
       </c>
     </row>
     <row r="222">
@@ -2204,7 +2204,7 @@
         <v>36746</v>
       </c>
       <c r="B222" t="n">
-        <v>0.4690986678124334</v>
+        <v>-1.18821772674151</v>
       </c>
     </row>
     <row r="223">
@@ -2212,7 +2212,7 @@
         <v>36747</v>
       </c>
       <c r="B223" t="n">
-        <v>-0.5021290927420916</v>
+        <v>-0.5005190833455573</v>
       </c>
     </row>
     <row r="224">
@@ -2220,7 +2220,7 @@
         <v>36748</v>
       </c>
       <c r="B224" t="n">
-        <v>-0.9222683916078823</v>
+        <v>0.1119221542559786</v>
       </c>
     </row>
     <row r="225">
@@ -2228,7 +2228,7 @@
         <v>36749</v>
       </c>
       <c r="B225" t="n">
-        <v>0.3409650732880034</v>
+        <v>-0.5305622781279646</v>
       </c>
     </row>
     <row r="226">
@@ -2236,7 +2236,7 @@
         <v>36750</v>
       </c>
       <c r="B226" t="n">
-        <v>0.6336268496109917</v>
+        <v>-0.4483533144257815</v>
       </c>
     </row>
     <row r="227">
@@ -2244,7 +2244,7 @@
         <v>36751</v>
       </c>
       <c r="B227" t="n">
-        <v>-0.09488543432277881</v>
+        <v>1.777641708773991</v>
       </c>
     </row>
     <row r="228">
@@ -2252,7 +2252,7 @@
         <v>36752</v>
       </c>
       <c r="B228" t="n">
-        <v>-1.386566473576996</v>
+        <v>-1.264118387490709</v>
       </c>
     </row>
     <row r="229">
@@ -2260,7 +2260,7 @@
         <v>36753</v>
       </c>
       <c r="B229" t="n">
-        <v>-0.774778507220108</v>
+        <v>-0.4701113276014782</v>
       </c>
     </row>
     <row r="230">
@@ -2268,7 +2268,7 @@
         <v>36754</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.7654580637203954</v>
+        <v>0.3028088581968978</v>
       </c>
     </row>
     <row r="231">
@@ -2276,7 +2276,7 @@
         <v>36755</v>
       </c>
       <c r="B231" t="n">
-        <v>-1.64200984007872</v>
+        <v>-0.4912361873386976</v>
       </c>
     </row>
     <row r="232">
@@ -2284,7 +2284,7 @@
         <v>36756</v>
       </c>
       <c r="B232" t="n">
-        <v>0.186196609853477</v>
+        <v>0.3093657361172157</v>
       </c>
     </row>
     <row r="233">
@@ -2292,7 +2292,7 @@
         <v>36757</v>
       </c>
       <c r="B233" t="n">
-        <v>0.3393073934130518</v>
+        <v>0.7104175307479699</v>
       </c>
     </row>
     <row r="234">
@@ -2300,7 +2300,7 @@
         <v>36758</v>
       </c>
       <c r="B234" t="n">
-        <v>-1.277078086148482</v>
+        <v>-0.153096404481378</v>
       </c>
     </row>
     <row r="235">
@@ -2308,7 +2308,7 @@
         <v>36759</v>
       </c>
       <c r="B235" t="n">
-        <v>0.6902705260087413</v>
+        <v>-0.875773987865842</v>
       </c>
     </row>
     <row r="236">
@@ -2316,7 +2316,7 @@
         <v>36760</v>
       </c>
       <c r="B236" t="n">
-        <v>0.9447738353328592</v>
+        <v>1.191978662476974</v>
       </c>
     </row>
     <row r="237">
@@ -2324,7 +2324,7 @@
         <v>36761</v>
       </c>
       <c r="B237" t="n">
-        <v>-1.803541613382325</v>
+        <v>-0.3335641931264746</v>
       </c>
     </row>
     <row r="238">
@@ -2332,7 +2332,7 @@
         <v>36762</v>
       </c>
       <c r="B238" t="n">
-        <v>2.070662822882954</v>
+        <v>-0.770757845817818</v>
       </c>
     </row>
     <row r="239">
@@ -2340,7 +2340,7 @@
         <v>36763</v>
       </c>
       <c r="B239" t="n">
-        <v>0.6755856099851751</v>
+        <v>0.9498849654900856</v>
       </c>
     </row>
     <row r="240">
@@ -2348,7 +2348,7 @@
         <v>36764</v>
       </c>
       <c r="B240" t="n">
-        <v>0.3284577777640643</v>
+        <v>-0.5518825623477905</v>
       </c>
     </row>
     <row r="241">
@@ -2356,7 +2356,7 @@
         <v>36765</v>
       </c>
       <c r="B241" t="n">
-        <v>-0.9133176608417657</v>
+        <v>0.8112279132912157</v>
       </c>
     </row>
     <row r="242">
@@ -2364,7 +2364,7 @@
         <v>36766</v>
       </c>
       <c r="B242" t="n">
-        <v>0.9900642364905026</v>
+        <v>-0.7007607302226952</v>
       </c>
     </row>
     <row r="243">
@@ -2372,7 +2372,7 @@
         <v>36767</v>
       </c>
       <c r="B243" t="n">
-        <v>-0.4180430013663153</v>
+        <v>1.450194816591396</v>
       </c>
     </row>
     <row r="244">
@@ -2380,7 +2380,7 @@
         <v>36768</v>
       </c>
       <c r="B244" t="n">
-        <v>1.276928049534499</v>
+        <v>-0.8856789790040541</v>
       </c>
     </row>
     <row r="245">
@@ -2388,7 +2388,7 @@
         <v>36769</v>
       </c>
       <c r="B245" t="n">
-        <v>-0.2952294405101902</v>
+        <v>1.695284093555607</v>
       </c>
     </row>
     <row r="246">
@@ -2396,7 +2396,7 @@
         <v>36770</v>
       </c>
       <c r="B246" t="n">
-        <v>1.918179825125223</v>
+        <v>0.6813213264235936</v>
       </c>
     </row>
     <row r="247">
@@ -2404,7 +2404,7 @@
         <v>36771</v>
       </c>
       <c r="B247" t="n">
-        <v>0.7545281670007222</v>
+        <v>-0.654040159694075</v>
       </c>
     </row>
     <row r="248">
@@ -2412,7 +2412,7 @@
         <v>36772</v>
       </c>
       <c r="B248" t="n">
-        <v>-0.1317959776564454</v>
+        <v>-1.467611659965754</v>
       </c>
     </row>
     <row r="249">
@@ -2420,7 +2420,7 @@
         <v>36773</v>
       </c>
       <c r="B249" t="n">
-        <v>-1.386471747751558</v>
+        <v>1.032441757684625</v>
       </c>
     </row>
     <row r="250">
@@ -2428,7 +2428,7 @@
         <v>36774</v>
       </c>
       <c r="B250" t="n">
-        <v>-0.2616831664404812</v>
+        <v>-1.75318096832237</v>
       </c>
     </row>
     <row r="251">
@@ -2436,7 +2436,7 @@
         <v>36775</v>
       </c>
       <c r="B251" t="n">
-        <v>-1.295403306857238</v>
+        <v>-0.9265619824025193</v>
       </c>
     </row>
     <row r="252">
@@ -2444,7 +2444,7 @@
         <v>36776</v>
       </c>
       <c r="B252" t="n">
-        <v>-0.8618011924530365</v>
+        <v>-0.2873989257488386</v>
       </c>
     </row>
     <row r="253">
@@ -2452,7 +2452,7 @@
         <v>36777</v>
       </c>
       <c r="B253" t="n">
-        <v>1.436098356895587</v>
+        <v>1.786409052461761</v>
       </c>
     </row>
     <row r="254">
@@ -2460,7 +2460,7 @@
         <v>36778</v>
       </c>
       <c r="B254" t="n">
-        <v>-0.3926887032813504</v>
+        <v>2.082679169225938</v>
       </c>
     </row>
     <row r="255">
@@ -2468,7 +2468,7 @@
         <v>36779</v>
       </c>
       <c r="B255" t="n">
-        <v>0.5616697704120578</v>
+        <v>-1.374482390784759</v>
       </c>
     </row>
     <row r="256">
@@ -2476,7 +2476,7 @@
         <v>36780</v>
       </c>
       <c r="B256" t="n">
-        <v>-1.165974593786281</v>
+        <v>1.100387768260133</v>
       </c>
     </row>
     <row r="257">
@@ -2484,7 +2484,7 @@
         <v>36781</v>
       </c>
       <c r="B257" t="n">
-        <v>1.686026306865583</v>
+        <v>3.548743544944458</v>
       </c>
     </row>
     <row r="258">
@@ -2492,7 +2492,7 @@
         <v>36782</v>
       </c>
       <c r="B258" t="n">
-        <v>-0.3217687052435519</v>
+        <v>-0.1160308521190854</v>
       </c>
     </row>
     <row r="259">
@@ -2500,7 +2500,7 @@
         <v>36783</v>
       </c>
       <c r="B259" t="n">
-        <v>2.357812704082451</v>
+        <v>1.686053946516775</v>
       </c>
     </row>
     <row r="260">
@@ -2508,7 +2508,7 @@
         <v>36784</v>
       </c>
       <c r="B260" t="n">
-        <v>-1.241372171277685</v>
+        <v>-0.2272813533492198</v>
       </c>
     </row>
     <row r="261">
@@ -2516,7 +2516,7 @@
         <v>36785</v>
       </c>
       <c r="B261" t="n">
-        <v>0.7072847958004458</v>
+        <v>1.616488756910456</v>
       </c>
     </row>
     <row r="262">
@@ -2524,7 +2524,7 @@
         <v>36786</v>
       </c>
       <c r="B262" t="n">
-        <v>1.044954524065563</v>
+        <v>0.8814868051378945</v>
       </c>
     </row>
     <row r="263">
@@ -2532,7 +2532,7 @@
         <v>36787</v>
       </c>
       <c r="B263" t="n">
-        <v>-0.4198172638131277</v>
+        <v>-0.0776710715222505</v>
       </c>
     </row>
     <row r="264">
@@ -2540,7 +2540,7 @@
         <v>36788</v>
       </c>
       <c r="B264" t="n">
-        <v>-1.006477275730886</v>
+        <v>-0.6996085129862796</v>
       </c>
     </row>
     <row r="265">
@@ -2548,7 +2548,7 @@
         <v>36789</v>
       </c>
       <c r="B265" t="n">
-        <v>0.3033898074027236</v>
+        <v>0.2582460195484776</v>
       </c>
     </row>
     <row r="266">
@@ -2556,7 +2556,7 @@
         <v>36790</v>
       </c>
       <c r="B266" t="n">
-        <v>-0.4719995490519969</v>
+        <v>0.8767786004017595</v>
       </c>
     </row>
     <row r="267">
@@ -2564,7 +2564,7 @@
         <v>36791</v>
       </c>
       <c r="B267" t="n">
-        <v>0.1981047988305357</v>
+        <v>-0.1020684687054614</v>
       </c>
     </row>
     <row r="268">
@@ -2572,7 +2572,7 @@
         <v>36792</v>
       </c>
       <c r="B268" t="n">
-        <v>0.2890241551603558</v>
+        <v>-1.023300659862823</v>
       </c>
     </row>
     <row r="269">
@@ -2580,7 +2580,7 @@
         <v>36793</v>
       </c>
       <c r="B269" t="n">
-        <v>0.4638526620140521</v>
+        <v>-0.6316128860230695</v>
       </c>
     </row>
     <row r="270">
@@ -2588,7 +2588,7 @@
         <v>36794</v>
       </c>
       <c r="B270" t="n">
-        <v>-0.2613073838893001</v>
+        <v>-0.2841100421974928</v>
       </c>
     </row>
     <row r="271">
@@ -2596,7 +2596,7 @@
         <v>36795</v>
       </c>
       <c r="B271" t="n">
-        <v>0.6867105568976627</v>
+        <v>-0.5741952348922754</v>
       </c>
     </row>
     <row r="272">
@@ -2604,7 +2604,7 @@
         <v>36796</v>
       </c>
       <c r="B272" t="n">
-        <v>1.441254053438781</v>
+        <v>-1.114378261057879</v>
       </c>
     </row>
     <row r="273">
@@ -2612,7 +2612,7 @@
         <v>36797</v>
       </c>
       <c r="B273" t="n">
-        <v>0.5973547002507352</v>
+        <v>0.1346747598372098</v>
       </c>
     </row>
     <row r="274">
@@ -2620,7 +2620,7 @@
         <v>36798</v>
       </c>
       <c r="B274" t="n">
-        <v>0.4718070191684322</v>
+        <v>-1.500115576493157</v>
       </c>
     </row>
     <row r="275">
@@ -2628,7 +2628,7 @@
         <v>36799</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.4307209707686863</v>
+        <v>-0.2048079731276384</v>
       </c>
     </row>
     <row r="276">
@@ -2636,7 +2636,7 @@
         <v>36800</v>
       </c>
       <c r="B276" t="n">
-        <v>1.463338908342059</v>
+        <v>0.1012816129548712</v>
       </c>
     </row>
     <row r="277">
@@ -2644,7 +2644,7 @@
         <v>36801</v>
       </c>
       <c r="B277" t="n">
-        <v>-1.350584056695894</v>
+        <v>0.03808251270986628</v>
       </c>
     </row>
     <row r="278">
@@ -2652,7 +2652,7 @@
         <v>36802</v>
       </c>
       <c r="B278" t="n">
-        <v>-1.022109197090298</v>
+        <v>1.05793648084123</v>
       </c>
     </row>
     <row r="279">
@@ -2660,7 +2660,7 @@
         <v>36803</v>
       </c>
       <c r="B279" t="n">
-        <v>-1.189008067629814</v>
+        <v>0.3679232319953097</v>
       </c>
     </row>
     <row r="280">
@@ -2668,7 +2668,7 @@
         <v>36804</v>
       </c>
       <c r="B280" t="n">
-        <v>-0.7815672021684631</v>
+        <v>1.175650864979194</v>
       </c>
     </row>
     <row r="281">
@@ -2676,7 +2676,7 @@
         <v>36805</v>
       </c>
       <c r="B281" t="n">
-        <v>0.5159434273986023</v>
+        <v>-1.267257610093328</v>
       </c>
     </row>
     <row r="282">
@@ -2684,7 +2684,7 @@
         <v>36806</v>
       </c>
       <c r="B282" t="n">
-        <v>-1.391862492150269</v>
+        <v>-0.7388623917725053</v>
       </c>
     </row>
     <row r="283">
@@ -2692,7 +2692,7 @@
         <v>36807</v>
       </c>
       <c r="B283" t="n">
-        <v>1.029616190012469</v>
+        <v>-0.08589727370878351</v>
       </c>
     </row>
     <row r="284">
@@ -2700,7 +2700,7 @@
         <v>36808</v>
       </c>
       <c r="B284" t="n">
-        <v>1.567761106870161</v>
+        <v>1.427536817807907</v>
       </c>
     </row>
     <row r="285">
@@ -2708,7 +2708,7 @@
         <v>36809</v>
       </c>
       <c r="B285" t="n">
-        <v>0.9926531343644414</v>
+        <v>0.8187753690424776</v>
       </c>
     </row>
     <row r="286">
@@ -2716,7 +2716,7 @@
         <v>36810</v>
       </c>
       <c r="B286" t="n">
-        <v>-0.1061825418748005</v>
+        <v>-0.207124055485312</v>
       </c>
     </row>
     <row r="287">
@@ -2724,7 +2724,7 @@
         <v>36811</v>
       </c>
       <c r="B287" t="n">
-        <v>1.127963313595287</v>
+        <v>-0.6339867397997225</v>
       </c>
     </row>
     <row r="288">
@@ -2732,7 +2732,7 @@
         <v>36812</v>
       </c>
       <c r="B288" t="n">
-        <v>1.14153447291195</v>
+        <v>0.1394512093942409</v>
       </c>
     </row>
     <row r="289">
@@ -2740,7 +2740,7 @@
         <v>36813</v>
       </c>
       <c r="B289" t="n">
-        <v>-0.1875906102821957</v>
+        <v>0.1708419553898607</v>
       </c>
     </row>
     <row r="290">
@@ -2748,7 +2748,7 @@
         <v>36814</v>
       </c>
       <c r="B290" t="n">
-        <v>1.421675133543033</v>
+        <v>1.888444364123059</v>
       </c>
     </row>
     <row r="291">
@@ -2756,7 +2756,7 @@
         <v>36815</v>
       </c>
       <c r="B291" t="n">
-        <v>-0.1253806974272243</v>
+        <v>-1.449986017842494</v>
       </c>
     </row>
     <row r="292">
@@ -2764,7 +2764,7 @@
         <v>36816</v>
       </c>
       <c r="B292" t="n">
-        <v>1.253660944399379</v>
+        <v>0.6235346095673017</v>
       </c>
     </row>
     <row r="293">
@@ -2772,7 +2772,7 @@
         <v>36817</v>
       </c>
       <c r="B293" t="n">
-        <v>-0.5581261518787455</v>
+        <v>-0.2698559202888048</v>
       </c>
     </row>
     <row r="294">
@@ -2780,7 +2780,7 @@
         <v>36818</v>
       </c>
       <c r="B294" t="n">
-        <v>0.07742102920498861</v>
+        <v>1.142621734659298</v>
       </c>
     </row>
     <row r="295">
@@ -2788,7 +2788,7 @@
         <v>36819</v>
       </c>
       <c r="B295" t="n">
-        <v>-0.4950357797346622</v>
+        <v>-1.563662420141862</v>
       </c>
     </row>
     <row r="296">
@@ -2796,7 +2796,7 @@
         <v>36820</v>
       </c>
       <c r="B296" t="n">
-        <v>-1.116128403687112</v>
+        <v>-0.8920526320536633</v>
       </c>
     </row>
     <row r="297">
@@ -2804,7 +2804,7 @@
         <v>36821</v>
       </c>
       <c r="B297" t="n">
-        <v>-1.019868747825683</v>
+        <v>0.4853499092030226</v>
       </c>
     </row>
     <row r="298">
@@ -2812,7 +2812,7 @@
         <v>36822</v>
       </c>
       <c r="B298" t="n">
-        <v>-0.2126581210558736</v>
+        <v>-0.7646518754613149</v>
       </c>
     </row>
     <row r="299">
@@ -2820,7 +2820,7 @@
         <v>36823</v>
       </c>
       <c r="B299" t="n">
-        <v>2.329444056976001</v>
+        <v>1.30098724112006</v>
       </c>
     </row>
     <row r="300">
@@ -2828,7 +2828,7 @@
         <v>36824</v>
       </c>
       <c r="B300" t="n">
-        <v>0.3512589973239397</v>
+        <v>1.039031569528771</v>
       </c>
     </row>
     <row r="301">
@@ -2836,7 +2836,7 @@
         <v>36825</v>
       </c>
       <c r="B301" t="n">
-        <v>-0.8334901395488239</v>
+        <v>-1.557348338390598</v>
       </c>
     </row>
     <row r="302">
@@ -2844,7 +2844,7 @@
         <v>36826</v>
       </c>
       <c r="B302" t="n">
-        <v>-0.8461190097188525</v>
+        <v>-0.6718310765128276</v>
       </c>
     </row>
     <row r="303">
@@ -2852,7 +2852,7 @@
         <v>36827</v>
       </c>
       <c r="B303" t="n">
-        <v>0.2730630808001806</v>
+        <v>1.600030741695197</v>
       </c>
     </row>
     <row r="304">
@@ -2860,7 +2860,7 @@
         <v>36828</v>
       </c>
       <c r="B304" t="n">
-        <v>1.939083791155997</v>
+        <v>-0.8502878334856958</v>
       </c>
     </row>
     <row r="305">
@@ -2868,7 +2868,7 @@
         <v>36829</v>
       </c>
       <c r="B305" t="n">
-        <v>-0.7704038772725187</v>
+        <v>-0.09894094769190692</v>
       </c>
     </row>
     <row r="306">
@@ -2876,7 +2876,7 @@
         <v>36830</v>
       </c>
       <c r="B306" t="n">
-        <v>0.7999634666736883</v>
+        <v>-0.2989169168382282</v>
       </c>
     </row>
     <row r="307">
@@ -2884,7 +2884,7 @@
         <v>36831</v>
       </c>
       <c r="B307" t="n">
-        <v>-0.7100652003303052</v>
+        <v>0.8950591336408276</v>
       </c>
     </row>
     <row r="308">
@@ -2892,7 +2892,7 @@
         <v>36832</v>
       </c>
       <c r="B308" t="n">
-        <v>0.8373764753689803</v>
+        <v>1.83164582397414</v>
       </c>
     </row>
     <row r="309">
@@ -2900,7 +2900,7 @@
         <v>36833</v>
       </c>
       <c r="B309" t="n">
-        <v>1.056182934738379</v>
+        <v>-0.2451535003638038</v>
       </c>
     </row>
     <row r="310">
@@ -2908,7 +2908,7 @@
         <v>36834</v>
       </c>
       <c r="B310" t="n">
-        <v>0.1277302435375379</v>
+        <v>1.704998310861293</v>
       </c>
     </row>
     <row r="311">
@@ -2916,7 +2916,7 @@
         <v>36835</v>
       </c>
       <c r="B311" t="n">
-        <v>0.4310219892968623</v>
+        <v>-0.2126903271390698</v>
       </c>
     </row>
     <row r="312">
@@ -2924,7 +2924,7 @@
         <v>36836</v>
       </c>
       <c r="B312" t="n">
-        <v>-0.01207290644666465</v>
+        <v>0.495530184603567</v>
       </c>
     </row>
     <row r="313">
@@ -2932,7 +2932,7 @@
         <v>36837</v>
       </c>
       <c r="B313" t="n">
-        <v>0.1346021702209477</v>
+        <v>-0.360557426375354</v>
       </c>
     </row>
     <row r="314">
@@ -2940,7 +2940,7 @@
         <v>36838</v>
       </c>
       <c r="B314" t="n">
-        <v>-1.404017817387746</v>
+        <v>0.5869788403351457</v>
       </c>
     </row>
     <row r="315">
@@ -2948,7 +2948,7 @@
         <v>36839</v>
       </c>
       <c r="B315" t="n">
-        <v>1.299966719676785</v>
+        <v>-0.8671863919834415</v>
       </c>
     </row>
     <row r="316">
@@ -2956,7 +2956,7 @@
         <v>36840</v>
       </c>
       <c r="B316" t="n">
-        <v>1.414722991866346</v>
+        <v>-0.8184163441057416</v>
       </c>
     </row>
     <row r="317">
@@ -2964,7 +2964,7 @@
         <v>36841</v>
       </c>
       <c r="B317" t="n">
-        <v>-0.195700891799608</v>
+        <v>0.7542150042359371</v>
       </c>
     </row>
     <row r="318">
@@ -2972,7 +2972,7 @@
         <v>36842</v>
       </c>
       <c r="B318" t="n">
-        <v>1.852339159722062</v>
+        <v>-1.636592084899795</v>
       </c>
     </row>
     <row r="319">
@@ -2980,7 +2980,7 @@
         <v>36843</v>
       </c>
       <c r="B319" t="n">
-        <v>-2.050540142821682</v>
+        <v>0.6248882751488369</v>
       </c>
     </row>
     <row r="320">
@@ -2988,7 +2988,7 @@
         <v>36844</v>
       </c>
       <c r="B320" t="n">
-        <v>-0.4901828587173129</v>
+        <v>-0.890707231583576</v>
       </c>
     </row>
     <row r="321">
@@ -2996,7 +2996,7 @@
         <v>36845</v>
       </c>
       <c r="B321" t="n">
-        <v>0.05184269021343716</v>
+        <v>-0.2840411591582834</v>
       </c>
     </row>
     <row r="322">
@@ -3004,7 +3004,7 @@
         <v>36846</v>
       </c>
       <c r="B322" t="n">
-        <v>-1.143123260489016</v>
+        <v>-0.5765793368327774</v>
       </c>
     </row>
     <row r="323">
@@ -3012,7 +3012,7 @@
         <v>36847</v>
       </c>
       <c r="B323" t="n">
-        <v>0.6088894963876508</v>
+        <v>2.267110498066864</v>
       </c>
     </row>
     <row r="324">
@@ -3020,7 +3020,7 @@
         <v>36848</v>
       </c>
       <c r="B324" t="n">
-        <v>-1.051804151988784</v>
+        <v>0.6581228301510829</v>
       </c>
     </row>
     <row r="325">
@@ -3028,7 +3028,7 @@
         <v>36849</v>
       </c>
       <c r="B325" t="n">
-        <v>-1.430769937360118</v>
+        <v>-0.4713775500382126</v>
       </c>
     </row>
     <row r="326">
@@ -3036,7 +3036,7 @@
         <v>36850</v>
       </c>
       <c r="B326" t="n">
-        <v>1.108563651995596</v>
+        <v>1.199042658606805</v>
       </c>
     </row>
     <row r="327">
@@ -3044,7 +3044,7 @@
         <v>36851</v>
       </c>
       <c r="B327" t="n">
-        <v>-0.4087717056352028</v>
+        <v>0.4479211000466375</v>
       </c>
     </row>
     <row r="328">
@@ -3052,7 +3052,7 @@
         <v>36852</v>
       </c>
       <c r="B328" t="n">
-        <v>1.410472845654467</v>
+        <v>-0.5028625361034718</v>
       </c>
     </row>
     <row r="329">
@@ -3060,7 +3060,7 @@
         <v>36853</v>
       </c>
       <c r="B329" t="n">
-        <v>-0.4870258136349058</v>
+        <v>-1.618103794499087</v>
       </c>
     </row>
     <row r="330">
@@ -3068,7 +3068,7 @@
         <v>36854</v>
       </c>
       <c r="B330" t="n">
-        <v>-1.248725566652651</v>
+        <v>0.5100563417685705</v>
       </c>
     </row>
     <row r="331">
@@ -3076,7 +3076,7 @@
         <v>36855</v>
       </c>
       <c r="B331" t="n">
-        <v>0.6520040073330097</v>
+        <v>1.42316908633157</v>
       </c>
     </row>
     <row r="332">
@@ -3084,7 +3084,7 @@
         <v>36856</v>
       </c>
       <c r="B332" t="n">
-        <v>1.698774977198615</v>
+        <v>-0.3555060607342928</v>
       </c>
     </row>
     <row r="333">
@@ -3092,7 +3092,7 @@
         <v>36857</v>
       </c>
       <c r="B333" t="n">
-        <v>0.2210213494077966</v>
+        <v>-0.9466245742204766</v>
       </c>
     </row>
     <row r="334">
@@ -3100,7 +3100,7 @@
         <v>36858</v>
       </c>
       <c r="B334" t="n">
-        <v>1.783941327729492</v>
+        <v>-1.406332675392017</v>
       </c>
     </row>
     <row r="335">
@@ -3108,7 +3108,7 @@
         <v>36859</v>
       </c>
       <c r="B335" t="n">
-        <v>-0.9588031692683388</v>
+        <v>0.2143805163200656</v>
       </c>
     </row>
     <row r="336">
@@ -3116,7 +3116,7 @@
         <v>36860</v>
       </c>
       <c r="B336" t="n">
-        <v>-0.7718588974154773</v>
+        <v>-0.957733714229548</v>
       </c>
     </row>
     <row r="337">
@@ -3124,7 +3124,7 @@
         <v>36861</v>
       </c>
       <c r="B337" t="n">
-        <v>1.69322844037935</v>
+        <v>0.9608010239042927</v>
       </c>
     </row>
     <row r="338">
@@ -3132,7 +3132,7 @@
         <v>36862</v>
       </c>
       <c r="B338" t="n">
-        <v>0.2838753825619379</v>
+        <v>-0.3891962903549273</v>
       </c>
     </row>
     <row r="339">
@@ -3140,7 +3140,7 @@
         <v>36863</v>
       </c>
       <c r="B339" t="n">
-        <v>-0.42987707200151</v>
+        <v>0.5103785399650914</v>
       </c>
     </row>
     <row r="340">
@@ -3148,7 +3148,7 @@
         <v>36864</v>
       </c>
       <c r="B340" t="n">
-        <v>-0.05919928076141741</v>
+        <v>-0.7485693195412232</v>
       </c>
     </row>
     <row r="341">
@@ -3156,7 +3156,7 @@
         <v>36865</v>
       </c>
       <c r="B341" t="n">
-        <v>0.09489137620577703</v>
+        <v>-0.3916320411552628</v>
       </c>
     </row>
     <row r="342">
@@ -3164,7 +3164,7 @@
         <v>36866</v>
       </c>
       <c r="B342" t="n">
-        <v>-2.165492250982523</v>
+        <v>-0.1064832057627101</v>
       </c>
     </row>
     <row r="343">
@@ -3172,7 +3172,7 @@
         <v>36867</v>
       </c>
       <c r="B343" t="n">
-        <v>0.1606314249465511</v>
+        <v>0.491919648732613</v>
       </c>
     </row>
     <row r="344">
@@ -3180,7 +3180,7 @@
         <v>36868</v>
       </c>
       <c r="B344" t="n">
-        <v>1.029207624968058</v>
+        <v>0.3490746649124261</v>
       </c>
     </row>
     <row r="345">
@@ -3188,7 +3188,7 @@
         <v>36869</v>
       </c>
       <c r="B345" t="n">
-        <v>1.048482772804773</v>
+        <v>-0.009189904570776309</v>
       </c>
     </row>
     <row r="346">
@@ -3196,7 +3196,7 @@
         <v>36870</v>
       </c>
       <c r="B346" t="n">
-        <v>-0.4367263446595617</v>
+        <v>-0.3505634918192095</v>
       </c>
     </row>
     <row r="347">
@@ -3204,7 +3204,7 @@
         <v>36871</v>
       </c>
       <c r="B347" t="n">
-        <v>-0.7873187267348516</v>
+        <v>1.342760482753044</v>
       </c>
     </row>
     <row r="348">
@@ -3212,7 +3212,7 @@
         <v>36872</v>
       </c>
       <c r="B348" t="n">
-        <v>-0.258145339464596</v>
+        <v>-0.2541452047119132</v>
       </c>
     </row>
     <row r="349">
@@ -3220,7 +3220,7 @@
         <v>36873</v>
       </c>
       <c r="B349" t="n">
-        <v>-0.2521964970043886</v>
+        <v>-0.235017886979107</v>
       </c>
     </row>
     <row r="350">
@@ -3228,7 +3228,7 @@
         <v>36874</v>
       </c>
       <c r="B350" t="n">
-        <v>-0.6019085517754228</v>
+        <v>0.5770372066657182</v>
       </c>
     </row>
     <row r="351">
@@ -3236,7 +3236,7 @@
         <v>36875</v>
       </c>
       <c r="B351" t="n">
-        <v>-1.29623029806956</v>
+        <v>-0.2115531423757985</v>
       </c>
     </row>
     <row r="352">
@@ -3244,7 +3244,7 @@
         <v>36876</v>
       </c>
       <c r="B352" t="n">
-        <v>0.2581749856810381</v>
+        <v>-2.769665896897477</v>
       </c>
     </row>
     <row r="353">
@@ -3252,7 +3252,7 @@
         <v>36877</v>
       </c>
       <c r="B353" t="n">
-        <v>-0.5916370691130335</v>
+        <v>0.7298093138188088</v>
       </c>
     </row>
     <row r="354">
@@ -3260,7 +3260,7 @@
         <v>36878</v>
       </c>
       <c r="B354" t="n">
-        <v>-0.6114831721360192</v>
+        <v>-0.7513653620315356</v>
       </c>
     </row>
     <row r="355">
@@ -3268,7 +3268,7 @@
         <v>36879</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.2947751289852691</v>
+        <v>-0.2071679787212581</v>
       </c>
     </row>
     <row r="356">
@@ -3276,7 +3276,7 @@
         <v>36880</v>
       </c>
       <c r="B356" t="n">
-        <v>-1.161277272658239</v>
+        <v>0.4010523885143339</v>
       </c>
     </row>
     <row r="357">
@@ -3284,7 +3284,7 @@
         <v>36881</v>
       </c>
       <c r="B357" t="n">
-        <v>0.01367866059495288</v>
+        <v>1.088468419840136</v>
       </c>
     </row>
     <row r="358">
@@ -3292,7 +3292,7 @@
         <v>36882</v>
       </c>
       <c r="B358" t="n">
-        <v>-0.4520642659958544</v>
+        <v>0.5518972207867874</v>
       </c>
     </row>
     <row r="359">
@@ -3300,7 +3300,7 @@
         <v>36883</v>
       </c>
       <c r="B359" t="n">
-        <v>0.7171247628099213</v>
+        <v>1.01858341789357</v>
       </c>
     </row>
     <row r="360">
@@ -3308,7 +3308,7 @@
         <v>36884</v>
       </c>
       <c r="B360" t="n">
-        <v>-1.678771506459267</v>
+        <v>-0.7840478495151439</v>
       </c>
     </row>
     <row r="361">
@@ -3316,7 +3316,7 @@
         <v>36885</v>
       </c>
       <c r="B361" t="n">
-        <v>0.6226753937019628</v>
+        <v>-0.259117795247199</v>
       </c>
     </row>
     <row r="362">
@@ -3324,7 +3324,7 @@
         <v>36886</v>
       </c>
       <c r="B362" t="n">
-        <v>1.520724141743692</v>
+        <v>-0.8275466632052936</v>
       </c>
     </row>
     <row r="363">
@@ -3332,7 +3332,7 @@
         <v>36887</v>
       </c>
       <c r="B363" t="n">
-        <v>-0.4993969107404677</v>
+        <v>0.2545850107720626</v>
       </c>
     </row>
     <row r="364">
@@ -3340,7 +3340,7 @@
         <v>36888</v>
       </c>
       <c r="B364" t="n">
-        <v>-0.1523063849365643</v>
+        <v>0.4032231557935939</v>
       </c>
     </row>
     <row r="365">
@@ -3348,7 +3348,7 @@
         <v>36889</v>
       </c>
       <c r="B365" t="n">
-        <v>1.151337608194454</v>
+        <v>0.3698416335995277</v>
       </c>
     </row>
     <row r="366">
@@ -3356,7 +3356,7 @@
         <v>36890</v>
       </c>
       <c r="B366" t="n">
-        <v>-1.031578209091427</v>
+        <v>-1.180757982689133</v>
       </c>
     </row>
     <row r="367">
@@ -3364,7 +3364,7 @@
         <v>36891</v>
       </c>
       <c r="B367" t="n">
-        <v>0.7783750687458346</v>
+        <v>-0.3572323001960417</v>
       </c>
     </row>
     <row r="368">
@@ -3372,7 +3372,7 @@
         <v>36892</v>
       </c>
       <c r="B368" t="n">
-        <v>0.2174950106873652</v>
+        <v>0.3818619358923826</v>
       </c>
     </row>
     <row r="369">
@@ -3380,7 +3380,7 @@
         <v>36893</v>
       </c>
       <c r="B369" t="n">
-        <v>0.3083426363050881</v>
+        <v>0.5261877380467131</v>
       </c>
     </row>
     <row r="370">
@@ -3388,7 +3388,7 @@
         <v>36894</v>
       </c>
       <c r="B370" t="n">
-        <v>-0.44519021968788</v>
+        <v>0.4374036986061106</v>
       </c>
     </row>
     <row r="371">
@@ -3396,7 +3396,7 @@
         <v>36895</v>
       </c>
       <c r="B371" t="n">
-        <v>1.492265489631629</v>
+        <v>0.7768272811846589</v>
       </c>
     </row>
     <row r="372">
@@ -3404,7 +3404,7 @@
         <v>36896</v>
       </c>
       <c r="B372" t="n">
-        <v>-1.868230565441816</v>
+        <v>0.5646318019590867</v>
       </c>
     </row>
     <row r="373">
@@ -3412,7 +3412,7 @@
         <v>36897</v>
       </c>
       <c r="B373" t="n">
-        <v>1.562134824557174</v>
+        <v>0.643458665702938</v>
       </c>
     </row>
     <row r="374">
@@ -3420,7 +3420,7 @@
         <v>36898</v>
       </c>
       <c r="B374" t="n">
-        <v>0.03182180646562925</v>
+        <v>-0.02920385913720611</v>
       </c>
     </row>
     <row r="375">
@@ -3428,7 +3428,7 @@
         <v>36899</v>
       </c>
       <c r="B375" t="n">
-        <v>2.076440277511624</v>
+        <v>1.460640389541441</v>
       </c>
     </row>
     <row r="376">
@@ -3436,7 +3436,7 @@
         <v>36900</v>
       </c>
       <c r="B376" t="n">
-        <v>-1.039269411337281</v>
+        <v>-0.04007486520423651</v>
       </c>
     </row>
     <row r="377">
@@ -3444,7 +3444,7 @@
         <v>36901</v>
       </c>
       <c r="B377" t="n">
-        <v>1.00539455556752</v>
+        <v>-1.540872556501538</v>
       </c>
     </row>
     <row r="378">
@@ -3452,7 +3452,7 @@
         <v>36902</v>
       </c>
       <c r="B378" t="n">
-        <v>-0.9740163501514827</v>
+        <v>-0.3116157855151536</v>
       </c>
     </row>
     <row r="379">
@@ -3460,7 +3460,7 @@
         <v>36903</v>
       </c>
       <c r="B379" t="n">
-        <v>-0.9665315058346156</v>
+        <v>0.4495724267703785</v>
       </c>
     </row>
     <row r="380">
@@ -3468,7 +3468,7 @@
         <v>36904</v>
       </c>
       <c r="B380" t="n">
-        <v>0.9989443393850468</v>
+        <v>0.1403462276999774</v>
       </c>
     </row>
     <row r="381">
@@ -3476,7 +3476,7 @@
         <v>36905</v>
       </c>
       <c r="B381" t="n">
-        <v>0.2772385495611762</v>
+        <v>0.3290944383079109</v>
       </c>
     </row>
     <row r="382">
@@ -3484,7 +3484,7 @@
         <v>36906</v>
       </c>
       <c r="B382" t="n">
-        <v>-0.5331389666682365</v>
+        <v>-1.433904592806097</v>
       </c>
     </row>
     <row r="383">
@@ -3492,7 +3492,7 @@
         <v>36907</v>
       </c>
       <c r="B383" t="n">
-        <v>1.133310628541287</v>
+        <v>0.9950167273230244</v>
       </c>
     </row>
     <row r="384">
@@ -3500,7 +3500,7 @@
         <v>36908</v>
       </c>
       <c r="B384" t="n">
-        <v>0.04396451200695436</v>
+        <v>0.09650828311452948</v>
       </c>
     </row>
     <row r="385">
@@ -3508,7 +3508,7 @@
         <v>36909</v>
       </c>
       <c r="B385" t="n">
-        <v>-0.2315096735669474</v>
+        <v>0.1344988331573851</v>
       </c>
     </row>
     <row r="386">
@@ -3516,7 +3516,7 @@
         <v>36910</v>
       </c>
       <c r="B386" t="n">
-        <v>0.6322332425249784</v>
+        <v>0.1198128636468464</v>
       </c>
     </row>
     <row r="387">
@@ -3524,7 +3524,7 @@
         <v>36911</v>
       </c>
       <c r="B387" t="n">
-        <v>-0.6908355743104807</v>
+        <v>1.754557628616493</v>
       </c>
     </row>
     <row r="388">
@@ -3532,7 +3532,7 @@
         <v>36912</v>
       </c>
       <c r="B388" t="n">
-        <v>0.97947915619005</v>
+        <v>0.7055098198220066</v>
       </c>
     </row>
     <row r="389">
@@ -3540,7 +3540,7 @@
         <v>36913</v>
       </c>
       <c r="B389" t="n">
-        <v>-0.3093094335608212</v>
+        <v>-1.387871023213363</v>
       </c>
     </row>
     <row r="390">
@@ -3548,7 +3548,7 @@
         <v>36914</v>
       </c>
       <c r="B390" t="n">
-        <v>1.706672959187654</v>
+        <v>-1.039261990192145</v>
       </c>
     </row>
     <row r="391">
@@ -3556,7 +3556,7 @@
         <v>36915</v>
       </c>
       <c r="B391" t="n">
-        <v>0.8877737976022504</v>
+        <v>-0.2223685415814565</v>
       </c>
     </row>
     <row r="392">
@@ -3564,7 +3564,7 @@
         <v>36916</v>
       </c>
       <c r="B392" t="n">
-        <v>2.075874377859359</v>
+        <v>0.09750565217019679</v>
       </c>
     </row>
     <row r="393">
@@ -3572,7 +3572,7 @@
         <v>36917</v>
       </c>
       <c r="B393" t="n">
-        <v>0.07715064197277115</v>
+        <v>-0.6695067057293256</v>
       </c>
     </row>
     <row r="394">
@@ -3580,7 +3580,7 @@
         <v>36918</v>
       </c>
       <c r="B394" t="n">
-        <v>-1.449603672046818</v>
+        <v>1.907063072880819</v>
       </c>
     </row>
     <row r="395">
@@ -3588,7 +3588,7 @@
         <v>36919</v>
       </c>
       <c r="B395" t="n">
-        <v>0.03242070553713948</v>
+        <v>0.1228774972929821</v>
       </c>
     </row>
     <row r="396">
@@ -3596,7 +3596,7 @@
         <v>36920</v>
       </c>
       <c r="B396" t="n">
-        <v>-0.994200824735293</v>
+        <v>1.352048033098953</v>
       </c>
     </row>
     <row r="397">
@@ -3604,7 +3604,7 @@
         <v>36921</v>
       </c>
       <c r="B397" t="n">
-        <v>1.189410828036697</v>
+        <v>0.608733903253137</v>
       </c>
     </row>
     <row r="398">
@@ -3612,7 +3612,7 @@
         <v>36922</v>
       </c>
       <c r="B398" t="n">
-        <v>0.6494586363133252</v>
+        <v>-0.4472732544276148</v>
       </c>
     </row>
     <row r="399">
@@ -3620,7 +3620,7 @@
         <v>36923</v>
       </c>
       <c r="B399" t="n">
-        <v>-1.175721805752681</v>
+        <v>-1.138566642638481</v>
       </c>
     </row>
     <row r="400">
@@ -3628,7 +3628,7 @@
         <v>36924</v>
       </c>
       <c r="B400" t="n">
-        <v>0.7355575541044658</v>
+        <v>-0.6905832328612949</v>
       </c>
     </row>
     <row r="401">
@@ -3636,7 +3636,7 @@
         <v>36925</v>
       </c>
       <c r="B401" t="n">
-        <v>-1.174843847051095</v>
+        <v>-0.2711685217614401</v>
       </c>
     </row>
     <row r="402">
@@ -3644,7 +3644,7 @@
         <v>36926</v>
       </c>
       <c r="B402" t="n">
-        <v>0.5961382539200325</v>
+        <v>-1.747965052290758</v>
       </c>
     </row>
     <row r="403">
@@ -3652,7 +3652,7 @@
         <v>36927</v>
       </c>
       <c r="B403" t="n">
-        <v>1.26970446025014</v>
+        <v>-3.000007689254076</v>
       </c>
     </row>
     <row r="404">
@@ -3660,7 +3660,7 @@
         <v>36928</v>
       </c>
       <c r="B404" t="n">
-        <v>-2.017424278895109</v>
+        <v>1.211957353792785</v>
       </c>
     </row>
     <row r="405">
@@ -3668,7 +3668,7 @@
         <v>36929</v>
       </c>
       <c r="B405" t="n">
-        <v>1.275891514448921</v>
+        <v>0.7622876308175038</v>
       </c>
     </row>
     <row r="406">
@@ -3676,7 +3676,7 @@
         <v>36930</v>
       </c>
       <c r="B406" t="n">
-        <v>1.524850734824322</v>
+        <v>-0.561306754523614</v>
       </c>
     </row>
     <row r="407">
@@ -3684,7 +3684,7 @@
         <v>36931</v>
       </c>
       <c r="B407" t="n">
-        <v>-0.7772798917038872</v>
+        <v>-0.07650108398892823</v>
       </c>
     </row>
     <row r="408">
@@ -3692,7 +3692,7 @@
         <v>36932</v>
       </c>
       <c r="B408" t="n">
-        <v>0.1426229994623201</v>
+        <v>0.6838221319298891</v>
       </c>
     </row>
     <row r="409">
@@ -3700,7 +3700,7 @@
         <v>36933</v>
       </c>
       <c r="B409" t="n">
-        <v>1.717325814992015</v>
+        <v>-1.75402985942299</v>
       </c>
     </row>
     <row r="410">
@@ -3708,7 +3708,7 @@
         <v>36934</v>
       </c>
       <c r="B410" t="n">
-        <v>-1.345859129241302</v>
+        <v>1.090320146758452</v>
       </c>
     </row>
     <row r="411">
@@ -3716,7 +3716,7 @@
         <v>36935</v>
       </c>
       <c r="B411" t="n">
-        <v>0.4598434995477896</v>
+        <v>-1.212351272251243</v>
       </c>
     </row>
     <row r="412">
@@ -3724,7 +3724,7 @@
         <v>36936</v>
       </c>
       <c r="B412" t="n">
-        <v>1.433148662133762</v>
+        <v>1.028231600004378</v>
       </c>
     </row>
     <row r="413">
@@ -3732,7 +3732,7 @@
         <v>36937</v>
       </c>
       <c r="B413" t="n">
-        <v>0.1443755455876161</v>
+        <v>-1.711883145004474</v>
       </c>
     </row>
     <row r="414">
@@ -3740,7 +3740,7 @@
         <v>36938</v>
       </c>
       <c r="B414" t="n">
-        <v>-2.238273255981144</v>
+        <v>0.1660888349154563</v>
       </c>
     </row>
     <row r="415">
@@ -3748,7 +3748,7 @@
         <v>36939</v>
       </c>
       <c r="B415" t="n">
-        <v>-1.442767000545725</v>
+        <v>-1.338758404920412</v>
       </c>
     </row>
     <row r="416">
@@ -3756,7 +3756,7 @@
         <v>36940</v>
       </c>
       <c r="B416" t="n">
-        <v>-1.004761486095984</v>
+        <v>-0.4493522947121571</v>
       </c>
     </row>
     <row r="417">
@@ -3764,7 +3764,7 @@
         <v>36941</v>
       </c>
       <c r="B417" t="n">
-        <v>1.348231062535757</v>
+        <v>-0.728622351985168</v>
       </c>
     </row>
     <row r="418">
@@ -3772,7 +3772,7 @@
         <v>36942</v>
       </c>
       <c r="B418" t="n">
-        <v>1.078782280189828</v>
+        <v>-0.5457520034020863</v>
       </c>
     </row>
     <row r="419">
@@ -3780,7 +3780,7 @@
         <v>36943</v>
       </c>
       <c r="B419" t="n">
-        <v>-1.073712915225475</v>
+        <v>-1.754776754909662</v>
       </c>
     </row>
     <row r="420">
@@ -3788,7 +3788,7 @@
         <v>36944</v>
       </c>
       <c r="B420" t="n">
-        <v>1.229364730723528</v>
+        <v>1.452837815021957</v>
       </c>
     </row>
     <row r="421">
@@ -3796,7 +3796,7 @@
         <v>36945</v>
       </c>
       <c r="B421" t="n">
-        <v>0.3822042481936321</v>
+        <v>0.3264881172548655</v>
       </c>
     </row>
     <row r="422">
@@ -3804,7 +3804,7 @@
         <v>36946</v>
       </c>
       <c r="B422" t="n">
-        <v>-1.60230018044936</v>
+        <v>-0.3312753598491998</v>
       </c>
     </row>
     <row r="423">
@@ -3812,7 +3812,7 @@
         <v>36947</v>
       </c>
       <c r="B423" t="n">
-        <v>0.07446909826741181</v>
+        <v>-0.7514861682422406</v>
       </c>
     </row>
     <row r="424">
@@ -3820,7 +3820,7 @@
         <v>36948</v>
       </c>
       <c r="B424" t="n">
-        <v>0.5186064747390414</v>
+        <v>-1.654748029581931</v>
       </c>
     </row>
     <row r="425">
@@ -3828,7 +3828,7 @@
         <v>36949</v>
       </c>
       <c r="B425" t="n">
-        <v>-0.3428335989064913</v>
+        <v>0.2469075531524014</v>
       </c>
     </row>
     <row r="426">
@@ -3836,7 +3836,7 @@
         <v>36950</v>
       </c>
       <c r="B426" t="n">
-        <v>0.03859789121376045</v>
+        <v>1.972922236977694</v>
       </c>
     </row>
     <row r="427">
@@ -3844,7 +3844,7 @@
         <v>36951</v>
       </c>
       <c r="B427" t="n">
-        <v>0.002100325369060834</v>
+        <v>-0.8662214363447858</v>
       </c>
     </row>
     <row r="428">
@@ -3852,7 +3852,7 @@
         <v>36952</v>
       </c>
       <c r="B428" t="n">
-        <v>-1.383465157796155</v>
+        <v>-1.473008552352248</v>
       </c>
     </row>
     <row r="429">
@@ -3860,7 +3860,7 @@
         <v>36953</v>
       </c>
       <c r="B429" t="n">
-        <v>1.143212720570695</v>
+        <v>0.7357360181959771</v>
       </c>
     </row>
     <row r="430">
@@ -3868,7 +3868,7 @@
         <v>36954</v>
       </c>
       <c r="B430" t="n">
-        <v>-0.2554696951352992</v>
+        <v>-0.413031116142595</v>
       </c>
     </row>
     <row r="431">
@@ -3876,7 +3876,7 @@
         <v>36955</v>
       </c>
       <c r="B431" t="n">
-        <v>-1.35692564821685</v>
+        <v>1.311323521854582</v>
       </c>
     </row>
     <row r="432">
@@ -3884,7 +3884,7 @@
         <v>36956</v>
       </c>
       <c r="B432" t="n">
-        <v>0.1157378019939651</v>
+        <v>-0.1340274998081538</v>
       </c>
     </row>
     <row r="433">
@@ -3892,7 +3892,7 @@
         <v>36957</v>
       </c>
       <c r="B433" t="n">
-        <v>0.3562699697971403</v>
+        <v>-0.6956512852101048</v>
       </c>
     </row>
     <row r="434">
@@ -3900,7 +3900,7 @@
         <v>36958</v>
       </c>
       <c r="B434" t="n">
-        <v>-1.30191234061097</v>
+        <v>-0.5962622358950811</v>
       </c>
     </row>
     <row r="435">
@@ -3908,7 +3908,7 @@
         <v>36959</v>
       </c>
       <c r="B435" t="n">
-        <v>0.2103268719243907</v>
+        <v>-0.05219370550433245</v>
       </c>
     </row>
     <row r="436">
@@ -3916,7 +3916,7 @@
         <v>36960</v>
       </c>
       <c r="B436" t="n">
-        <v>0.01869355273096589</v>
+        <v>0.2639948471975335</v>
       </c>
     </row>
     <row r="437">
@@ -3924,7 +3924,7 @@
         <v>36961</v>
       </c>
       <c r="B437" t="n">
-        <v>-1.432421482534204</v>
+        <v>0.3549080107327871</v>
       </c>
     </row>
     <row r="438">
@@ -3932,7 +3932,7 @@
         <v>36962</v>
       </c>
       <c r="B438" t="n">
-        <v>-0.06181075829709023</v>
+        <v>-0.1847742797502756</v>
       </c>
     </row>
     <row r="439">
@@ -3940,7 +3940,7 @@
         <v>36963</v>
       </c>
       <c r="B439" t="n">
-        <v>-0.7781353500554897</v>
+        <v>-0.1961357501500945</v>
       </c>
     </row>
     <row r="440">
@@ -3948,7 +3948,7 @@
         <v>36964</v>
       </c>
       <c r="B440" t="n">
-        <v>0.90895553143754</v>
+        <v>0.7673231235948527</v>
       </c>
     </row>
     <row r="441">
@@ -3956,7 +3956,7 @@
         <v>36965</v>
       </c>
       <c r="B441" t="n">
-        <v>-0.9699518197316126</v>
+        <v>-0.7736693734306616</v>
       </c>
     </row>
     <row r="442">
@@ -3964,7 +3964,7 @@
         <v>36966</v>
       </c>
       <c r="B442" t="n">
-        <v>0.9964835795159398</v>
+        <v>1.554813202615861</v>
       </c>
     </row>
     <row r="443">
@@ -3972,7 +3972,7 @@
         <v>36967</v>
       </c>
       <c r="B443" t="n">
-        <v>0.5690975998354564</v>
+        <v>-0.5021813867758945</v>
       </c>
     </row>
     <row r="444">
@@ -3980,7 +3980,7 @@
         <v>36968</v>
       </c>
       <c r="B444" t="n">
-        <v>-0.03458660824611796</v>
+        <v>1.55401736264394</v>
       </c>
     </row>
     <row r="445">
@@ -3988,7 +3988,7 @@
         <v>36969</v>
       </c>
       <c r="B445" t="n">
-        <v>-0.8238190746698948</v>
+        <v>-0.5554882573364244</v>
       </c>
     </row>
     <row r="446">
@@ -3996,7 +3996,7 @@
         <v>36970</v>
       </c>
       <c r="B446" t="n">
-        <v>-2.87137597894032</v>
+        <v>0.7035521523246879</v>
       </c>
     </row>
     <row r="447">
@@ -4004,7 +4004,7 @@
         <v>36971</v>
       </c>
       <c r="B447" t="n">
-        <v>-0.06067183448180759</v>
+        <v>-1.676185698666471</v>
       </c>
     </row>
     <row r="448">
@@ -4012,7 +4012,7 @@
         <v>36972</v>
       </c>
       <c r="B448" t="n">
-        <v>1.520372007373634</v>
+        <v>-0.2941503521562165</v>
       </c>
     </row>
     <row r="449">
@@ -4020,7 +4020,7 @@
         <v>36973</v>
       </c>
       <c r="B449" t="n">
-        <v>1.002897831627558</v>
+        <v>-0.01606638111726436</v>
       </c>
     </row>
     <row r="450">
@@ -4028,7 +4028,7 @@
         <v>36974</v>
       </c>
       <c r="B450" t="n">
-        <v>-2.402315476613759</v>
+        <v>-0.9031717397016604</v>
       </c>
     </row>
     <row r="451">
@@ -4036,7 +4036,7 @@
         <v>36975</v>
       </c>
       <c r="B451" t="n">
-        <v>-0.2033684298353982</v>
+        <v>-0.5795740629695442</v>
       </c>
     </row>
     <row r="452">
@@ -4044,7 +4044,7 @@
         <v>36976</v>
       </c>
       <c r="B452" t="n">
-        <v>-1.393815852173147</v>
+        <v>1.406451312186589</v>
       </c>
     </row>
     <row r="453">
@@ -4052,7 +4052,7 @@
         <v>36977</v>
       </c>
       <c r="B453" t="n">
-        <v>1.014467105964468</v>
+        <v>0.02047101402792157</v>
       </c>
     </row>
     <row r="454">
@@ -4060,7 +4060,7 @@
         <v>36978</v>
       </c>
       <c r="B454" t="n">
-        <v>-0.9082805895577738</v>
+        <v>-0.9329602687886942</v>
       </c>
     </row>
     <row r="455">
@@ -4068,7 +4068,7 @@
         <v>36979</v>
       </c>
       <c r="B455" t="n">
-        <v>-0.386783025669268</v>
+        <v>0.8197800961181436</v>
       </c>
     </row>
     <row r="456">
@@ -4076,7 +4076,7 @@
         <v>36980</v>
       </c>
       <c r="B456" t="n">
-        <v>-0.6994128048131535</v>
+        <v>-0.03803877333799617</v>
       </c>
     </row>
     <row r="457">
@@ -4084,7 +4084,7 @@
         <v>36981</v>
       </c>
       <c r="B457" t="n">
-        <v>-1.04473177532458</v>
+        <v>-0.8535332844030298</v>
       </c>
     </row>
     <row r="458">
@@ -4092,7 +4092,7 @@
         <v>36982</v>
       </c>
       <c r="B458" t="n">
-        <v>-1.069662880675955</v>
+        <v>1.060938357637297</v>
       </c>
     </row>
     <row r="459">
@@ -4100,7 +4100,7 @@
         <v>36983</v>
       </c>
       <c r="B459" t="n">
-        <v>1.445090584630065</v>
+        <v>1.554782373103875</v>
       </c>
     </row>
     <row r="460">
@@ -4108,7 +4108,7 @@
         <v>36984</v>
       </c>
       <c r="B460" t="n">
-        <v>-0.8560779368489949</v>
+        <v>0.2847735234492697</v>
       </c>
     </row>
     <row r="461">
@@ -4116,7 +4116,7 @@
         <v>36985</v>
       </c>
       <c r="B461" t="n">
-        <v>1.520006510334022</v>
+        <v>0.4737402794580395</v>
       </c>
     </row>
     <row r="462">
@@ -4124,7 +4124,7 @@
         <v>36986</v>
       </c>
       <c r="B462" t="n">
-        <v>-1.52185293263562</v>
+        <v>0.09847803466665422</v>
       </c>
     </row>
     <row r="463">
@@ -4132,7 +4132,7 @@
         <v>36987</v>
       </c>
       <c r="B463" t="n">
-        <v>-0.2153520259282805</v>
+        <v>-0.04034948981382246</v>
       </c>
     </row>
     <row r="464">
@@ -4140,7 +4140,7 @@
         <v>36988</v>
       </c>
       <c r="B464" t="n">
-        <v>-0.5852316090024704</v>
+        <v>-1.009863079934699</v>
       </c>
     </row>
     <row r="465">
@@ -4148,7 +4148,7 @@
         <v>36989</v>
       </c>
       <c r="B465" t="n">
-        <v>-1.518741823820326</v>
+        <v>0.8264376874474154</v>
       </c>
     </row>
     <row r="466">
@@ -4156,7 +4156,7 @@
         <v>36990</v>
       </c>
       <c r="B466" t="n">
-        <v>1.76582438205722</v>
+        <v>-0.4577826796564508</v>
       </c>
     </row>
     <row r="467">
@@ -4164,7 +4164,7 @@
         <v>36991</v>
       </c>
       <c r="B467" t="n">
-        <v>-1.235287293604499</v>
+        <v>0.6257204614717035</v>
       </c>
     </row>
     <row r="468">
@@ -4172,7 +4172,7 @@
         <v>36992</v>
       </c>
       <c r="B468" t="n">
-        <v>0.1894022667054203</v>
+        <v>-1.038566049727104</v>
       </c>
     </row>
     <row r="469">
@@ -4180,7 +4180,7 @@
         <v>36993</v>
       </c>
       <c r="B469" t="n">
-        <v>-1.698889154981541</v>
+        <v>-0.07323953685766948</v>
       </c>
     </row>
     <row r="470">
@@ -4188,7 +4188,7 @@
         <v>36994</v>
       </c>
       <c r="B470" t="n">
-        <v>0.4722339381426153</v>
+        <v>1.76433392363166</v>
       </c>
     </row>
     <row r="471">
@@ -4196,7 +4196,7 @@
         <v>36995</v>
       </c>
       <c r="B471" t="n">
-        <v>-0.5788792551026227</v>
+        <v>-0.0314703702523941</v>
       </c>
     </row>
     <row r="472">
@@ -4204,7 +4204,7 @@
         <v>36996</v>
       </c>
       <c r="B472" t="n">
-        <v>-0.8950130366439318</v>
+        <v>1.487883571278</v>
       </c>
     </row>
     <row r="473">
@@ -4212,7 +4212,7 @@
         <v>36997</v>
       </c>
       <c r="B473" t="n">
-        <v>0.6276985915176538</v>
+        <v>0.8547412127203705</v>
       </c>
     </row>
     <row r="474">
@@ -4220,7 +4220,7 @@
         <v>36998</v>
       </c>
       <c r="B474" t="n">
-        <v>-1.635983389642266</v>
+        <v>-0.334735008484767</v>
       </c>
     </row>
     <row r="475">
@@ -4228,7 +4228,7 @@
         <v>36999</v>
       </c>
       <c r="B475" t="n">
-        <v>1.282301048718514</v>
+        <v>0.2102963372180279</v>
       </c>
     </row>
     <row r="476">
@@ -4236,7 +4236,7 @@
         <v>37000</v>
       </c>
       <c r="B476" t="n">
-        <v>-0.4732097027714903</v>
+        <v>0.7181273101434685</v>
       </c>
     </row>
     <row r="477">
@@ -4244,7 +4244,7 @@
         <v>37001</v>
       </c>
       <c r="B477" t="n">
-        <v>-0.5810264905053485</v>
+        <v>1.489723150207549</v>
       </c>
     </row>
     <row r="478">
@@ -4252,7 +4252,7 @@
         <v>37002</v>
       </c>
       <c r="B478" t="n">
-        <v>0.003122013885569329</v>
+        <v>-0.1056584924088831</v>
       </c>
     </row>
     <row r="479">
@@ -4260,7 +4260,7 @@
         <v>37003</v>
       </c>
       <c r="B479" t="n">
-        <v>0.5103058307687267</v>
+        <v>-0.4717814775011676</v>
       </c>
     </row>
     <row r="480">
@@ -4268,7 +4268,7 @@
         <v>37004</v>
       </c>
       <c r="B480" t="n">
-        <v>-0.323870563183759</v>
+        <v>-1.231800330888822</v>
       </c>
     </row>
     <row r="481">
@@ -4276,7 +4276,7 @@
         <v>37005</v>
       </c>
       <c r="B481" t="n">
-        <v>0.1248413181282451</v>
+        <v>-1.139013281881789</v>
       </c>
     </row>
     <row r="482">
@@ -4284,7 +4284,7 @@
         <v>37006</v>
       </c>
       <c r="B482" t="n">
-        <v>-0.520535756179734</v>
+        <v>0.4623703796129012</v>
       </c>
     </row>
     <row r="483">
@@ -4292,7 +4292,7 @@
         <v>37007</v>
       </c>
       <c r="B483" t="n">
-        <v>0.6843740034451956</v>
+        <v>0.1349640250651898</v>
       </c>
     </row>
     <row r="484">
@@ -4300,7 +4300,7 @@
         <v>37008</v>
       </c>
       <c r="B484" t="n">
-        <v>-0.1691655585973727</v>
+        <v>-0.7029586252810508</v>
       </c>
     </row>
     <row r="485">
@@ -4308,7 +4308,7 @@
         <v>37009</v>
       </c>
       <c r="B485" t="n">
-        <v>-0.7456509196500324</v>
+        <v>-0.7687778021919887</v>
       </c>
     </row>
     <row r="486">
@@ -4316,7 +4316,7 @@
         <v>37010</v>
       </c>
       <c r="B486" t="n">
-        <v>-1.308956490273267</v>
+        <v>0.7817895957925263</v>
       </c>
     </row>
     <row r="487">
@@ -4324,7 +4324,7 @@
         <v>37011</v>
       </c>
       <c r="B487" t="n">
-        <v>-0.4627957265452319</v>
+        <v>-0.1644791050190365</v>
       </c>
     </row>
     <row r="488">
@@ -4332,7 +4332,7 @@
         <v>37012</v>
       </c>
       <c r="B488" t="n">
-        <v>0.7087621794037003</v>
+        <v>0.0408350970923551</v>
       </c>
     </row>
     <row r="489">
@@ -4340,7 +4340,7 @@
         <v>37013</v>
       </c>
       <c r="B489" t="n">
-        <v>0.6987649143546013</v>
+        <v>-0.3654462740276296</v>
       </c>
     </row>
     <row r="490">
@@ -4348,7 +4348,7 @@
         <v>37014</v>
       </c>
       <c r="B490" t="n">
-        <v>1.121038553660286</v>
+        <v>-0.07224215232662137</v>
       </c>
     </row>
     <row r="491">
@@ -4356,7 +4356,7 @@
         <v>37015</v>
       </c>
       <c r="B491" t="n">
-        <v>0.933773132383975</v>
+        <v>0.3634605977894177</v>
       </c>
     </row>
     <row r="492">
@@ -4364,7 +4364,7 @@
         <v>37016</v>
       </c>
       <c r="B492" t="n">
-        <v>0.7272784598634905</v>
+        <v>-0.5383346207918521</v>
       </c>
     </row>
     <row r="493">
@@ -4372,7 +4372,7 @@
         <v>37017</v>
       </c>
       <c r="B493" t="n">
-        <v>-1.160110811495341</v>
+        <v>-0.4101234611386561</v>
       </c>
     </row>
     <row r="494">
@@ -4380,7 +4380,7 @@
         <v>37018</v>
       </c>
       <c r="B494" t="n">
-        <v>-0.6810644367022698</v>
+        <v>-0.9435598738732948</v>
       </c>
     </row>
     <row r="495">
@@ -4388,7 +4388,7 @@
         <v>37019</v>
       </c>
       <c r="B495" t="n">
-        <v>0.9627778332784429</v>
+        <v>0.656614502363818</v>
       </c>
     </row>
     <row r="496">
@@ -4396,7 +4396,7 @@
         <v>37020</v>
       </c>
       <c r="B496" t="n">
-        <v>0.1304795253132748</v>
+        <v>1.168131695560988</v>
       </c>
     </row>
     <row r="497">
@@ -4404,7 +4404,7 @@
         <v>37021</v>
       </c>
       <c r="B497" t="n">
-        <v>0.4240502683619569</v>
+        <v>0.8771383623558276</v>
       </c>
     </row>
     <row r="498">
@@ -4412,7 +4412,7 @@
         <v>37022</v>
       </c>
       <c r="B498" t="n">
-        <v>0.7488564567523702</v>
+        <v>-0.3782681085139157</v>
       </c>
     </row>
     <row r="499">
@@ -4420,7 +4420,7 @@
         <v>37023</v>
       </c>
       <c r="B499" t="n">
-        <v>-1.09036539257621</v>
+        <v>0.8237996559052356</v>
       </c>
     </row>
     <row r="500">
@@ -4428,7 +4428,7 @@
         <v>37024</v>
       </c>
       <c r="B500" t="n">
-        <v>-0.1108906926493954</v>
+        <v>-1.043117018459543</v>
       </c>
     </row>
     <row r="501">
@@ -4436,7 +4436,7 @@
         <v>37025</v>
       </c>
       <c r="B501" t="n">
-        <v>0.4112898181135896</v>
+        <v>-1.046055648703575</v>
       </c>
     </row>
     <row r="502">
@@ -4444,7 +4444,7 @@
         <v>37026</v>
       </c>
       <c r="B502" t="n">
-        <v>-0.4136059886592474</v>
+        <v>0.2149358031312505</v>
       </c>
     </row>
     <row r="503">
@@ -4452,7 +4452,7 @@
         <v>37027</v>
       </c>
       <c r="B503" t="n">
-        <v>0.4252989952614204</v>
+        <v>0.4366645893162114</v>
       </c>
     </row>
     <row r="504">
@@ -4460,7 +4460,7 @@
         <v>37028</v>
       </c>
       <c r="B504" t="n">
-        <v>-1.090152970217044</v>
+        <v>-0.6389264511085395</v>
       </c>
     </row>
     <row r="505">
@@ -4468,7 +4468,7 @@
         <v>37029</v>
       </c>
       <c r="B505" t="n">
-        <v>2.687169649432779</v>
+        <v>1.589040825237162</v>
       </c>
     </row>
     <row r="506">
@@ -4476,7 +4476,7 @@
         <v>37030</v>
       </c>
       <c r="B506" t="n">
-        <v>0.9421440829546728</v>
+        <v>0.2955161163457186</v>
       </c>
     </row>
     <row r="507">
@@ -4484,7 +4484,7 @@
         <v>37031</v>
       </c>
       <c r="B507" t="n">
-        <v>0.1074045091520362</v>
+        <v>0.4505819133591323</v>
       </c>
     </row>
     <row r="508">
@@ -4492,7 +4492,7 @@
         <v>37032</v>
       </c>
       <c r="B508" t="n">
-        <v>0.287730208485495</v>
+        <v>-1.405652628708651</v>
       </c>
     </row>
     <row r="509">
@@ -4500,7 +4500,7 @@
         <v>37033</v>
       </c>
       <c r="B509" t="n">
-        <v>-0.3157383068333253</v>
+        <v>-0.09881401725966803</v>
       </c>
     </row>
     <row r="510">
@@ -4508,7 +4508,7 @@
         <v>37034</v>
       </c>
       <c r="B510" t="n">
-        <v>-0.3584326361973638</v>
+        <v>1.168094743379108</v>
       </c>
     </row>
     <row r="511">
@@ -4516,7 +4516,7 @@
         <v>37035</v>
       </c>
       <c r="B511" t="n">
-        <v>-2.310102909731365</v>
+        <v>0.5066035100376578</v>
       </c>
     </row>
     <row r="512">
@@ -4524,7 +4524,7 @@
         <v>37036</v>
       </c>
       <c r="B512" t="n">
-        <v>0.6130703998197128</v>
+        <v>-1.475436615783752</v>
       </c>
     </row>
     <row r="513">
@@ -4532,7 +4532,7 @@
         <v>37037</v>
       </c>
       <c r="B513" t="n">
-        <v>0.7362862868256377</v>
+        <v>-1.822113960263635</v>
       </c>
     </row>
     <row r="514">
@@ -4540,7 +4540,7 @@
         <v>37038</v>
       </c>
       <c r="B514" t="n">
-        <v>0.9118707472739819</v>
+        <v>-0.0009287762368647317</v>
       </c>
     </row>
     <row r="515">
@@ -4548,7 +4548,7 @@
         <v>37039</v>
       </c>
       <c r="B515" t="n">
-        <v>2.662736905429972</v>
+        <v>0.7937610634175846</v>
       </c>
     </row>
     <row r="516">
@@ -4556,7 +4556,7 @@
         <v>37040</v>
       </c>
       <c r="B516" t="n">
-        <v>0.2620903414896525</v>
+        <v>0.1217580642454575</v>
       </c>
     </row>
     <row r="517">
@@ -4564,7 +4564,7 @@
         <v>37041</v>
       </c>
       <c r="B517" t="n">
-        <v>0.7903966351270388</v>
+        <v>-0.4843649338061571</v>
       </c>
     </row>
     <row r="518">
@@ -4572,7 +4572,7 @@
         <v>37042</v>
       </c>
       <c r="B518" t="n">
-        <v>-0.7205711832729572</v>
+        <v>0.123582290631006</v>
       </c>
     </row>
     <row r="519">
@@ -4580,7 +4580,7 @@
         <v>37043</v>
       </c>
       <c r="B519" t="n">
-        <v>-1.753634630716718</v>
+        <v>-0.3605312801397082</v>
       </c>
     </row>
     <row r="520">
@@ -4588,7 +4588,7 @@
         <v>37044</v>
       </c>
       <c r="B520" t="n">
-        <v>-0.8372527237704139</v>
+        <v>0.03343824609420769</v>
       </c>
     </row>
     <row r="521">
@@ -4596,7 +4596,7 @@
         <v>37045</v>
       </c>
       <c r="B521" t="n">
-        <v>-0.08046989199439211</v>
+        <v>0.5389203022557629</v>
       </c>
     </row>
     <row r="522">
@@ -4604,7 +4604,7 @@
         <v>37046</v>
       </c>
       <c r="B522" t="n">
-        <v>0.04792766673816286</v>
+        <v>1.631841377437551</v>
       </c>
     </row>
     <row r="523">
@@ -4612,7 +4612,7 @@
         <v>37047</v>
       </c>
       <c r="B523" t="n">
-        <v>-0.03991835609254818</v>
+        <v>-0.7583427918656772</v>
       </c>
     </row>
     <row r="524">
@@ -4620,7 +4620,7 @@
         <v>37048</v>
       </c>
       <c r="B524" t="n">
-        <v>-1.100133457549168</v>
+        <v>-1.208045255519165</v>
       </c>
     </row>
     <row r="525">
@@ -4628,7 +4628,7 @@
         <v>37049</v>
       </c>
       <c r="B525" t="n">
-        <v>-0.5355443873258637</v>
+        <v>-0.01809612878302939</v>
       </c>
     </row>
     <row r="526">
@@ -4636,7 +4636,7 @@
         <v>37050</v>
       </c>
       <c r="B526" t="n">
-        <v>-0.7492428410806312</v>
+        <v>0.8930887444781519</v>
       </c>
     </row>
     <row r="527">
@@ -4644,7 +4644,7 @@
         <v>37051</v>
       </c>
       <c r="B527" t="n">
-        <v>-0.5121549468970711</v>
+        <v>-0.3668437672167768</v>
       </c>
     </row>
     <row r="528">
@@ -4652,7 +4652,7 @@
         <v>37052</v>
       </c>
       <c r="B528" t="n">
-        <v>-0.903076519404342</v>
+        <v>-0.01152401094334588</v>
       </c>
     </row>
     <row r="529">
@@ -4660,7 +4660,7 @@
         <v>37053</v>
       </c>
       <c r="B529" t="n">
-        <v>0.1974745248148927</v>
+        <v>-0.06224605176441764</v>
       </c>
     </row>
     <row r="530">
@@ -4668,7 +4668,7 @@
         <v>37054</v>
       </c>
       <c r="B530" t="n">
-        <v>-1.639710229778884</v>
+        <v>0.6292865755574977</v>
       </c>
     </row>
     <row r="531">
@@ -4676,7 +4676,7 @@
         <v>37055</v>
       </c>
       <c r="B531" t="n">
-        <v>-0.5199936271309611</v>
+        <v>1.17396718863768</v>
       </c>
     </row>
     <row r="532">
@@ -4684,7 +4684,7 @@
         <v>37056</v>
       </c>
       <c r="B532" t="n">
-        <v>-0.2803015864003037</v>
+        <v>-1.387820524628476</v>
       </c>
     </row>
     <row r="533">
@@ -4692,7 +4692,7 @@
         <v>37057</v>
       </c>
       <c r="B533" t="n">
-        <v>-0.05227364531312439</v>
+        <v>0.4066330025381203</v>
       </c>
     </row>
     <row r="534">
@@ -4700,7 +4700,7 @@
         <v>37058</v>
       </c>
       <c r="B534" t="n">
-        <v>-1.269683528581763</v>
+        <v>-2.813588905130191</v>
       </c>
     </row>
     <row r="535">
@@ -4708,7 +4708,7 @@
         <v>37059</v>
       </c>
       <c r="B535" t="n">
-        <v>0.4907353175333592</v>
+        <v>-1.215954621524351</v>
       </c>
     </row>
     <row r="536">
@@ -4716,7 +4716,7 @@
         <v>37060</v>
       </c>
       <c r="B536" t="n">
-        <v>-0.3692307556411191</v>
+        <v>-0.05697665708649417</v>
       </c>
     </row>
     <row r="537">
@@ -4724,7 +4724,7 @@
         <v>37061</v>
       </c>
       <c r="B537" t="n">
-        <v>0.30510228509472</v>
+        <v>0.3232240774986929</v>
       </c>
     </row>
     <row r="538">
@@ -4732,7 +4732,7 @@
         <v>37062</v>
       </c>
       <c r="B538" t="n">
-        <v>0.4425014066562713</v>
+        <v>0.9720048494197815</v>
       </c>
     </row>
     <row r="539">
@@ -4740,7 +4740,7 @@
         <v>37063</v>
       </c>
       <c r="B539" t="n">
-        <v>-0.1372084186507753</v>
+        <v>1.008226253701552</v>
       </c>
     </row>
     <row r="540">
@@ -4748,7 +4748,7 @@
         <v>37064</v>
       </c>
       <c r="B540" t="n">
-        <v>-1.209226368203257</v>
+        <v>0.9736971640632108</v>
       </c>
     </row>
     <row r="541">
@@ -4756,7 +4756,7 @@
         <v>37065</v>
       </c>
       <c r="B541" t="n">
-        <v>0.4833813614607159</v>
+        <v>1.34539647950256</v>
       </c>
     </row>
     <row r="542">
@@ -4764,7 +4764,7 @@
         <v>37066</v>
       </c>
       <c r="B542" t="n">
-        <v>0.3201844673018522</v>
+        <v>-1.184413859027258</v>
       </c>
     </row>
     <row r="543">
@@ -4772,7 +4772,7 @@
         <v>37067</v>
       </c>
       <c r="B543" t="n">
-        <v>-0.9321754614161747</v>
+        <v>-0.146409961767447</v>
       </c>
     </row>
     <row r="544">
@@ -4780,7 +4780,7 @@
         <v>37068</v>
       </c>
       <c r="B544" t="n">
-        <v>-0.6775703418740697</v>
+        <v>1.7982417455413</v>
       </c>
     </row>
     <row r="545">
@@ -4788,7 +4788,7 @@
         <v>37069</v>
       </c>
       <c r="B545" t="n">
-        <v>0.3031461739403222</v>
+        <v>-0.4974468655245301</v>
       </c>
     </row>
     <row r="546">
@@ -4796,7 +4796,7 @@
         <v>37070</v>
       </c>
       <c r="B546" t="n">
-        <v>0.2860403801645021</v>
+        <v>-0.1872817061456998</v>
       </c>
     </row>
     <row r="547">
@@ -4804,7 +4804,7 @@
         <v>37071</v>
       </c>
       <c r="B547" t="n">
-        <v>1.026231188356381</v>
+        <v>-1.027636884007979</v>
       </c>
     </row>
     <row r="548">
@@ -4812,7 +4812,7 @@
         <v>37072</v>
       </c>
       <c r="B548" t="n">
-        <v>-0.6610552022235383</v>
+        <v>0.2067100227696178</v>
       </c>
     </row>
     <row r="549">
@@ -4820,7 +4820,7 @@
         <v>37073</v>
       </c>
       <c r="B549" t="n">
-        <v>-1.474690966608742</v>
+        <v>1.208242030391744</v>
       </c>
     </row>
     <row r="550">
@@ -4828,7 +4828,7 @@
         <v>37074</v>
       </c>
       <c r="B550" t="n">
-        <v>-0.483943683320309</v>
+        <v>0.9904580367765076</v>
       </c>
     </row>
     <row r="551">
@@ -4836,7 +4836,7 @@
         <v>37075</v>
       </c>
       <c r="B551" t="n">
-        <v>0.188795251342175</v>
+        <v>-0.5611555989172758</v>
       </c>
     </row>
     <row r="552">
@@ -4844,7 +4844,7 @@
         <v>37076</v>
       </c>
       <c r="B552" t="n">
-        <v>-0.04437785335455183</v>
+        <v>-1.022972295547851</v>
       </c>
     </row>
     <row r="553">
@@ -4852,7 +4852,7 @@
         <v>37077</v>
       </c>
       <c r="B553" t="n">
-        <v>0.1699307148595494</v>
+        <v>0.7759539032936931</v>
       </c>
     </row>
     <row r="554">
@@ -4860,7 +4860,7 @@
         <v>37078</v>
       </c>
       <c r="B554" t="n">
-        <v>-1.891905975997099</v>
+        <v>-1.472090613201358</v>
       </c>
     </row>
     <row r="555">
@@ -4868,7 +4868,7 @@
         <v>37079</v>
       </c>
       <c r="B555" t="n">
-        <v>-1.47105057896692</v>
+        <v>-0.5077496229259054</v>
       </c>
     </row>
     <row r="556">
@@ -4876,7 +4876,7 @@
         <v>37080</v>
       </c>
       <c r="B556" t="n">
-        <v>-0.6399377341036457</v>
+        <v>0.01782182104531132</v>
       </c>
     </row>
     <row r="557">
@@ -4884,7 +4884,7 @@
         <v>37081</v>
       </c>
       <c r="B557" t="n">
-        <v>-0.090119751350554</v>
+        <v>0.3514270154988663</v>
       </c>
     </row>
     <row r="558">
@@ -4892,7 +4892,7 @@
         <v>37082</v>
       </c>
       <c r="B558" t="n">
-        <v>-0.2989354532877731</v>
+        <v>-0.6809876345553685</v>
       </c>
     </row>
     <row r="559">
@@ -4900,7 +4900,7 @@
         <v>37083</v>
       </c>
       <c r="B559" t="n">
-        <v>0.2004092857131214</v>
+        <v>-0.9750372182893161</v>
       </c>
     </row>
     <row r="560">
@@ -4908,7 +4908,7 @@
         <v>37084</v>
       </c>
       <c r="B560" t="n">
-        <v>0.923676468263298</v>
+        <v>0.02863661170965111</v>
       </c>
     </row>
     <row r="561">
@@ -4916,7 +4916,7 @@
         <v>37085</v>
       </c>
       <c r="B561" t="n">
-        <v>-1.414809974292707</v>
+        <v>0.6958271084943506</v>
       </c>
     </row>
     <row r="562">
@@ -4924,7 +4924,7 @@
         <v>37086</v>
       </c>
       <c r="B562" t="n">
-        <v>-0.7256075488948633</v>
+        <v>-0.09573357040886073</v>
       </c>
     </row>
     <row r="563">
@@ -4932,7 +4932,7 @@
         <v>37087</v>
       </c>
       <c r="B563" t="n">
-        <v>0.8859994071863793</v>
+        <v>-0.8077533320347567</v>
       </c>
     </row>
     <row r="564">
@@ -4940,7 +4940,7 @@
         <v>37088</v>
       </c>
       <c r="B564" t="n">
-        <v>-0.2757253805504278</v>
+        <v>2.009699703966316</v>
       </c>
     </row>
     <row r="565">
@@ -4948,7 +4948,7 @@
         <v>37089</v>
       </c>
       <c r="B565" t="n">
-        <v>2.024213314093681</v>
+        <v>0.9872629611676106</v>
       </c>
     </row>
     <row r="566">
@@ -4956,7 +4956,7 @@
         <v>37090</v>
       </c>
       <c r="B566" t="n">
-        <v>0.9499279981958407</v>
+        <v>0.5484718151275806</v>
       </c>
     </row>
     <row r="567">
@@ -4964,7 +4964,7 @@
         <v>37091</v>
       </c>
       <c r="B567" t="n">
-        <v>-1.223047257674062</v>
+        <v>-1.584143168815901</v>
       </c>
     </row>
     <row r="568">
@@ -4972,7 +4972,7 @@
         <v>37092</v>
       </c>
       <c r="B568" t="n">
-        <v>-0.3515421250598617</v>
+        <v>-0.2527907591632008</v>
       </c>
     </row>
     <row r="569">
@@ -4980,7 +4980,7 @@
         <v>37093</v>
       </c>
       <c r="B569" t="n">
-        <v>0.3720428532002559</v>
+        <v>-0.9108468579661787</v>
       </c>
     </row>
     <row r="570">
@@ -4988,7 +4988,7 @@
         <v>37094</v>
       </c>
       <c r="B570" t="n">
-        <v>-0.2783061132011657</v>
+        <v>0.05648750136496271</v>
       </c>
     </row>
     <row r="571">
@@ -4996,7 +4996,7 @@
         <v>37095</v>
       </c>
       <c r="B571" t="n">
-        <v>2.749980524024489</v>
+        <v>-0.5054666591833367</v>
       </c>
     </row>
     <row r="572">
@@ -5004,7 +5004,7 @@
         <v>37096</v>
       </c>
       <c r="B572" t="n">
-        <v>0.6240147377323592</v>
+        <v>1.311118902727895</v>
       </c>
     </row>
     <row r="573">
@@ -5012,7 +5012,7 @@
         <v>37097</v>
       </c>
       <c r="B573" t="n">
-        <v>2.266722961852773</v>
+        <v>-0.3589485400457313</v>
       </c>
     </row>
     <row r="574">
@@ -5020,7 +5020,7 @@
         <v>37098</v>
       </c>
       <c r="B574" t="n">
-        <v>0.3138707935680366</v>
+        <v>0.4690702452520266</v>
       </c>
     </row>
     <row r="575">
@@ -5028,7 +5028,7 @@
         <v>37099</v>
       </c>
       <c r="B575" t="n">
-        <v>0.2324406834047504</v>
+        <v>-0.6047211094782613</v>
       </c>
     </row>
     <row r="576">
@@ -5036,7 +5036,7 @@
         <v>37100</v>
       </c>
       <c r="B576" t="n">
-        <v>-0.8835964166469495</v>
+        <v>-0.9332056235849316</v>
       </c>
     </row>
     <row r="577">
@@ -5044,7 +5044,7 @@
         <v>37101</v>
       </c>
       <c r="B577" t="n">
-        <v>1.837691756316109</v>
+        <v>-1.447823972355976</v>
       </c>
     </row>
     <row r="578">
@@ -5052,7 +5052,7 @@
         <v>37102</v>
       </c>
       <c r="B578" t="n">
-        <v>-0.6099707923089359</v>
+        <v>1.730663904650253</v>
       </c>
     </row>
     <row r="579">
@@ -5060,7 +5060,7 @@
         <v>37103</v>
       </c>
       <c r="B579" t="n">
-        <v>1.158973702377354</v>
+        <v>-0.007070038640602332</v>
       </c>
     </row>
     <row r="580">
@@ -5068,7 +5068,7 @@
         <v>37104</v>
       </c>
       <c r="B580" t="n">
-        <v>-0.2094143959126801</v>
+        <v>0.4778205810227543</v>
       </c>
     </row>
     <row r="581">
@@ -5076,7 +5076,7 @@
         <v>37105</v>
       </c>
       <c r="B581" t="n">
-        <v>-0.7748043214034327</v>
+        <v>-0.3717714881171289</v>
       </c>
     </row>
     <row r="582">
@@ -5084,7 +5084,7 @@
         <v>37106</v>
       </c>
       <c r="B582" t="n">
-        <v>0.6460466993261378</v>
+        <v>0.5210177828186145</v>
       </c>
     </row>
     <row r="583">
@@ -5092,7 +5092,7 @@
         <v>37107</v>
       </c>
       <c r="B583" t="n">
-        <v>-0.2979234723291369</v>
+        <v>0.3826471082819812</v>
       </c>
     </row>
     <row r="584">
@@ -5100,7 +5100,7 @@
         <v>37108</v>
       </c>
       <c r="B584" t="n">
-        <v>-1.31106191923171</v>
+        <v>0.9729163686727058</v>
       </c>
     </row>
     <row r="585">
@@ -5108,7 +5108,7 @@
         <v>37109</v>
       </c>
       <c r="B585" t="n">
-        <v>-0.3910398846424582</v>
+        <v>-0.2785374418220997</v>
       </c>
     </row>
     <row r="586">
@@ -5116,7 +5116,7 @@
         <v>37110</v>
       </c>
       <c r="B586" t="n">
-        <v>-0.210788403034988</v>
+        <v>1.815108033086112</v>
       </c>
     </row>
     <row r="587">
@@ -5124,7 +5124,7 @@
         <v>37111</v>
       </c>
       <c r="B587" t="n">
-        <v>-0.3431870286684987</v>
+        <v>0.5391834238591325</v>
       </c>
     </row>
     <row r="588">
@@ -5132,7 +5132,7 @@
         <v>37112</v>
       </c>
       <c r="B588" t="n">
-        <v>-0.2437446711152006</v>
+        <v>2.777737877559921</v>
       </c>
     </row>
     <row r="589">
@@ -5140,7 +5140,7 @@
         <v>37113</v>
       </c>
       <c r="B589" t="n">
-        <v>-1.079892882883396</v>
+        <v>-0.5161737727412227</v>
       </c>
     </row>
     <row r="590">
@@ -5148,7 +5148,7 @@
         <v>37114</v>
       </c>
       <c r="B590" t="n">
-        <v>-0.7958955131184575</v>
+        <v>0.2414250422766257</v>
       </c>
     </row>
     <row r="591">
@@ -5156,7 +5156,7 @@
         <v>37115</v>
       </c>
       <c r="B591" t="n">
-        <v>-0.6703767672069715</v>
+        <v>1.130285715916403</v>
       </c>
     </row>
     <row r="592">
@@ -5164,7 +5164,7 @@
         <v>37116</v>
       </c>
       <c r="B592" t="n">
-        <v>-0.8552806790465366</v>
+        <v>-1.244156501129094</v>
       </c>
     </row>
     <row r="593">
@@ -5172,7 +5172,7 @@
         <v>37117</v>
       </c>
       <c r="B593" t="n">
-        <v>0.1335787518135039</v>
+        <v>0.7360857394102478</v>
       </c>
     </row>
     <row r="594">
@@ -5180,7 +5180,7 @@
         <v>37118</v>
       </c>
       <c r="B594" t="n">
-        <v>-0.07044399988390138</v>
+        <v>0.364584014058154</v>
       </c>
     </row>
     <row r="595">
@@ -5188,7 +5188,7 @@
         <v>37119</v>
       </c>
       <c r="B595" t="n">
-        <v>0.3263190654333662</v>
+        <v>0.6425752545161489</v>
       </c>
     </row>
     <row r="596">
@@ -5196,7 +5196,7 @@
         <v>37120</v>
       </c>
       <c r="B596" t="n">
-        <v>1.040862844145373</v>
+        <v>0.8593454372961885</v>
       </c>
     </row>
     <row r="597">
@@ -5204,7 +5204,7 @@
         <v>37121</v>
       </c>
       <c r="B597" t="n">
-        <v>0.4359404865321904</v>
+        <v>-0.9099038941166082</v>
       </c>
     </row>
     <row r="598">
@@ -5212,7 +5212,7 @@
         <v>37122</v>
       </c>
       <c r="B598" t="n">
-        <v>1.125998122225894</v>
+        <v>2.253156341147339</v>
       </c>
     </row>
     <row r="599">
@@ -5220,7 +5220,7 @@
         <v>37123</v>
       </c>
       <c r="B599" t="n">
-        <v>-0.1133419061476668</v>
+        <v>-0.02272112698027162</v>
       </c>
     </row>
     <row r="600">
@@ -5228,7 +5228,7 @@
         <v>37124</v>
       </c>
       <c r="B600" t="n">
-        <v>-0.4449488815225269</v>
+        <v>0.2928153673538114</v>
       </c>
     </row>
     <row r="601">
@@ -5236,7 +5236,7 @@
         <v>37125</v>
       </c>
       <c r="B601" t="n">
-        <v>0.6574412893728001</v>
+        <v>-1.324112246472706</v>
       </c>
     </row>
     <row r="602">
@@ -5244,7 +5244,7 @@
         <v>37126</v>
       </c>
       <c r="B602" t="n">
-        <v>-0.2188253952448239</v>
+        <v>1.858262853984788</v>
       </c>
     </row>
     <row r="603">
@@ -5252,7 +5252,7 @@
         <v>37127</v>
       </c>
       <c r="B603" t="n">
-        <v>0.07874241459653308</v>
+        <v>-0.2260833741188369</v>
       </c>
     </row>
     <row r="604">
@@ -5260,7 +5260,7 @@
         <v>37128</v>
       </c>
       <c r="B604" t="n">
-        <v>-1.445711241573236</v>
+        <v>-0.544677850604308</v>
       </c>
     </row>
     <row r="605">
@@ -5268,7 +5268,7 @@
         <v>37129</v>
       </c>
       <c r="B605" t="n">
-        <v>-0.4644338437614347</v>
+        <v>0.58329366918722</v>
       </c>
     </row>
     <row r="606">
@@ -5276,7 +5276,7 @@
         <v>37130</v>
       </c>
       <c r="B606" t="n">
-        <v>-0.1608097138125725</v>
+        <v>0.04629821164775999</v>
       </c>
     </row>
     <row r="607">
@@ -5284,7 +5284,7 @@
         <v>37131</v>
       </c>
       <c r="B607" t="n">
-        <v>1.197124466996915</v>
+        <v>-2.596689659581162</v>
       </c>
     </row>
     <row r="608">
@@ -5292,7 +5292,7 @@
         <v>37132</v>
       </c>
       <c r="B608" t="n">
-        <v>-1.123017877456285</v>
+        <v>-0.4108849278666595</v>
       </c>
     </row>
     <row r="609">
@@ -5300,7 +5300,7 @@
         <v>37133</v>
       </c>
       <c r="B609" t="n">
-        <v>0.3488598024246859</v>
+        <v>-1.347456840412611</v>
       </c>
     </row>
     <row r="610">
@@ -5308,7 +5308,7 @@
         <v>37134</v>
       </c>
       <c r="B610" t="n">
-        <v>1.379880018671625</v>
+        <v>1.121594659633763</v>
       </c>
     </row>
     <row r="611">
@@ -5316,7 +5316,7 @@
         <v>37135</v>
       </c>
       <c r="B611" t="n">
-        <v>-1.523017084294188</v>
+        <v>0.7739920585721466</v>
       </c>
     </row>
     <row r="612">
@@ -5324,7 +5324,7 @@
         <v>37136</v>
       </c>
       <c r="B612" t="n">
-        <v>-1.652621832511453</v>
+        <v>-1.032001560831353</v>
       </c>
     </row>
     <row r="613">
@@ -5332,7 +5332,7 @@
         <v>37137</v>
       </c>
       <c r="B613" t="n">
-        <v>-1.776076973837482</v>
+        <v>0.8879015811927028</v>
       </c>
     </row>
     <row r="614">
@@ -5340,7 +5340,7 @@
         <v>37138</v>
       </c>
       <c r="B614" t="n">
-        <v>-0.4339182833591229</v>
+        <v>-1.680265214283338</v>
       </c>
     </row>
     <row r="615">
@@ -5348,7 +5348,7 @@
         <v>37139</v>
       </c>
       <c r="B615" t="n">
-        <v>0.4271900836780911</v>
+        <v>0.1460419828731427</v>
       </c>
     </row>
     <row r="616">
@@ -5356,7 +5356,7 @@
         <v>37140</v>
       </c>
       <c r="B616" t="n">
-        <v>1.459932523200916</v>
+        <v>2.073069284341918</v>
       </c>
     </row>
     <row r="617">
@@ -5364,7 +5364,7 @@
         <v>37141</v>
       </c>
       <c r="B617" t="n">
-        <v>-0.3330729820051619</v>
+        <v>-0.3735396232080601</v>
       </c>
     </row>
     <row r="618">
@@ -5372,7 +5372,7 @@
         <v>37142</v>
       </c>
       <c r="B618" t="n">
-        <v>0.0859929096348747</v>
+        <v>0.08663588785350106</v>
       </c>
     </row>
     <row r="619">
@@ -5380,7 +5380,7 @@
         <v>37143</v>
       </c>
       <c r="B619" t="n">
-        <v>0.4440284506435848</v>
+        <v>-0.4839477042231886</v>
       </c>
     </row>
     <row r="620">
@@ -5388,7 +5388,7 @@
         <v>37144</v>
       </c>
       <c r="B620" t="n">
-        <v>-0.5206513468422228</v>
+        <v>-0.06625585199668749</v>
       </c>
     </row>
     <row r="621">
@@ -5396,7 +5396,7 @@
         <v>37145</v>
       </c>
       <c r="B621" t="n">
-        <v>-2.064134519635283</v>
+        <v>-0.3520300934482037</v>
       </c>
     </row>
     <row r="622">
@@ -5404,7 +5404,7 @@
         <v>37146</v>
       </c>
       <c r="B622" t="n">
-        <v>-0.3185503469774703</v>
+        <v>1.199173588113805</v>
       </c>
     </row>
     <row r="623">
@@ -5412,7 +5412,7 @@
         <v>37147</v>
       </c>
       <c r="B623" t="n">
-        <v>0.6871459442323291</v>
+        <v>1.953567742698451</v>
       </c>
     </row>
     <row r="624">
@@ -5420,7 +5420,7 @@
         <v>37148</v>
       </c>
       <c r="B624" t="n">
-        <v>-1.056030989733376</v>
+        <v>-0.3251174938180771</v>
       </c>
     </row>
     <row r="625">
@@ -5428,7 +5428,7 @@
         <v>37149</v>
       </c>
       <c r="B625" t="n">
-        <v>-0.6024303117708973</v>
+        <v>-0.9318028189357503</v>
       </c>
     </row>
     <row r="626">
@@ -5436,7 +5436,7 @@
         <v>37150</v>
       </c>
       <c r="B626" t="n">
-        <v>-0.6888411774602883</v>
+        <v>0.01814126954057628</v>
       </c>
     </row>
     <row r="627">
@@ -5444,7 +5444,7 @@
         <v>37151</v>
       </c>
       <c r="B627" t="n">
-        <v>0.5957869114575888</v>
+        <v>-0.5087254889720648</v>
       </c>
     </row>
     <row r="628">
@@ -5452,7 +5452,7 @@
         <v>37152</v>
       </c>
       <c r="B628" t="n">
-        <v>0.1340531484480545</v>
+        <v>-0.8663341470279122</v>
       </c>
     </row>
     <row r="629">
@@ -5460,7 +5460,7 @@
         <v>37153</v>
       </c>
       <c r="B629" t="n">
-        <v>0.06477386573014741</v>
+        <v>0.257170910333067</v>
       </c>
     </row>
     <row r="630">
@@ -5468,7 +5468,7 @@
         <v>37154</v>
       </c>
       <c r="B630" t="n">
-        <v>0.3013913460109029</v>
+        <v>-2.525029757901078</v>
       </c>
     </row>
     <row r="631">
@@ -5476,7 +5476,7 @@
         <v>37155</v>
       </c>
       <c r="B631" t="n">
-        <v>-0.2431434479361378</v>
+        <v>2.108333070339484</v>
       </c>
     </row>
     <row r="632">
@@ -5484,7 +5484,7 @@
         <v>37156</v>
       </c>
       <c r="B632" t="n">
-        <v>-0.6040464687163684</v>
+        <v>0.2409366217575266</v>
       </c>
     </row>
     <row r="633">
@@ -5492,7 +5492,7 @@
         <v>37157</v>
       </c>
       <c r="B633" t="n">
-        <v>0.8789028367504359</v>
+        <v>1.27369963516952</v>
       </c>
     </row>
     <row r="634">
@@ -5500,7 +5500,7 @@
         <v>37158</v>
       </c>
       <c r="B634" t="n">
-        <v>1.777176708597544</v>
+        <v>-0.7722704671838898</v>
       </c>
     </row>
     <row r="635">
@@ -5508,7 +5508,7 @@
         <v>37159</v>
       </c>
       <c r="B635" t="n">
-        <v>1.42466380652835</v>
+        <v>-0.6123373839183075</v>
       </c>
     </row>
     <row r="636">
@@ -5516,7 +5516,7 @@
         <v>37160</v>
       </c>
       <c r="B636" t="n">
-        <v>0.1134632683867228</v>
+        <v>-0.1266603832466968</v>
       </c>
     </row>
     <row r="637">
@@ -5524,7 +5524,7 @@
         <v>37161</v>
       </c>
       <c r="B637" t="n">
-        <v>1.444381120364999</v>
+        <v>-0.7218571532744196</v>
       </c>
     </row>
     <row r="638">
@@ -5532,7 +5532,7 @@
         <v>37162</v>
       </c>
       <c r="B638" t="n">
-        <v>0.214427922224735</v>
+        <v>0.3254003862036697</v>
       </c>
     </row>
     <row r="639">
@@ -5540,7 +5540,7 @@
         <v>37163</v>
       </c>
       <c r="B639" t="n">
-        <v>-0.2098233298963926</v>
+        <v>-1.059350084693977</v>
       </c>
     </row>
     <row r="640">
@@ -5548,7 +5548,7 @@
         <v>37164</v>
       </c>
       <c r="B640" t="n">
-        <v>-1.035756562765524</v>
+        <v>0.8348591588458354</v>
       </c>
     </row>
     <row r="641">
@@ -5556,7 +5556,7 @@
         <v>37165</v>
       </c>
       <c r="B641" t="n">
-        <v>0.6913162850185611</v>
+        <v>-0.4879586975967936</v>
       </c>
     </row>
     <row r="642">
@@ -5564,7 +5564,7 @@
         <v>37166</v>
       </c>
       <c r="B642" t="n">
-        <v>-0.4075713620521898</v>
+        <v>-0.3418985056353199</v>
       </c>
     </row>
     <row r="643">
@@ -5572,7 +5572,7 @@
         <v>37167</v>
       </c>
       <c r="B643" t="n">
-        <v>-0.4473036322802538</v>
+        <v>-0.04572409712577032</v>
       </c>
     </row>
     <row r="644">
@@ -5580,7 +5580,7 @@
         <v>37168</v>
       </c>
       <c r="B644" t="n">
-        <v>-0.382673119284585</v>
+        <v>-0.6280888293522122</v>
       </c>
     </row>
     <row r="645">
@@ -5588,7 +5588,7 @@
         <v>37169</v>
       </c>
       <c r="B645" t="n">
-        <v>-0.5803809813332443</v>
+        <v>1.591632158264461</v>
       </c>
     </row>
     <row r="646">
@@ -5596,7 +5596,7 @@
         <v>37170</v>
       </c>
       <c r="B646" t="n">
-        <v>-0.3377538295214425</v>
+        <v>-0.6024670069910151</v>
       </c>
     </row>
     <row r="647">
@@ -5604,7 +5604,7 @@
         <v>37171</v>
       </c>
       <c r="B647" t="n">
-        <v>0.157793671679774</v>
+        <v>0.0002299592818219656</v>
       </c>
     </row>
     <row r="648">
@@ -5612,7 +5612,7 @@
         <v>37172</v>
       </c>
       <c r="B648" t="n">
-        <v>0.3162608919986329</v>
+        <v>-0.4038742420682898</v>
       </c>
     </row>
     <row r="649">
@@ -5620,7 +5620,7 @@
         <v>37173</v>
       </c>
       <c r="B649" t="n">
-        <v>-0.5221155163116112</v>
+        <v>-0.308897133162104</v>
       </c>
     </row>
     <row r="650">
@@ -5628,7 +5628,7 @@
         <v>37174</v>
       </c>
       <c r="B650" t="n">
-        <v>-0.9818108651516968</v>
+        <v>0.9982739558115712</v>
       </c>
     </row>
     <row r="651">
@@ -5636,7 +5636,7 @@
         <v>37175</v>
       </c>
       <c r="B651" t="n">
-        <v>1.259701796225498</v>
+        <v>1.334009539456342</v>
       </c>
     </row>
     <row r="652">
@@ -5644,7 +5644,7 @@
         <v>37176</v>
       </c>
       <c r="B652" t="n">
-        <v>0.2971243965618626</v>
+        <v>0.3649642021918484</v>
       </c>
     </row>
     <row r="653">
@@ -5652,7 +5652,7 @@
         <v>37177</v>
       </c>
       <c r="B653" t="n">
-        <v>0.0660840563785326</v>
+        <v>0.2937030204233155</v>
       </c>
     </row>
     <row r="654">
@@ -5660,7 +5660,7 @@
         <v>37178</v>
       </c>
       <c r="B654" t="n">
-        <v>-0.8183437274825052</v>
+        <v>2.713934891589309</v>
       </c>
     </row>
     <row r="655">
@@ -5668,7 +5668,7 @@
         <v>37179</v>
       </c>
       <c r="B655" t="n">
-        <v>-0.6945316342887957</v>
+        <v>-0.7241426285512209</v>
       </c>
     </row>
     <row r="656">
@@ -5676,7 +5676,7 @@
         <v>37180</v>
       </c>
       <c r="B656" t="n">
-        <v>0.5377416591192051</v>
+        <v>0.09903781286916311</v>
       </c>
     </row>
     <row r="657">
@@ -5684,7 +5684,7 @@
         <v>37181</v>
       </c>
       <c r="B657" t="n">
-        <v>0.5843708525569932</v>
+        <v>-1.650174345651973</v>
       </c>
     </row>
     <row r="658">
@@ -5692,7 +5692,7 @@
         <v>37182</v>
       </c>
       <c r="B658" t="n">
-        <v>-1.221138517450944</v>
+        <v>-0.6166346600100685</v>
       </c>
     </row>
     <row r="659">
@@ -5700,7 +5700,7 @@
         <v>37183</v>
       </c>
       <c r="B659" t="n">
-        <v>-2.10338125584496</v>
+        <v>-0.215850412014632</v>
       </c>
     </row>
     <row r="660">
@@ -5708,7 +5708,7 @@
         <v>37184</v>
       </c>
       <c r="B660" t="n">
-        <v>0.7091431633961637</v>
+        <v>-1.616816472781214</v>
       </c>
     </row>
     <row r="661">
@@ -5716,7 +5716,7 @@
         <v>37185</v>
       </c>
       <c r="B661" t="n">
-        <v>-0.2750708226313472</v>
+        <v>-1.597383291584767</v>
       </c>
     </row>
     <row r="662">
@@ -5724,7 +5724,7 @@
         <v>37186</v>
       </c>
       <c r="B662" t="n">
-        <v>2.377178202851144</v>
+        <v>0.5851391315319296</v>
       </c>
     </row>
     <row r="663">
@@ -5732,7 +5732,7 @@
         <v>37187</v>
       </c>
       <c r="B663" t="n">
-        <v>-0.5328958894772353</v>
+        <v>-1.005326232967648</v>
       </c>
     </row>
     <row r="664">
@@ -5740,7 +5740,7 @@
         <v>37188</v>
       </c>
       <c r="B664" t="n">
-        <v>0.2396017463873879</v>
+        <v>1.646335934156553</v>
       </c>
     </row>
     <row r="665">
@@ -5748,7 +5748,7 @@
         <v>37189</v>
       </c>
       <c r="B665" t="n">
-        <v>0.1152225632819402</v>
+        <v>-0.9141366046377291</v>
       </c>
     </row>
     <row r="666">
@@ -5756,7 +5756,7 @@
         <v>37190</v>
       </c>
       <c r="B666" t="n">
-        <v>0.3407778130590116</v>
+        <v>1.196038484987298</v>
       </c>
     </row>
     <row r="667">
@@ -5764,7 +5764,7 @@
         <v>37191</v>
       </c>
       <c r="B667" t="n">
-        <v>-1.390811105865061</v>
+        <v>0.5138735806295364</v>
       </c>
     </row>
     <row r="668">
@@ -5772,7 +5772,7 @@
         <v>37192</v>
       </c>
       <c r="B668" t="n">
-        <v>0.6283950107009315</v>
+        <v>0.7354204404569401</v>
       </c>
     </row>
     <row r="669">
@@ -5780,7 +5780,7 @@
         <v>37193</v>
       </c>
       <c r="B669" t="n">
-        <v>1.02399546483503</v>
+        <v>0.1365819022803253</v>
       </c>
     </row>
     <row r="670">
@@ -5788,7 +5788,7 @@
         <v>37194</v>
       </c>
       <c r="B670" t="n">
-        <v>-2.228825926687465</v>
+        <v>0.1566423615284931</v>
       </c>
     </row>
     <row r="671">
@@ -5796,7 +5796,7 @@
         <v>37195</v>
       </c>
       <c r="B671" t="n">
-        <v>-0.4287759969379401</v>
+        <v>0.2340843972324317</v>
       </c>
     </row>
     <row r="672">
@@ -5804,7 +5804,7 @@
         <v>37196</v>
       </c>
       <c r="B672" t="n">
-        <v>-0.02046155994231981</v>
+        <v>0.700710657891535</v>
       </c>
     </row>
     <row r="673">
@@ -5812,7 +5812,7 @@
         <v>37197</v>
       </c>
       <c r="B673" t="n">
-        <v>-0.9678769382491836</v>
+        <v>1.841534915166303</v>
       </c>
     </row>
     <row r="674">
@@ -5820,7 +5820,7 @@
         <v>37198</v>
       </c>
       <c r="B674" t="n">
-        <v>-0.5667436970559677</v>
+        <v>0.4198543711694771</v>
       </c>
     </row>
     <row r="675">
@@ -5828,7 +5828,7 @@
         <v>37199</v>
       </c>
       <c r="B675" t="n">
-        <v>0.838016329825417</v>
+        <v>-0.4664375663143602</v>
       </c>
     </row>
     <row r="676">
@@ -5836,7 +5836,7 @@
         <v>37200</v>
       </c>
       <c r="B676" t="n">
-        <v>0.4419896269520039</v>
+        <v>0.3307696156129326</v>
       </c>
     </row>
     <row r="677">
@@ -5844,7 +5844,7 @@
         <v>37201</v>
       </c>
       <c r="B677" t="n">
-        <v>0.4028883771456246</v>
+        <v>0.240184272320509</v>
       </c>
     </row>
     <row r="678">
@@ -5852,7 +5852,7 @@
         <v>37202</v>
       </c>
       <c r="B678" t="n">
-        <v>1.68696449073</v>
+        <v>0.1051109385347474</v>
       </c>
     </row>
     <row r="679">
@@ -5860,7 +5860,7 @@
         <v>37203</v>
       </c>
       <c r="B679" t="n">
-        <v>1.722091359082728</v>
+        <v>-1.434456957961365</v>
       </c>
     </row>
     <row r="680">
@@ -5868,7 +5868,7 @@
         <v>37204</v>
       </c>
       <c r="B680" t="n">
-        <v>-0.3902483307284526</v>
+        <v>-1.767617809186795</v>
       </c>
     </row>
     <row r="681">
@@ -5876,7 +5876,7 @@
         <v>37205</v>
       </c>
       <c r="B681" t="n">
-        <v>0.6177037869854585</v>
+        <v>-0.3542893795931242</v>
       </c>
     </row>
     <row r="682">
@@ -5884,7 +5884,7 @@
         <v>37206</v>
       </c>
       <c r="B682" t="n">
-        <v>0.4243149656778133</v>
+        <v>2.03744308542995</v>
       </c>
     </row>
     <row r="683">
@@ -5892,7 +5892,7 @@
         <v>37207</v>
       </c>
       <c r="B683" t="n">
-        <v>-0.5171542764214178</v>
+        <v>0.5747137927961841</v>
       </c>
     </row>
     <row r="684">
@@ -5900,7 +5900,7 @@
         <v>37208</v>
       </c>
       <c r="B684" t="n">
-        <v>0.1611642719856003</v>
+        <v>0.5133073314563684</v>
       </c>
     </row>
     <row r="685">
@@ -5908,7 +5908,7 @@
         <v>37209</v>
       </c>
       <c r="B685" t="n">
-        <v>1.211363525869985</v>
+        <v>0.5390628566362221</v>
       </c>
     </row>
     <row r="686">
@@ -5916,7 +5916,7 @@
         <v>37210</v>
       </c>
       <c r="B686" t="n">
-        <v>0.6160547923712202</v>
+        <v>2.098462292194561</v>
       </c>
     </row>
     <row r="687">
@@ -5924,7 +5924,7 @@
         <v>37211</v>
       </c>
       <c r="B687" t="n">
-        <v>0.2882960726680446</v>
+        <v>0.683373548982287</v>
       </c>
     </row>
     <row r="688">
@@ -5932,7 +5932,7 @@
         <v>37212</v>
       </c>
       <c r="B688" t="n">
-        <v>0.8717069865251761</v>
+        <v>-1.614910838688928</v>
       </c>
     </row>
     <row r="689">
@@ -5940,7 +5940,7 @@
         <v>37213</v>
       </c>
       <c r="B689" t="n">
-        <v>0.8523537722821333</v>
+        <v>0.8377098908569802</v>
       </c>
     </row>
     <row r="690">
@@ -5948,7 +5948,7 @@
         <v>37214</v>
       </c>
       <c r="B690" t="n">
-        <v>0.313615327057483</v>
+        <v>0.9274266829294819</v>
       </c>
     </row>
     <row r="691">
@@ -5956,7 +5956,7 @@
         <v>37215</v>
       </c>
       <c r="B691" t="n">
-        <v>0.554832046389514</v>
+        <v>0.4975551941105614</v>
       </c>
     </row>
     <row r="692">
@@ -5964,7 +5964,7 @@
         <v>37216</v>
       </c>
       <c r="B692" t="n">
-        <v>-0.6157343052807269</v>
+        <v>-1.03004633279036</v>
       </c>
     </row>
     <row r="693">
@@ -5972,7 +5972,7 @@
         <v>37217</v>
       </c>
       <c r="B693" t="n">
-        <v>-0.6094992709171236</v>
+        <v>1.282671315370981</v>
       </c>
     </row>
     <row r="694">
@@ -5980,7 +5980,7 @@
         <v>37218</v>
       </c>
       <c r="B694" t="n">
-        <v>-0.1322166034510073</v>
+        <v>0.6878021251007933</v>
       </c>
     </row>
     <row r="695">
@@ -5988,7 +5988,7 @@
         <v>37219</v>
       </c>
       <c r="B695" t="n">
-        <v>-0.5081611122973662</v>
+        <v>1.059498858115756</v>
       </c>
     </row>
     <row r="696">
@@ -5996,7 +5996,7 @@
         <v>37220</v>
       </c>
       <c r="B696" t="n">
-        <v>0.9276217149694226</v>
+        <v>0.8146798255768435</v>
       </c>
     </row>
     <row r="697">
@@ -6004,7 +6004,7 @@
         <v>37221</v>
       </c>
       <c r="B697" t="n">
-        <v>-0.06083776936567688</v>
+        <v>0.8340346315322462</v>
       </c>
     </row>
     <row r="698">
@@ -6012,7 +6012,7 @@
         <v>37222</v>
       </c>
       <c r="B698" t="n">
-        <v>-0.9093544504871023</v>
+        <v>0.08167799232046431</v>
       </c>
     </row>
     <row r="699">
@@ -6020,7 +6020,7 @@
         <v>37223</v>
       </c>
       <c r="B699" t="n">
-        <v>1.137260213395116</v>
+        <v>1.925306252453966</v>
       </c>
     </row>
     <row r="700">
@@ -6028,7 +6028,7 @@
         <v>37224</v>
       </c>
       <c r="B700" t="n">
-        <v>-0.9010895638041736</v>
+        <v>-0.8372088735866047</v>
       </c>
     </row>
     <row r="701">
@@ -6036,7 +6036,7 @@
         <v>37225</v>
       </c>
       <c r="B701" t="n">
-        <v>-1.964203113041654</v>
+        <v>-0.1240614213289063</v>
       </c>
     </row>
     <row r="702">
@@ -6044,7 +6044,7 @@
         <v>37226</v>
       </c>
       <c r="B702" t="n">
-        <v>-0.07407960751366989</v>
+        <v>0.3939620301214425</v>
       </c>
     </row>
     <row r="703">
@@ -6052,7 +6052,7 @@
         <v>37227</v>
       </c>
       <c r="B703" t="n">
-        <v>-0.009931143239751649</v>
+        <v>-0.570696784856721</v>
       </c>
     </row>
     <row r="704">
@@ -6060,7 +6060,7 @@
         <v>37228</v>
       </c>
       <c r="B704" t="n">
-        <v>-0.02657538915266117</v>
+        <v>0.7114386316688325</v>
       </c>
     </row>
     <row r="705">
@@ -6068,7 +6068,7 @@
         <v>37229</v>
       </c>
       <c r="B705" t="n">
-        <v>1.822246309587432</v>
+        <v>-0.158691792872931</v>
       </c>
     </row>
     <row r="706">
@@ -6076,7 +6076,7 @@
         <v>37230</v>
       </c>
       <c r="B706" t="n">
-        <v>0.7633706683907843</v>
+        <v>-0.5416156923691186</v>
       </c>
     </row>
     <row r="707">
@@ -6084,7 +6084,7 @@
         <v>37231</v>
       </c>
       <c r="B707" t="n">
-        <v>-0.5112765227507566</v>
+        <v>1.04817941929498</v>
       </c>
     </row>
     <row r="708">
@@ -6092,7 +6092,7 @@
         <v>37232</v>
       </c>
       <c r="B708" t="n">
-        <v>-1.244582350687569</v>
+        <v>0.9062203653310517</v>
       </c>
     </row>
     <row r="709">
@@ -6100,7 +6100,7 @@
         <v>37233</v>
       </c>
       <c r="B709" t="n">
-        <v>-0.2096469091042504</v>
+        <v>-0.4519794710182609</v>
       </c>
     </row>
     <row r="710">
@@ -6108,7 +6108,7 @@
         <v>37234</v>
       </c>
       <c r="B710" t="n">
-        <v>-0.3641256008078048</v>
+        <v>-1.246748940997163</v>
       </c>
     </row>
     <row r="711">
@@ -6116,7 +6116,7 @@
         <v>37235</v>
       </c>
       <c r="B711" t="n">
-        <v>-0.01381585792435504</v>
+        <v>1.419708000361352</v>
       </c>
     </row>
     <row r="712">
@@ -6124,7 +6124,7 @@
         <v>37236</v>
       </c>
       <c r="B712" t="n">
-        <v>0.5425594969909117</v>
+        <v>0.7584495533382215</v>
       </c>
     </row>
     <row r="713">
@@ -6132,7 +6132,7 @@
         <v>37237</v>
       </c>
       <c r="B713" t="n">
-        <v>0.2795662775598434</v>
+        <v>-1.225724470450003</v>
       </c>
     </row>
     <row r="714">
@@ -6140,7 +6140,7 @@
         <v>37238</v>
       </c>
       <c r="B714" t="n">
-        <v>-1.044733838066226</v>
+        <v>0.6860631328294484</v>
       </c>
     </row>
     <row r="715">
@@ -6148,7 +6148,7 @@
         <v>37239</v>
       </c>
       <c r="B715" t="n">
-        <v>0.8314271810489282</v>
+        <v>0.08272540165290045</v>
       </c>
     </row>
     <row r="716">
@@ -6156,7 +6156,7 @@
         <v>37240</v>
       </c>
       <c r="B716" t="n">
-        <v>1.24516170160542</v>
+        <v>0.3866249970569661</v>
       </c>
     </row>
     <row r="717">
@@ -6164,7 +6164,7 @@
         <v>37241</v>
       </c>
       <c r="B717" t="n">
-        <v>-0.7017791478814526</v>
+        <v>-2.241842604914792</v>
       </c>
     </row>
     <row r="718">
@@ -6172,7 +6172,7 @@
         <v>37242</v>
       </c>
       <c r="B718" t="n">
-        <v>-0.72286429432667</v>
+        <v>-0.3623601024408089</v>
       </c>
     </row>
     <row r="719">
@@ -6180,7 +6180,7 @@
         <v>37243</v>
       </c>
       <c r="B719" t="n">
-        <v>1.6143736884688</v>
+        <v>0.9203743742392744</v>
       </c>
     </row>
     <row r="720">
@@ -6188,7 +6188,7 @@
         <v>37244</v>
       </c>
       <c r="B720" t="n">
-        <v>0.09970033981319991</v>
+        <v>-0.6184999492838525</v>
       </c>
     </row>
     <row r="721">
@@ -6196,7 +6196,7 @@
         <v>37245</v>
       </c>
       <c r="B721" t="n">
-        <v>-0.9464546634780315</v>
+        <v>-2.173801277917241</v>
       </c>
     </row>
     <row r="722">
@@ -6204,7 +6204,7 @@
         <v>37246</v>
       </c>
       <c r="B722" t="n">
-        <v>0.06003298879782382</v>
+        <v>2.380976072710135</v>
       </c>
     </row>
     <row r="723">
@@ -6212,7 +6212,7 @@
         <v>37247</v>
       </c>
       <c r="B723" t="n">
-        <v>0.277085686125948</v>
+        <v>-0.7522986291595186</v>
       </c>
     </row>
     <row r="724">
@@ -6220,7 +6220,7 @@
         <v>37248</v>
       </c>
       <c r="B724" t="n">
-        <v>0.3654014064685078</v>
+        <v>-0.6685504809137737</v>
       </c>
     </row>
     <row r="725">
@@ -6228,7 +6228,7 @@
         <v>37249</v>
       </c>
       <c r="B725" t="n">
-        <v>-1.394881632136976</v>
+        <v>0.227197727985787</v>
       </c>
     </row>
     <row r="726">
@@ -6236,7 +6236,7 @@
         <v>37250</v>
       </c>
       <c r="B726" t="n">
-        <v>-0.2519753259278573</v>
+        <v>0.563558984560992</v>
       </c>
     </row>
     <row r="727">
@@ -6244,7 +6244,7 @@
         <v>37251</v>
       </c>
       <c r="B727" t="n">
-        <v>-0.9109622908055697</v>
+        <v>-0.1466515991558563</v>
       </c>
     </row>
     <row r="728">
@@ -6252,7 +6252,7 @@
         <v>37252</v>
       </c>
       <c r="B728" t="n">
-        <v>1.90793937647261</v>
+        <v>0.3371584682855638</v>
       </c>
     </row>
     <row r="729">
@@ -6260,7 +6260,7 @@
         <v>37253</v>
       </c>
       <c r="B729" t="n">
-        <v>-1.098953179396408</v>
+        <v>-2.084112770217673</v>
       </c>
     </row>
     <row r="730">
@@ -6268,7 +6268,7 @@
         <v>37254</v>
       </c>
       <c r="B730" t="n">
-        <v>-0.7284637231160935</v>
+        <v>0.9923318208824174</v>
       </c>
     </row>
     <row r="731">
@@ -6276,7 +6276,7 @@
         <v>37255</v>
       </c>
       <c r="B731" t="n">
-        <v>-2.331170428773804</v>
+        <v>-0.5085394531662472</v>
       </c>
     </row>
     <row r="732">
@@ -6284,7 +6284,7 @@
         <v>37256</v>
       </c>
       <c r="B732" t="n">
-        <v>-0.9042159178539519</v>
+        <v>-0.9128239144226546</v>
       </c>
     </row>
     <row r="733">
@@ -6292,7 +6292,7 @@
         <v>37257</v>
       </c>
       <c r="B733" t="n">
-        <v>1.364220219271522</v>
+        <v>-0.01098096046920004</v>
       </c>
     </row>
     <row r="734">
@@ -6300,7 +6300,7 @@
         <v>37258</v>
       </c>
       <c r="B734" t="n">
-        <v>-0.2693293857413061</v>
+        <v>-0.05584537489191919</v>
       </c>
     </row>
     <row r="735">
@@ -6308,7 +6308,7 @@
         <v>37259</v>
       </c>
       <c r="B735" t="n">
-        <v>2.01476284695625</v>
+        <v>-0.4981304631712394</v>
       </c>
     </row>
     <row r="736">
@@ -6316,7 +6316,7 @@
         <v>37260</v>
       </c>
       <c r="B736" t="n">
-        <v>-0.2437658778431185</v>
+        <v>-0.202297492756766</v>
       </c>
     </row>
     <row r="737">
@@ -6324,7 +6324,7 @@
         <v>37261</v>
       </c>
       <c r="B737" t="n">
-        <v>-1.44733529414185</v>
+        <v>2.186163540806989</v>
       </c>
     </row>
     <row r="738">
@@ -6332,7 +6332,7 @@
         <v>37262</v>
       </c>
       <c r="B738" t="n">
-        <v>-0.7234466550154309</v>
+        <v>-0.5062222759856548</v>
       </c>
     </row>
     <row r="739">
@@ -6340,7 +6340,7 @@
         <v>37263</v>
       </c>
       <c r="B739" t="n">
-        <v>0.215993642198517</v>
+        <v>-0.5686205402890718</v>
       </c>
     </row>
     <row r="740">
@@ -6348,7 +6348,7 @@
         <v>37264</v>
       </c>
       <c r="B740" t="n">
-        <v>-0.7807357233909933</v>
+        <v>1.302897492933988</v>
       </c>
     </row>
     <row r="741">
@@ -6356,7 +6356,7 @@
         <v>37265</v>
       </c>
       <c r="B741" t="n">
-        <v>-0.9425631685128401</v>
+        <v>0.04607897761838807</v>
       </c>
     </row>
     <row r="742">
@@ -6364,7 +6364,7 @@
         <v>37266</v>
       </c>
       <c r="B742" t="n">
-        <v>-0.392967052681476</v>
+        <v>-0.2043893924366172</v>
       </c>
     </row>
     <row r="743">
@@ -6372,7 +6372,7 @@
         <v>37267</v>
       </c>
       <c r="B743" t="n">
-        <v>0.8301885880749578</v>
+        <v>0.1084088115723422</v>
       </c>
     </row>
     <row r="744">
@@ -6380,7 +6380,7 @@
         <v>37268</v>
       </c>
       <c r="B744" t="n">
-        <v>0.7296137821306563</v>
+        <v>1.518668739271193</v>
       </c>
     </row>
     <row r="745">
@@ -6388,7 +6388,7 @@
         <v>37269</v>
       </c>
       <c r="B745" t="n">
-        <v>-0.5920863184613805</v>
+        <v>-0.5637097779999801</v>
       </c>
     </row>
     <row r="746">
@@ -6396,7 +6396,7 @@
         <v>37270</v>
       </c>
       <c r="B746" t="n">
-        <v>0.1167953333569776</v>
+        <v>1.11259412230899</v>
       </c>
     </row>
     <row r="747">
@@ -6404,7 +6404,7 @@
         <v>37271</v>
       </c>
       <c r="B747" t="n">
-        <v>-0.5034658569033837</v>
+        <v>-0.4744349193663582</v>
       </c>
     </row>
     <row r="748">
@@ -6412,7 +6412,7 @@
         <v>37272</v>
       </c>
       <c r="B748" t="n">
-        <v>1.133100490910176</v>
+        <v>0.08009362238015387</v>
       </c>
     </row>
     <row r="749">
@@ -6420,7 +6420,7 @@
         <v>37273</v>
       </c>
       <c r="B749" t="n">
-        <v>1.832748477612305</v>
+        <v>1.348836929043598</v>
       </c>
     </row>
     <row r="750">
@@ -6428,7 +6428,7 @@
         <v>37274</v>
       </c>
       <c r="B750" t="n">
-        <v>-0.01416227304593967</v>
+        <v>-0.528183081951316</v>
       </c>
     </row>
     <row r="751">
@@ -6436,7 +6436,7 @@
         <v>37275</v>
       </c>
       <c r="B751" t="n">
-        <v>1.04859313713409</v>
+        <v>0.6865783184027948</v>
       </c>
     </row>
     <row r="752">
@@ -6444,7 +6444,7 @@
         <v>37276</v>
       </c>
       <c r="B752" t="n">
-        <v>2.035433420241394</v>
+        <v>0.3072699355524973</v>
       </c>
     </row>
     <row r="753">
@@ -6452,7 +6452,7 @@
         <v>37277</v>
       </c>
       <c r="B753" t="n">
-        <v>-0.4175253763727064</v>
+        <v>-0.4428987902620704</v>
       </c>
     </row>
     <row r="754">
@@ -6460,7 +6460,7 @@
         <v>37278</v>
       </c>
       <c r="B754" t="n">
-        <v>-0.5720854840084618</v>
+        <v>0.216144002131695</v>
       </c>
     </row>
     <row r="755">
@@ -6468,7 +6468,7 @@
         <v>37279</v>
       </c>
       <c r="B755" t="n">
-        <v>2.481447734141423</v>
+        <v>2.062348526894793</v>
       </c>
     </row>
     <row r="756">
@@ -6476,7 +6476,7 @@
         <v>37280</v>
       </c>
       <c r="B756" t="n">
-        <v>-0.08005784082289505</v>
+        <v>-0.6509539307533231</v>
       </c>
     </row>
     <row r="757">
@@ -6484,7 +6484,7 @@
         <v>37281</v>
       </c>
       <c r="B757" t="n">
-        <v>1.013830184338486</v>
+        <v>-0.4896403300030014</v>
       </c>
     </row>
     <row r="758">
@@ -6492,7 +6492,7 @@
         <v>37282</v>
       </c>
       <c r="B758" t="n">
-        <v>-1.185744928518073</v>
+        <v>1.593755837553264</v>
       </c>
     </row>
     <row r="759">
@@ -6500,7 +6500,7 @@
         <v>37283</v>
       </c>
       <c r="B759" t="n">
-        <v>-0.6507590468024476</v>
+        <v>-1.4671193209767</v>
       </c>
     </row>
     <row r="760">
@@ -6508,7 +6508,7 @@
         <v>37284</v>
       </c>
       <c r="B760" t="n">
-        <v>1.831684707974678</v>
+        <v>0.09048505654645887</v>
       </c>
     </row>
     <row r="761">
@@ -6516,7 +6516,7 @@
         <v>37285</v>
       </c>
       <c r="B761" t="n">
-        <v>-0.9624329165639333</v>
+        <v>1.453172559270033</v>
       </c>
     </row>
     <row r="762">
@@ -6524,7 +6524,7 @@
         <v>37286</v>
       </c>
       <c r="B762" t="n">
-        <v>0.4843547073702403</v>
+        <v>-1.680924370036758</v>
       </c>
     </row>
     <row r="763">
@@ -6532,7 +6532,7 @@
         <v>37287</v>
       </c>
       <c r="B763" t="n">
-        <v>-0.6727751573089448</v>
+        <v>-0.04550596369818786</v>
       </c>
     </row>
     <row r="764">
@@ -6540,7 +6540,7 @@
         <v>37288</v>
       </c>
       <c r="B764" t="n">
-        <v>-1.464210869549761</v>
+        <v>-1.023459417013041</v>
       </c>
     </row>
     <row r="765">
@@ -6548,7 +6548,7 @@
         <v>37289</v>
       </c>
       <c r="B765" t="n">
-        <v>-0.02847745846214854</v>
+        <v>-0.7311511658410392</v>
       </c>
     </row>
     <row r="766">
@@ -6556,7 +6556,7 @@
         <v>37290</v>
       </c>
       <c r="B766" t="n">
-        <v>1.02651709811376</v>
+        <v>1.03892648771053</v>
       </c>
     </row>
     <row r="767">
@@ -6564,7 +6564,7 @@
         <v>37291</v>
       </c>
       <c r="B767" t="n">
-        <v>-0.2455142418097435</v>
+        <v>0.2011587341870801</v>
       </c>
     </row>
     <row r="768">
@@ -6572,7 +6572,7 @@
         <v>37292</v>
       </c>
       <c r="B768" t="n">
-        <v>0.4008406419466534</v>
+        <v>-2.266193429322763</v>
       </c>
     </row>
     <row r="769">
@@ -6580,7 +6580,7 @@
         <v>37293</v>
       </c>
       <c r="B769" t="n">
-        <v>1.630006694429489</v>
+        <v>-0.6992904915335503</v>
       </c>
     </row>
     <row r="770">
@@ -6588,7 +6588,7 @@
         <v>37294</v>
       </c>
       <c r="B770" t="n">
-        <v>-0.1667076386479845</v>
+        <v>-0.711488189566272</v>
       </c>
     </row>
     <row r="771">
@@ -6596,7 +6596,7 @@
         <v>37295</v>
       </c>
       <c r="B771" t="n">
-        <v>-0.8617279091550336</v>
+        <v>-2.225102079354701</v>
       </c>
     </row>
     <row r="772">
@@ -6604,7 +6604,7 @@
         <v>37296</v>
       </c>
       <c r="B772" t="n">
-        <v>-0.4160726963015086</v>
+        <v>1.180010809128136</v>
       </c>
     </row>
     <row r="773">
@@ -6612,7 +6612,7 @@
         <v>37297</v>
       </c>
       <c r="B773" t="n">
-        <v>0.9393611233035908</v>
+        <v>0.9646268155923603</v>
       </c>
     </row>
     <row r="774">
@@ -6620,7 +6620,7 @@
         <v>37298</v>
       </c>
       <c r="B774" t="n">
-        <v>-0.4975362436930809</v>
+        <v>0.1017314506930035</v>
       </c>
     </row>
     <row r="775">
@@ -6628,7 +6628,7 @@
         <v>37299</v>
       </c>
       <c r="B775" t="n">
-        <v>0.5797692300589604</v>
+        <v>-0.8920512356289214</v>
       </c>
     </row>
     <row r="776">
@@ -6636,7 +6636,7 @@
         <v>37300</v>
       </c>
       <c r="B776" t="n">
-        <v>-0.5036228425196498</v>
+        <v>-0.2865271014091411</v>
       </c>
     </row>
     <row r="777">
@@ -6644,7 +6644,7 @@
         <v>37301</v>
       </c>
       <c r="B777" t="n">
-        <v>1.622685283558446</v>
+        <v>2.265455983127285</v>
       </c>
     </row>
     <row r="778">
@@ -6652,7 +6652,7 @@
         <v>37302</v>
       </c>
       <c r="B778" t="n">
-        <v>-1.896711751029198</v>
+        <v>2.499583720891479</v>
       </c>
     </row>
     <row r="779">
@@ -6660,7 +6660,7 @@
         <v>37303</v>
       </c>
       <c r="B779" t="n">
-        <v>0.7722251761751668</v>
+        <v>-0.08523389959349351</v>
       </c>
     </row>
     <row r="780">
@@ -6668,7 +6668,7 @@
         <v>37304</v>
       </c>
       <c r="B780" t="n">
-        <v>0.3950197286966925</v>
+        <v>-0.4665099591990693</v>
       </c>
     </row>
     <row r="781">
@@ -6676,7 +6676,7 @@
         <v>37305</v>
       </c>
       <c r="B781" t="n">
-        <v>-1.062370230383603</v>
+        <v>0.6922303765591084</v>
       </c>
     </row>
     <row r="782">
@@ -6684,7 +6684,7 @@
         <v>37306</v>
       </c>
       <c r="B782" t="n">
-        <v>-1.928834494227803</v>
+        <v>-0.2484402633865441</v>
       </c>
     </row>
     <row r="783">
@@ -6692,7 +6692,7 @@
         <v>37307</v>
       </c>
       <c r="B783" t="n">
-        <v>-0.3461529598067439</v>
+        <v>-1.382389997968468</v>
       </c>
     </row>
     <row r="784">
@@ -6700,7 +6700,7 @@
         <v>37308</v>
       </c>
       <c r="B784" t="n">
-        <v>-0.2724019616127586</v>
+        <v>-0.6741190689013459</v>
       </c>
     </row>
     <row r="785">
@@ -6708,7 +6708,7 @@
         <v>37309</v>
       </c>
       <c r="B785" t="n">
-        <v>1.292521300618402</v>
+        <v>0.9131843367881555</v>
       </c>
     </row>
     <row r="786">
@@ -6716,7 +6716,7 @@
         <v>37310</v>
       </c>
       <c r="B786" t="n">
-        <v>0.2397310651584389</v>
+        <v>1.578107107696608</v>
       </c>
     </row>
     <row r="787">
@@ -6724,7 +6724,7 @@
         <v>37311</v>
       </c>
       <c r="B787" t="n">
-        <v>0.6365504825600919</v>
+        <v>-1.242919800571966</v>
       </c>
     </row>
     <row r="788">
@@ -6732,7 +6732,7 @@
         <v>37312</v>
       </c>
       <c r="B788" t="n">
-        <v>0.5714666973546323</v>
+        <v>2.191491939652122</v>
       </c>
     </row>
     <row r="789">
@@ -6740,7 +6740,7 @@
         <v>37313</v>
       </c>
       <c r="B789" t="n">
-        <v>2.758499077754803</v>
+        <v>0.1131043734879325</v>
       </c>
     </row>
     <row r="790">
@@ -6748,7 +6748,7 @@
         <v>37314</v>
       </c>
       <c r="B790" t="n">
-        <v>0.5413860659209189</v>
+        <v>0.04921922413790155</v>
       </c>
     </row>
     <row r="791">
@@ -6756,7 +6756,7 @@
         <v>37315</v>
       </c>
       <c r="B791" t="n">
-        <v>0.2162790202189888</v>
+        <v>-0.2669692038255156</v>
       </c>
     </row>
     <row r="792">
@@ -6764,7 +6764,7 @@
         <v>37316</v>
       </c>
       <c r="B792" t="n">
-        <v>-0.8613441442772916</v>
+        <v>-1.140856557565089</v>
       </c>
     </row>
     <row r="793">
@@ -6772,7 +6772,7 @@
         <v>37317</v>
       </c>
       <c r="B793" t="n">
-        <v>-0.04715118852566764</v>
+        <v>-1.078032142111891</v>
       </c>
     </row>
     <row r="794">
@@ -6780,7 +6780,7 @@
         <v>37318</v>
       </c>
       <c r="B794" t="n">
-        <v>1.378821834023934</v>
+        <v>1.161182459886355</v>
       </c>
     </row>
     <row r="795">
@@ -6788,7 +6788,7 @@
         <v>37319</v>
       </c>
       <c r="B795" t="n">
-        <v>0.1037546572868501</v>
+        <v>-0.468591617614912</v>
       </c>
     </row>
     <row r="796">
@@ -6796,7 +6796,7 @@
         <v>37320</v>
       </c>
       <c r="B796" t="n">
-        <v>-0.9334715605724858</v>
+        <v>0.8496228331336623</v>
       </c>
     </row>
     <row r="797">
@@ -6804,7 +6804,7 @@
         <v>37321</v>
       </c>
       <c r="B797" t="n">
-        <v>1.177440592319444</v>
+        <v>0.7563861824323679</v>
       </c>
     </row>
     <row r="798">
@@ -6812,7 +6812,7 @@
         <v>37322</v>
       </c>
       <c r="B798" t="n">
-        <v>-1.030101454114911</v>
+        <v>1.167100769208278</v>
       </c>
     </row>
     <row r="799">
@@ -6820,7 +6820,7 @@
         <v>37323</v>
       </c>
       <c r="B799" t="n">
-        <v>-0.2829993466493002</v>
+        <v>0.9313193408717476</v>
       </c>
     </row>
     <row r="800">
@@ -6828,7 +6828,7 @@
         <v>37324</v>
       </c>
       <c r="B800" t="n">
-        <v>-0.7236327737252631</v>
+        <v>0.8723830694418716</v>
       </c>
     </row>
     <row r="801">
@@ -6836,7 +6836,7 @@
         <v>37325</v>
       </c>
       <c r="B801" t="n">
-        <v>1.736719598576251</v>
+        <v>1.635697232558611</v>
       </c>
     </row>
     <row r="802">
@@ -6844,7 +6844,7 @@
         <v>37326</v>
       </c>
       <c r="B802" t="n">
-        <v>1.457163238780204</v>
+        <v>0.5999759694821827</v>
       </c>
     </row>
     <row r="803">
@@ -6852,7 +6852,7 @@
         <v>37327</v>
       </c>
       <c r="B803" t="n">
-        <v>0.8453534226518482</v>
+        <v>-0.1377931486206422</v>
       </c>
     </row>
     <row r="804">
@@ -6860,7 +6860,7 @@
         <v>37328</v>
       </c>
       <c r="B804" t="n">
-        <v>-0.6971100137761767</v>
+        <v>-0.7749694610394045</v>
       </c>
     </row>
     <row r="805">
@@ -6868,7 +6868,7 @@
         <v>37329</v>
       </c>
       <c r="B805" t="n">
-        <v>0.03435407822489557</v>
+        <v>0.154794499106861</v>
       </c>
     </row>
     <row r="806">
@@ -6876,7 +6876,7 @@
         <v>37330</v>
       </c>
       <c r="B806" t="n">
-        <v>-1.033745260929781</v>
+        <v>-0.5781505995082379</v>
       </c>
     </row>
     <row r="807">
@@ -6884,7 +6884,7 @@
         <v>37331</v>
       </c>
       <c r="B807" t="n">
-        <v>-0.7728671508311291</v>
+        <v>-0.7991364068355962</v>
       </c>
     </row>
     <row r="808">
@@ -6892,7 +6892,7 @@
         <v>37332</v>
       </c>
       <c r="B808" t="n">
-        <v>-0.596175087466886</v>
+        <v>-0.1282026320661103</v>
       </c>
     </row>
     <row r="809">
@@ -6900,7 +6900,7 @@
         <v>37333</v>
       </c>
       <c r="B809" t="n">
-        <v>0.0829206247544293</v>
+        <v>-0.02290375076993547</v>
       </c>
     </row>
     <row r="810">
@@ -6908,7 +6908,7 @@
         <v>37334</v>
       </c>
       <c r="B810" t="n">
-        <v>1.144160170337132</v>
+        <v>1.320152990713878</v>
       </c>
     </row>
     <row r="811">
@@ -6916,7 +6916,7 @@
         <v>37335</v>
       </c>
       <c r="B811" t="n">
-        <v>0.7840285045678497</v>
+        <v>-0.9077227644802414</v>
       </c>
     </row>
     <row r="812">
@@ -6924,7 +6924,7 @@
         <v>37336</v>
       </c>
       <c r="B812" t="n">
-        <v>-0.1996627667732368</v>
+        <v>0.1765775092455579</v>
       </c>
     </row>
     <row r="813">
@@ -6932,7 +6932,7 @@
         <v>37337</v>
       </c>
       <c r="B813" t="n">
-        <v>-1.068288002411854</v>
+        <v>-0.3606772552740718</v>
       </c>
     </row>
     <row r="814">
@@ -6940,7 +6940,7 @@
         <v>37338</v>
       </c>
       <c r="B814" t="n">
-        <v>-0.8697905268690237</v>
+        <v>0.9951820215143623</v>
       </c>
     </row>
     <row r="815">
@@ -6948,7 +6948,7 @@
         <v>37339</v>
       </c>
       <c r="B815" t="n">
-        <v>0.08607982478502012</v>
+        <v>-0.8630555369565973</v>
       </c>
     </row>
     <row r="816">
@@ -6956,7 +6956,7 @@
         <v>37340</v>
       </c>
       <c r="B816" t="n">
-        <v>0.8097659191662986</v>
+        <v>-1.730058832970166</v>
       </c>
     </row>
     <row r="817">
@@ -6964,7 +6964,7 @@
         <v>37341</v>
       </c>
       <c r="B817" t="n">
-        <v>-0.09838428840222735</v>
+        <v>1.934333312277957</v>
       </c>
     </row>
     <row r="818">
@@ -6972,7 +6972,7 @@
         <v>37342</v>
       </c>
       <c r="B818" t="n">
-        <v>0.9093235182681733</v>
+        <v>0.1066074134519776</v>
       </c>
     </row>
     <row r="819">
@@ -6980,7 +6980,7 @@
         <v>37343</v>
       </c>
       <c r="B819" t="n">
-        <v>1.264804911652676</v>
+        <v>-2.462488004541027</v>
       </c>
     </row>
     <row r="820">
@@ -6988,7 +6988,7 @@
         <v>37344</v>
       </c>
       <c r="B820" t="n">
-        <v>-0.5902712480093552</v>
+        <v>-0.4142331477131388</v>
       </c>
     </row>
     <row r="821">
@@ -6996,7 +6996,7 @@
         <v>37345</v>
       </c>
       <c r="B821" t="n">
-        <v>-1.593164416723144</v>
+        <v>-2.074517519152446</v>
       </c>
     </row>
     <row r="822">
@@ -7004,7 +7004,7 @@
         <v>37346</v>
       </c>
       <c r="B822" t="n">
-        <v>0.6157517967902053</v>
+        <v>-0.1516374112553882</v>
       </c>
     </row>
     <row r="823">
@@ -7012,7 +7012,7 @@
         <v>37347</v>
       </c>
       <c r="B823" t="n">
-        <v>-1.01334682053294</v>
+        <v>0.006899394212577847</v>
       </c>
     </row>
     <row r="824">
@@ -7020,7 +7020,7 @@
         <v>37348</v>
       </c>
       <c r="B824" t="n">
-        <v>1.435167822924767</v>
+        <v>-0.4120564848839158</v>
       </c>
     </row>
     <row r="825">
@@ -7028,7 +7028,7 @@
         <v>37349</v>
       </c>
       <c r="B825" t="n">
-        <v>-0.7995852290278747</v>
+        <v>-0.5885352775743581</v>
       </c>
     </row>
     <row r="826">
@@ -7036,7 +7036,7 @@
         <v>37350</v>
       </c>
       <c r="B826" t="n">
-        <v>-1.302927035876938</v>
+        <v>0.4777494510066856</v>
       </c>
     </row>
     <row r="827">
@@ -7044,7 +7044,7 @@
         <v>37351</v>
       </c>
       <c r="B827" t="n">
-        <v>-0.9971267173384849</v>
+        <v>0.2617590882509406</v>
       </c>
     </row>
     <row r="828">
@@ -7052,7 +7052,7 @@
         <v>37352</v>
       </c>
       <c r="B828" t="n">
-        <v>-0.00468137374630315</v>
+        <v>0.7903535292068593</v>
       </c>
     </row>
     <row r="829">
@@ -7060,7 +7060,7 @@
         <v>37353</v>
       </c>
       <c r="B829" t="n">
-        <v>1.217089452995558</v>
+        <v>-1.408371881343321</v>
       </c>
     </row>
     <row r="830">
@@ -7068,7 +7068,7 @@
         <v>37354</v>
       </c>
       <c r="B830" t="n">
-        <v>0.02448993839076895</v>
+        <v>-0.3565753295873579</v>
       </c>
     </row>
     <row r="831">
@@ -7076,7 +7076,7 @@
         <v>37355</v>
       </c>
       <c r="B831" t="n">
-        <v>-0.07234388271136837</v>
+        <v>-0.7819239521808403</v>
       </c>
     </row>
     <row r="832">
@@ -7084,7 +7084,7 @@
         <v>37356</v>
       </c>
       <c r="B832" t="n">
-        <v>-0.1574606235501016</v>
+        <v>2.580371946878747</v>
       </c>
     </row>
     <row r="833">
@@ -7092,7 +7092,7 @@
         <v>37357</v>
       </c>
       <c r="B833" t="n">
-        <v>0.5041055915329877</v>
+        <v>0.5298131338970101</v>
       </c>
     </row>
     <row r="834">
@@ -7100,7 +7100,7 @@
         <v>37358</v>
       </c>
       <c r="B834" t="n">
-        <v>1.474340315380563</v>
+        <v>-0.8495353560892953</v>
       </c>
     </row>
     <row r="835">
@@ -7108,7 +7108,7 @@
         <v>37359</v>
       </c>
       <c r="B835" t="n">
-        <v>0.8020381599609969</v>
+        <v>-0.7213494198566667</v>
       </c>
     </row>
     <row r="836">
@@ -7116,7 +7116,7 @@
         <v>37360</v>
       </c>
       <c r="B836" t="n">
-        <v>0.197832195620301</v>
+        <v>0.1077801875522394</v>
       </c>
     </row>
     <row r="837">
@@ -7124,7 +7124,7 @@
         <v>37361</v>
       </c>
       <c r="B837" t="n">
-        <v>-0.03655137506103064</v>
+        <v>0.3576771394511311</v>
       </c>
     </row>
     <row r="838">
@@ -7132,7 +7132,7 @@
         <v>37362</v>
       </c>
       <c r="B838" t="n">
-        <v>-1.385545320333638</v>
+        <v>-0.4292709003331164</v>
       </c>
     </row>
     <row r="839">
@@ -7140,7 +7140,7 @@
         <v>37363</v>
       </c>
       <c r="B839" t="n">
-        <v>-2.168488155505064</v>
+        <v>-0.2172982542959609</v>
       </c>
     </row>
     <row r="840">
@@ -7148,7 +7148,7 @@
         <v>37364</v>
       </c>
       <c r="B840" t="n">
-        <v>-0.3968883977809097</v>
+        <v>1.52520315237698</v>
       </c>
     </row>
     <row r="841">
@@ -7156,7 +7156,7 @@
         <v>37365</v>
       </c>
       <c r="B841" t="n">
-        <v>0.1808453879578826</v>
+        <v>-0.5034654312745949</v>
       </c>
     </row>
     <row r="842">
@@ -7164,7 +7164,7 @@
         <v>37366</v>
       </c>
       <c r="B842" t="n">
-        <v>2.002277871912652</v>
+        <v>-1.538257936495956</v>
       </c>
     </row>
     <row r="843">
@@ -7172,7 +7172,7 @@
         <v>37367</v>
       </c>
       <c r="B843" t="n">
-        <v>1.04329614822453</v>
+        <v>-2.251611639863052</v>
       </c>
     </row>
     <row r="844">
@@ -7180,7 +7180,7 @@
         <v>37368</v>
       </c>
       <c r="B844" t="n">
-        <v>1.742490089199333</v>
+        <v>0.6631020626879773</v>
       </c>
     </row>
     <row r="845">
@@ -7188,7 +7188,7 @@
         <v>37369</v>
       </c>
       <c r="B845" t="n">
-        <v>2.404179977253219</v>
+        <v>1.540838792167176</v>
       </c>
     </row>
     <row r="846">
@@ -7196,7 +7196,7 @@
         <v>37370</v>
       </c>
       <c r="B846" t="n">
-        <v>-0.2585395619925226</v>
+        <v>-1.175431460280249</v>
       </c>
     </row>
     <row r="847">
@@ -7204,7 +7204,7 @@
         <v>37371</v>
       </c>
       <c r="B847" t="n">
-        <v>1.582856712470621</v>
+        <v>-0.644679492625806</v>
       </c>
     </row>
     <row r="848">
@@ -7212,7 +7212,7 @@
         <v>37372</v>
       </c>
       <c r="B848" t="n">
-        <v>-0.7340040285010624</v>
+        <v>1.842035890537546</v>
       </c>
     </row>
     <row r="849">
@@ -7220,7 +7220,7 @@
         <v>37373</v>
       </c>
       <c r="B849" t="n">
-        <v>0.6958233126224619</v>
+        <v>-0.1813561530905517</v>
       </c>
     </row>
     <row r="850">
@@ -7228,7 +7228,7 @@
         <v>37374</v>
       </c>
       <c r="B850" t="n">
-        <v>1.191361629547375</v>
+        <v>-1.385949081261542</v>
       </c>
     </row>
     <row r="851">
@@ -7236,7 +7236,7 @@
         <v>37375</v>
       </c>
       <c r="B851" t="n">
-        <v>0.5699092340099601</v>
+        <v>-0.2178242163083268</v>
       </c>
     </row>
     <row r="852">
@@ -7244,7 +7244,7 @@
         <v>37376</v>
       </c>
       <c r="B852" t="n">
-        <v>0.3949820457751365</v>
+        <v>0.8666684389966011</v>
       </c>
     </row>
     <row r="853">
@@ -7252,7 +7252,7 @@
         <v>37377</v>
       </c>
       <c r="B853" t="n">
-        <v>0.729033934133633</v>
+        <v>-0.02307532707579524</v>
       </c>
     </row>
     <row r="854">
@@ -7260,7 +7260,7 @@
         <v>37378</v>
       </c>
       <c r="B854" t="n">
-        <v>-1.859158084193518</v>
+        <v>1.148585430151082</v>
       </c>
     </row>
     <row r="855">
@@ -7268,7 +7268,7 @@
         <v>37379</v>
       </c>
       <c r="B855" t="n">
-        <v>-0.807276694246414</v>
+        <v>-0.5924117701373801</v>
       </c>
     </row>
     <row r="856">
@@ -7276,7 +7276,7 @@
         <v>37380</v>
       </c>
       <c r="B856" t="n">
-        <v>1.221954681189729</v>
+        <v>0.3106228381066012</v>
       </c>
     </row>
     <row r="857">
@@ -7284,7 +7284,7 @@
         <v>37381</v>
       </c>
       <c r="B857" t="n">
-        <v>-0.8173374808556128</v>
+        <v>0.985620974120028</v>
       </c>
     </row>
     <row r="858">
@@ -7292,7 +7292,7 @@
         <v>37382</v>
       </c>
       <c r="B858" t="n">
-        <v>-1.407866817542149</v>
+        <v>-2.015052120987515</v>
       </c>
     </row>
     <row r="859">
@@ -7300,7 +7300,7 @@
         <v>37383</v>
       </c>
       <c r="B859" t="n">
-        <v>0.7125453792847122</v>
+        <v>-0.4417277845132616</v>
       </c>
     </row>
     <row r="860">
@@ -7308,7 +7308,7 @@
         <v>37384</v>
       </c>
       <c r="B860" t="n">
-        <v>0.3375592410445238</v>
+        <v>0.181669314617044</v>
       </c>
     </row>
     <row r="861">
@@ -7316,7 +7316,7 @@
         <v>37385</v>
       </c>
       <c r="B861" t="n">
-        <v>-0.8324261615119669</v>
+        <v>-0.8939416069167812</v>
       </c>
     </row>
     <row r="862">
@@ -7324,7 +7324,7 @@
         <v>37386</v>
       </c>
       <c r="B862" t="n">
-        <v>-2.113231115412507</v>
+        <v>1.003975994249585</v>
       </c>
     </row>
     <row r="863">
@@ -7332,7 +7332,7 @@
         <v>37387</v>
       </c>
       <c r="B863" t="n">
-        <v>0.2294865868115286</v>
+        <v>0.7190363831589375</v>
       </c>
     </row>
     <row r="864">
@@ -7340,7 +7340,7 @@
         <v>37388</v>
       </c>
       <c r="B864" t="n">
-        <v>-0.4571809851891402</v>
+        <v>1.128376954569194</v>
       </c>
     </row>
     <row r="865">
@@ -7348,7 +7348,7 @@
         <v>37389</v>
       </c>
       <c r="B865" t="n">
-        <v>0.07565892964029799</v>
+        <v>1.382407353440785</v>
       </c>
     </row>
     <row r="866">
@@ -7356,7 +7356,7 @@
         <v>37390</v>
       </c>
       <c r="B866" t="n">
-        <v>-0.8483636899510313</v>
+        <v>1.173020881363643</v>
       </c>
     </row>
     <row r="867">
@@ -7364,7 +7364,7 @@
         <v>37391</v>
       </c>
       <c r="B867" t="n">
-        <v>-0.9460322163534035</v>
+        <v>0.7199536676962299</v>
       </c>
     </row>
     <row r="868">
@@ -7372,7 +7372,7 @@
         <v>37392</v>
       </c>
       <c r="B868" t="n">
-        <v>-0.8927152987043125</v>
+        <v>-0.4812112690157141</v>
       </c>
     </row>
     <row r="869">
@@ -7380,7 +7380,7 @@
         <v>37393</v>
       </c>
       <c r="B869" t="n">
-        <v>-0.6319215459727635</v>
+        <v>0.5982527742742825</v>
       </c>
     </row>
     <row r="870">
@@ -7388,7 +7388,7 @@
         <v>37394</v>
       </c>
       <c r="B870" t="n">
-        <v>1.201017683921364</v>
+        <v>-0.6394127107257848</v>
       </c>
     </row>
     <row r="871">
@@ -7396,7 +7396,7 @@
         <v>37395</v>
       </c>
       <c r="B871" t="n">
-        <v>-0.1740899794455193</v>
+        <v>0.7585240007173518</v>
       </c>
     </row>
     <row r="872">
@@ -7404,7 +7404,7 @@
         <v>37396</v>
       </c>
       <c r="B872" t="n">
-        <v>1.093197867268605</v>
+        <v>0.1558749776996016</v>
       </c>
     </row>
     <row r="873">
@@ -7412,7 +7412,7 @@
         <v>37397</v>
       </c>
       <c r="B873" t="n">
-        <v>0.3619342425666125</v>
+        <v>1.049975762617037</v>
       </c>
     </row>
     <row r="874">
@@ -7420,7 +7420,7 @@
         <v>37398</v>
       </c>
       <c r="B874" t="n">
-        <v>-1.639111248127066</v>
+        <v>-0.8076327545103789</v>
       </c>
     </row>
     <row r="875">
@@ -7428,7 +7428,7 @@
         <v>37399</v>
       </c>
       <c r="B875" t="n">
-        <v>-0.3874454293448103</v>
+        <v>1.469048759133532</v>
       </c>
     </row>
     <row r="876">
@@ -7436,7 +7436,7 @@
         <v>37400</v>
       </c>
       <c r="B876" t="n">
-        <v>0.23808075515231</v>
+        <v>0.04881124004971953</v>
       </c>
     </row>
     <row r="877">
@@ -7444,7 +7444,7 @@
         <v>37401</v>
       </c>
       <c r="B877" t="n">
-        <v>0.3822124256554618</v>
+        <v>-0.05422133054885422</v>
       </c>
     </row>
     <row r="878">
@@ -7452,7 +7452,7 @@
         <v>37402</v>
       </c>
       <c r="B878" t="n">
-        <v>1.337632433636238</v>
+        <v>-0.3357744449372945</v>
       </c>
     </row>
     <row r="879">
@@ -7460,7 +7460,7 @@
         <v>37403</v>
       </c>
       <c r="B879" t="n">
-        <v>-0.5751445324847601</v>
+        <v>-2.284738603391388</v>
       </c>
     </row>
     <row r="880">
@@ -7468,7 +7468,7 @@
         <v>37404</v>
       </c>
       <c r="B880" t="n">
-        <v>0.5155033065271833</v>
+        <v>-0.1995543897863156</v>
       </c>
     </row>
     <row r="881">
@@ -7476,7 +7476,7 @@
         <v>37405</v>
       </c>
       <c r="B881" t="n">
-        <v>1.158336276462815</v>
+        <v>-1.170802509296294</v>
       </c>
     </row>
     <row r="882">
@@ -7484,7 +7484,7 @@
         <v>37406</v>
       </c>
       <c r="B882" t="n">
-        <v>-0.2752499911462241</v>
+        <v>-0.9967386823458807</v>
       </c>
     </row>
     <row r="883">
@@ -7492,7 +7492,7 @@
         <v>37407</v>
       </c>
       <c r="B883" t="n">
-        <v>-0.09044276735706681</v>
+        <v>0.8964250646612233</v>
       </c>
     </row>
     <row r="884">
@@ -7500,7 +7500,7 @@
         <v>37408</v>
       </c>
       <c r="B884" t="n">
-        <v>-0.803639346183472</v>
+        <v>1.559777195135458</v>
       </c>
     </row>
     <row r="885">
@@ -7508,7 +7508,7 @@
         <v>37409</v>
       </c>
       <c r="B885" t="n">
-        <v>-1.815182685460052</v>
+        <v>0.3991971651692049</v>
       </c>
     </row>
     <row r="886">
@@ -7516,7 +7516,7 @@
         <v>37410</v>
       </c>
       <c r="B886" t="n">
-        <v>-0.9373541711466815</v>
+        <v>0.4134614158310693</v>
       </c>
     </row>
     <row r="887">
@@ -7524,7 +7524,7 @@
         <v>37411</v>
       </c>
       <c r="B887" t="n">
-        <v>-0.4258654041068446</v>
+        <v>3.411837404609016</v>
       </c>
     </row>
     <row r="888">
@@ -7532,7 +7532,7 @@
         <v>37412</v>
       </c>
       <c r="B888" t="n">
-        <v>-1.671552743335305</v>
+        <v>1.163359019031427</v>
       </c>
     </row>
     <row r="889">
@@ -7540,7 +7540,7 @@
         <v>37413</v>
       </c>
       <c r="B889" t="n">
-        <v>0.9275229979275849</v>
+        <v>-0.7203505743412364</v>
       </c>
     </row>
     <row r="890">
@@ -7548,7 +7548,7 @@
         <v>37414</v>
       </c>
       <c r="B890" t="n">
-        <v>-0.6960026949410386</v>
+        <v>-1.246994858705647</v>
       </c>
     </row>
     <row r="891">
@@ -7556,7 +7556,7 @@
         <v>37415</v>
       </c>
       <c r="B891" t="n">
-        <v>-0.704752369376978</v>
+        <v>-0.2884028482316793</v>
       </c>
     </row>
     <row r="892">
@@ -7564,7 +7564,7 @@
         <v>37416</v>
       </c>
       <c r="B892" t="n">
-        <v>0.4189581942107712</v>
+        <v>1.696161094954624</v>
       </c>
     </row>
     <row r="893">
@@ -7572,7 +7572,7 @@
         <v>37417</v>
       </c>
       <c r="B893" t="n">
-        <v>-0.0538770269036053</v>
+        <v>0.6978560599353357</v>
       </c>
     </row>
     <row r="894">
@@ -7580,7 +7580,7 @@
         <v>37418</v>
       </c>
       <c r="B894" t="n">
-        <v>-0.6946689691475743</v>
+        <v>2.357068314651725</v>
       </c>
     </row>
     <row r="895">
@@ -7588,7 +7588,7 @@
         <v>37419</v>
       </c>
       <c r="B895" t="n">
-        <v>0.1783888883656796</v>
+        <v>0.5570002153548441</v>
       </c>
     </row>
     <row r="896">
@@ -7596,7 +7596,7 @@
         <v>37420</v>
       </c>
       <c r="B896" t="n">
-        <v>-1.174994582765759</v>
+        <v>-0.3561607969448857</v>
       </c>
     </row>
     <row r="897">
@@ -7604,7 +7604,7 @@
         <v>37421</v>
       </c>
       <c r="B897" t="n">
-        <v>0.9232493414303127</v>
+        <v>-0.7028057244190677</v>
       </c>
     </row>
     <row r="898">
@@ -7612,7 +7612,7 @@
         <v>37422</v>
       </c>
       <c r="B898" t="n">
-        <v>-1.816150000729756</v>
+        <v>0.508960918391957</v>
       </c>
     </row>
     <row r="899">
@@ -7620,7 +7620,7 @@
         <v>37423</v>
       </c>
       <c r="B899" t="n">
-        <v>0.3363554858234889</v>
+        <v>0.687217502157484</v>
       </c>
     </row>
     <row r="900">
@@ -7628,7 +7628,7 @@
         <v>37424</v>
       </c>
       <c r="B900" t="n">
-        <v>0.1331513844600363</v>
+        <v>-0.4829155060673861</v>
       </c>
     </row>
     <row r="901">
@@ -7636,7 +7636,7 @@
         <v>37425</v>
       </c>
       <c r="B901" t="n">
-        <v>0.2145041729604446</v>
+        <v>-0.4693797331721415</v>
       </c>
     </row>
     <row r="902">
@@ -7644,7 +7644,7 @@
         <v>37426</v>
       </c>
       <c r="B902" t="n">
-        <v>-0.1643222753571645</v>
+        <v>-0.8157043011032908</v>
       </c>
     </row>
     <row r="903">
@@ -7652,7 +7652,7 @@
         <v>37427</v>
       </c>
       <c r="B903" t="n">
-        <v>-0.3017650641663273</v>
+        <v>-0.03840085700803646</v>
       </c>
     </row>
     <row r="904">
@@ -7660,7 +7660,7 @@
         <v>37428</v>
       </c>
       <c r="B904" t="n">
-        <v>-0.9428423383740392</v>
+        <v>-0.9056690716910264</v>
       </c>
     </row>
     <row r="905">
@@ -7668,7 +7668,7 @@
         <v>37429</v>
       </c>
       <c r="B905" t="n">
-        <v>1.254538756112464</v>
+        <v>-1.292452617255406</v>
       </c>
     </row>
     <row r="906">
@@ -7676,7 +7676,7 @@
         <v>37430</v>
       </c>
       <c r="B906" t="n">
-        <v>-0.1716130289586012</v>
+        <v>1.179996502013559</v>
       </c>
     </row>
     <row r="907">
@@ -7684,7 +7684,7 @@
         <v>37431</v>
       </c>
       <c r="B907" t="n">
-        <v>-1.043034556350546</v>
+        <v>0.3645880154949672</v>
       </c>
     </row>
     <row r="908">
@@ -7692,7 +7692,7 @@
         <v>37432</v>
       </c>
       <c r="B908" t="n">
-        <v>-0.1665260189193254</v>
+        <v>-0.5484564825941076</v>
       </c>
     </row>
     <row r="909">
@@ -7700,7 +7700,7 @@
         <v>37433</v>
       </c>
       <c r="B909" t="n">
-        <v>-1.50906954381565</v>
+        <v>-0.618544661232162</v>
       </c>
     </row>
     <row r="910">
@@ -7708,7 +7708,7 @@
         <v>37434</v>
       </c>
       <c r="B910" t="n">
-        <v>-0.7886741189027078</v>
+        <v>0.5077479978155749</v>
       </c>
     </row>
     <row r="911">
@@ -7716,7 +7716,7 @@
         <v>37435</v>
       </c>
       <c r="B911" t="n">
-        <v>0.6360635949889546</v>
+        <v>0.5026258656802206</v>
       </c>
     </row>
     <row r="912">
@@ -7724,7 +7724,7 @@
         <v>37436</v>
       </c>
       <c r="B912" t="n">
-        <v>0.9194269502438395</v>
+        <v>-0.9098853637235219</v>
       </c>
     </row>
     <row r="913">
@@ -7732,7 +7732,7 @@
         <v>37437</v>
       </c>
       <c r="B913" t="n">
-        <v>1.09356730989054</v>
+        <v>-0.5869927544187458</v>
       </c>
     </row>
     <row r="914">
@@ -7740,7 +7740,7 @@
         <v>37438</v>
       </c>
       <c r="B914" t="n">
-        <v>-0.4879767537560163</v>
+        <v>0.7665752916077183</v>
       </c>
     </row>
     <row r="915">
@@ -7748,7 +7748,7 @@
         <v>37439</v>
       </c>
       <c r="B915" t="n">
-        <v>1.23866112877125</v>
+        <v>1.563029468548792</v>
       </c>
     </row>
     <row r="916">
@@ -7756,7 +7756,7 @@
         <v>37440</v>
       </c>
       <c r="B916" t="n">
-        <v>0.3491532882593603</v>
+        <v>-0.7180529261980295</v>
       </c>
     </row>
     <row r="917">
@@ -7764,7 +7764,7 @@
         <v>37441</v>
       </c>
       <c r="B917" t="n">
-        <v>0.016645946083225</v>
+        <v>-0.8460469912657076</v>
       </c>
     </row>
     <row r="918">
@@ -7772,7 +7772,7 @@
         <v>37442</v>
       </c>
       <c r="B918" t="n">
-        <v>-1.266279049464487</v>
+        <v>0.1110639217332699</v>
       </c>
     </row>
     <row r="919">
@@ -7780,7 +7780,7 @@
         <v>37443</v>
       </c>
       <c r="B919" t="n">
-        <v>0.9878383285687025</v>
+        <v>0.8576433733324481</v>
       </c>
     </row>
     <row r="920">
@@ -7788,7 +7788,7 @@
         <v>37444</v>
       </c>
       <c r="B920" t="n">
-        <v>-0.08085464364272449</v>
+        <v>0.4191942754359131</v>
       </c>
     </row>
     <row r="921">
@@ -7796,7 +7796,7 @@
         <v>37445</v>
       </c>
       <c r="B921" t="n">
-        <v>-0.26705873476905</v>
+        <v>0.00906779737707572</v>
       </c>
     </row>
     <row r="922">
@@ -7804,7 +7804,7 @@
         <v>37446</v>
       </c>
       <c r="B922" t="n">
-        <v>-1.096943084191886</v>
+        <v>0.503577023475629</v>
       </c>
     </row>
     <row r="923">
@@ -7812,7 +7812,7 @@
         <v>37447</v>
       </c>
       <c r="B923" t="n">
-        <v>1.053076920852644</v>
+        <v>0.3835244637691118</v>
       </c>
     </row>
     <row r="924">
@@ -7820,7 +7820,7 @@
         <v>37448</v>
       </c>
       <c r="B924" t="n">
-        <v>-0.425006871730143</v>
+        <v>1.225726098753539</v>
       </c>
     </row>
     <row r="925">
@@ -7828,7 +7828,7 @@
         <v>37449</v>
       </c>
       <c r="B925" t="n">
-        <v>-1.161482796579953</v>
+        <v>-0.9261824378852123</v>
       </c>
     </row>
     <row r="926">
@@ -7836,7 +7836,7 @@
         <v>37450</v>
       </c>
       <c r="B926" t="n">
-        <v>-2.253043478105806</v>
+        <v>-0.4982529362860073</v>
       </c>
     </row>
     <row r="927">
@@ -7844,7 +7844,7 @@
         <v>37451</v>
       </c>
       <c r="B927" t="n">
-        <v>0.2593062655876857</v>
+        <v>0.5857522794047011</v>
       </c>
     </row>
     <row r="928">
@@ -7852,7 +7852,7 @@
         <v>37452</v>
       </c>
       <c r="B928" t="n">
-        <v>0.71762727659831</v>
+        <v>-0.661656948082001</v>
       </c>
     </row>
     <row r="929">
@@ -7860,7 +7860,7 @@
         <v>37453</v>
       </c>
       <c r="B929" t="n">
-        <v>0.1324476469989082</v>
+        <v>-0.5176338663969496</v>
       </c>
     </row>
     <row r="930">
@@ -7868,7 +7868,7 @@
         <v>37454</v>
       </c>
       <c r="B930" t="n">
-        <v>-1.519663170253161</v>
+        <v>-0.09491059246348196</v>
       </c>
     </row>
     <row r="931">
@@ -7876,7 +7876,7 @@
         <v>37455</v>
       </c>
       <c r="B931" t="n">
-        <v>-0.8131393713357362</v>
+        <v>0.2113986145137051</v>
       </c>
     </row>
     <row r="932">
@@ -7884,7 +7884,7 @@
         <v>37456</v>
       </c>
       <c r="B932" t="n">
-        <v>-0.4855884552466125</v>
+        <v>-1.028952747959424</v>
       </c>
     </row>
     <row r="933">
@@ -7892,7 +7892,7 @@
         <v>37457</v>
       </c>
       <c r="B933" t="n">
-        <v>1.14980456632644</v>
+        <v>-0.2060885488154659</v>
       </c>
     </row>
     <row r="934">
@@ -7900,7 +7900,7 @@
         <v>37458</v>
       </c>
       <c r="B934" t="n">
-        <v>0.7051020011419383</v>
+        <v>1.483346213892332</v>
       </c>
     </row>
     <row r="935">
@@ -7908,7 +7908,7 @@
         <v>37459</v>
       </c>
       <c r="B935" t="n">
-        <v>0.4089108028372229</v>
+        <v>0.2267775926352696</v>
       </c>
     </row>
     <row r="936">
@@ -7916,7 +7916,7 @@
         <v>37460</v>
       </c>
       <c r="B936" t="n">
-        <v>0.8252904054544232</v>
+        <v>-0.04150158610449136</v>
       </c>
     </row>
     <row r="937">
@@ -7924,7 +7924,7 @@
         <v>37461</v>
       </c>
       <c r="B937" t="n">
-        <v>0.2101712751517356</v>
+        <v>-0.8236891931754259</v>
       </c>
     </row>
     <row r="938">
@@ -7932,7 +7932,7 @@
         <v>37462</v>
       </c>
       <c r="B938" t="n">
-        <v>0.7360273512507171</v>
+        <v>0.5853464800751701</v>
       </c>
     </row>
     <row r="939">
@@ -7940,7 +7940,7 @@
         <v>37463</v>
       </c>
       <c r="B939" t="n">
-        <v>-0.4784208398680921</v>
+        <v>-0.416865976136122</v>
       </c>
     </row>
     <row r="940">
@@ -7948,7 +7948,7 @@
         <v>37464</v>
       </c>
       <c r="B940" t="n">
-        <v>0.4796104732796643</v>
+        <v>0.9202883110390533</v>
       </c>
     </row>
     <row r="941">
@@ -7956,7 +7956,7 @@
         <v>37465</v>
       </c>
       <c r="B941" t="n">
-        <v>2.257445411072004</v>
+        <v>0.2128126041009801</v>
       </c>
     </row>
     <row r="942">
@@ -7964,7 +7964,7 @@
         <v>37466</v>
       </c>
       <c r="B942" t="n">
-        <v>-0.2595237354557409</v>
+        <v>-0.8032638713258199</v>
       </c>
     </row>
     <row r="943">
@@ -7972,7 +7972,7 @@
         <v>37467</v>
       </c>
       <c r="B943" t="n">
-        <v>-1.825508103001538</v>
+        <v>0.178112489604743</v>
       </c>
     </row>
     <row r="944">
@@ -7980,7 +7980,7 @@
         <v>37468</v>
       </c>
       <c r="B944" t="n">
-        <v>1.218962728922473</v>
+        <v>-1.226437190184577</v>
       </c>
     </row>
     <row r="945">
@@ -7988,7 +7988,7 @@
         <v>37469</v>
       </c>
       <c r="B945" t="n">
-        <v>0.2516222593287055</v>
+        <v>-1.513039990795865</v>
       </c>
     </row>
     <row r="946">
@@ -7996,7 +7996,7 @@
         <v>37470</v>
       </c>
       <c r="B946" t="n">
-        <v>3.681474380079052</v>
+        <v>-0.9505899758374404</v>
       </c>
     </row>
     <row r="947">
@@ -8004,7 +8004,7 @@
         <v>37471</v>
       </c>
       <c r="B947" t="n">
-        <v>-1.252175088051912</v>
+        <v>-0.01509530596676949</v>
       </c>
     </row>
     <row r="948">
@@ -8012,7 +8012,7 @@
         <v>37472</v>
       </c>
       <c r="B948" t="n">
-        <v>0.5663041578214214</v>
+        <v>-0.3320018718155202</v>
       </c>
     </row>
     <row r="949">
@@ -8020,7 +8020,7 @@
         <v>37473</v>
       </c>
       <c r="B949" t="n">
-        <v>-0.4515648640611252</v>
+        <v>0.5026810184331981</v>
       </c>
     </row>
     <row r="950">
@@ -8028,7 +8028,7 @@
         <v>37474</v>
       </c>
       <c r="B950" t="n">
-        <v>1.070459430777521</v>
+        <v>0.2291112508161511</v>
       </c>
     </row>
     <row r="951">
@@ -8036,7 +8036,7 @@
         <v>37475</v>
       </c>
       <c r="B951" t="n">
-        <v>-0.2141602346750182</v>
+        <v>-0.1508860539232679</v>
       </c>
     </row>
     <row r="952">
@@ -8044,7 +8044,7 @@
         <v>37476</v>
       </c>
       <c r="B952" t="n">
-        <v>-1.010213380032491</v>
+        <v>0.9328804258563282</v>
       </c>
     </row>
     <row r="953">
@@ -8052,7 +8052,7 @@
         <v>37477</v>
       </c>
       <c r="B953" t="n">
-        <v>0.5989070108726487</v>
+        <v>0.7272432043561703</v>
       </c>
     </row>
     <row r="954">
@@ -8060,7 +8060,7 @@
         <v>37478</v>
       </c>
       <c r="B954" t="n">
-        <v>-1.225751156488723</v>
+        <v>0.1631529025030355</v>
       </c>
     </row>
     <row r="955">
@@ -8068,7 +8068,7 @@
         <v>37479</v>
       </c>
       <c r="B955" t="n">
-        <v>-1.046761739252113</v>
+        <v>-0.8832732129677597</v>
       </c>
     </row>
     <row r="956">
@@ -8076,7 +8076,7 @@
         <v>37480</v>
       </c>
       <c r="B956" t="n">
-        <v>0.779886634861002</v>
+        <v>0.2387409565846634</v>
       </c>
     </row>
     <row r="957">
@@ -8084,7 +8084,7 @@
         <v>37481</v>
       </c>
       <c r="B957" t="n">
-        <v>0.7462439809352144</v>
+        <v>1.368013017948355</v>
       </c>
     </row>
     <row r="958">
@@ -8092,7 +8092,7 @@
         <v>37482</v>
       </c>
       <c r="B958" t="n">
-        <v>1.046716975350561</v>
+        <v>0.3295568997044586</v>
       </c>
     </row>
     <row r="959">
@@ -8100,7 +8100,7 @@
         <v>37483</v>
       </c>
       <c r="B959" t="n">
-        <v>0.02911024824709721</v>
+        <v>-0.7262469256264227</v>
       </c>
     </row>
     <row r="960">
@@ -8108,7 +8108,7 @@
         <v>37484</v>
       </c>
       <c r="B960" t="n">
-        <v>-0.1114347589299966</v>
+        <v>-0.2479823721159901</v>
       </c>
     </row>
     <row r="961">
@@ -8116,7 +8116,7 @@
         <v>37485</v>
       </c>
       <c r="B961" t="n">
-        <v>0.3293817166374448</v>
+        <v>0.9856431895651226</v>
       </c>
     </row>
     <row r="962">
@@ -8124,7 +8124,7 @@
         <v>37486</v>
       </c>
       <c r="B962" t="n">
-        <v>1.206043043270403</v>
+        <v>0.1102311702399147</v>
       </c>
     </row>
     <row r="963">
@@ -8132,7 +8132,7 @@
         <v>37487</v>
       </c>
       <c r="B963" t="n">
-        <v>-1.212870721678145</v>
+        <v>-0.4335777678948528</v>
       </c>
     </row>
     <row r="964">
@@ -8140,7 +8140,7 @@
         <v>37488</v>
       </c>
       <c r="B964" t="n">
-        <v>-0.7191060997487417</v>
+        <v>0.7922659452757793</v>
       </c>
     </row>
     <row r="965">
@@ -8148,7 +8148,7 @@
         <v>37489</v>
       </c>
       <c r="B965" t="n">
-        <v>-0.6067327763627619</v>
+        <v>0.8568421276673872</v>
       </c>
     </row>
     <row r="966">
@@ -8156,7 +8156,7 @@
         <v>37490</v>
       </c>
       <c r="B966" t="n">
-        <v>-1.090314404567484</v>
+        <v>0.2321710314749624</v>
       </c>
     </row>
     <row r="967">
@@ -8164,7 +8164,7 @@
         <v>37491</v>
       </c>
       <c r="B967" t="n">
-        <v>0.4320705234513361</v>
+        <v>-1.237558703002015</v>
       </c>
     </row>
     <row r="968">
@@ -8172,7 +8172,7 @@
         <v>37492</v>
       </c>
       <c r="B968" t="n">
-        <v>0.814820076368053</v>
+        <v>-0.6376048139011674</v>
       </c>
     </row>
     <row r="969">
@@ -8180,7 +8180,7 @@
         <v>37493</v>
       </c>
       <c r="B969" t="n">
-        <v>-1.140906620347128</v>
+        <v>-0.03232274205470052</v>
       </c>
     </row>
     <row r="970">
@@ -8188,7 +8188,7 @@
         <v>37494</v>
       </c>
       <c r="B970" t="n">
-        <v>0.4041815310293214</v>
+        <v>1.26003553637013</v>
       </c>
     </row>
     <row r="971">
@@ -8196,7 +8196,7 @@
         <v>37495</v>
       </c>
       <c r="B971" t="n">
-        <v>-0.3113440794523872</v>
+        <v>-0.3906157657686182</v>
       </c>
     </row>
     <row r="972">
@@ -8204,7 +8204,7 @@
         <v>37496</v>
       </c>
       <c r="B972" t="n">
-        <v>1.214101262902058</v>
+        <v>-1.552958930807178</v>
       </c>
     </row>
     <row r="973">
@@ -8212,7 +8212,7 @@
         <v>37497</v>
       </c>
       <c r="B973" t="n">
-        <v>-0.2507850472898289</v>
+        <v>-0.7196659710886433</v>
       </c>
     </row>
     <row r="974">
@@ -8220,7 +8220,7 @@
         <v>37498</v>
       </c>
       <c r="B974" t="n">
-        <v>0.9209611628553368</v>
+        <v>0.785131857682139</v>
       </c>
     </row>
     <row r="975">
@@ -8228,7 +8228,7 @@
         <v>37499</v>
       </c>
       <c r="B975" t="n">
-        <v>-0.410913066884026</v>
+        <v>-0.5820877772685812</v>
       </c>
     </row>
     <row r="976">
@@ -8236,7 +8236,7 @@
         <v>37500</v>
       </c>
       <c r="B976" t="n">
-        <v>-0.9170322981747149</v>
+        <v>1.697909541324741</v>
       </c>
     </row>
     <row r="977">
@@ -8244,7 +8244,7 @@
         <v>37501</v>
       </c>
       <c r="B977" t="n">
-        <v>0.3982921566649504</v>
+        <v>-0.3504610951204629</v>
       </c>
     </row>
     <row r="978">
@@ -8252,7 +8252,7 @@
         <v>37502</v>
       </c>
       <c r="B978" t="n">
-        <v>-1.173759567444244</v>
+        <v>0.8399684022255118</v>
       </c>
     </row>
     <row r="979">
@@ -8260,7 +8260,7 @@
         <v>37503</v>
       </c>
       <c r="B979" t="n">
-        <v>1.125822466719746</v>
+        <v>-0.5663319711102445</v>
       </c>
     </row>
     <row r="980">
@@ -8268,7 +8268,7 @@
         <v>37504</v>
       </c>
       <c r="B980" t="n">
-        <v>-1.203612412304947</v>
+        <v>-0.5997689041232117</v>
       </c>
     </row>
     <row r="981">
@@ -8276,7 +8276,7 @@
         <v>37505</v>
       </c>
       <c r="B981" t="n">
-        <v>1.824130083135505</v>
+        <v>-0.218751922170927</v>
       </c>
     </row>
     <row r="982">
@@ -8284,7 +8284,7 @@
         <v>37506</v>
       </c>
       <c r="B982" t="n">
-        <v>-0.1833265697871694</v>
+        <v>0.4203491535541908</v>
       </c>
     </row>
     <row r="983">
@@ -8292,7 +8292,7 @@
         <v>37507</v>
       </c>
       <c r="B983" t="n">
-        <v>-0.5519300038512923</v>
+        <v>0.8546614294619501</v>
       </c>
     </row>
     <row r="984">
@@ -8300,7 +8300,7 @@
         <v>37508</v>
       </c>
       <c r="B984" t="n">
-        <v>-1.134319744403628</v>
+        <v>-1.597221269533736</v>
       </c>
     </row>
     <row r="985">
@@ -8308,7 +8308,7 @@
         <v>37509</v>
       </c>
       <c r="B985" t="n">
-        <v>1.272789636392513</v>
+        <v>0.9531426067207573</v>
       </c>
     </row>
     <row r="986">
@@ -8316,7 +8316,7 @@
         <v>37510</v>
       </c>
       <c r="B986" t="n">
-        <v>0.465523627823647</v>
+        <v>-1.404389204795514</v>
       </c>
     </row>
     <row r="987">
@@ -8324,7 +8324,7 @@
         <v>37511</v>
       </c>
       <c r="B987" t="n">
-        <v>-0.9913181268075493</v>
+        <v>1.010008948176883</v>
       </c>
     </row>
     <row r="988">
@@ -8332,7 +8332,7 @@
         <v>37512</v>
       </c>
       <c r="B988" t="n">
-        <v>0.108731740017246</v>
+        <v>-0.1333966776699925</v>
       </c>
     </row>
     <row r="989">
@@ -8340,7 +8340,7 @@
         <v>37513</v>
       </c>
       <c r="B989" t="n">
-        <v>2.0517502705151</v>
+        <v>1.133481218252377</v>
       </c>
     </row>
     <row r="990">
@@ -8348,7 +8348,7 @@
         <v>37514</v>
       </c>
       <c r="B990" t="n">
-        <v>1.441569676605148</v>
+        <v>-0.8068432465172289</v>
       </c>
     </row>
     <row r="991">
@@ -8356,7 +8356,7 @@
         <v>37515</v>
       </c>
       <c r="B991" t="n">
-        <v>-0.5924740422614162</v>
+        <v>-0.1696048243656457</v>
       </c>
     </row>
     <row r="992">
@@ -8364,7 +8364,7 @@
         <v>37516</v>
       </c>
       <c r="B992" t="n">
-        <v>0.3815372392395247</v>
+        <v>-1.44910844413096</v>
       </c>
     </row>
     <row r="993">
@@ -8372,7 +8372,7 @@
         <v>37517</v>
       </c>
       <c r="B993" t="n">
-        <v>-1.121999589480119</v>
+        <v>0.002815495001817651</v>
       </c>
     </row>
     <row r="994">
@@ -8380,7 +8380,7 @@
         <v>37518</v>
       </c>
       <c r="B994" t="n">
-        <v>1.158538824996948</v>
+        <v>-0.2144911198201497</v>
       </c>
     </row>
     <row r="995">
@@ -8388,7 +8388,7 @@
         <v>37519</v>
       </c>
       <c r="B995" t="n">
-        <v>-1.998629242378869</v>
+        <v>-1.854293746292912</v>
       </c>
     </row>
     <row r="996">
@@ -8396,7 +8396,7 @@
         <v>37520</v>
       </c>
       <c r="B996" t="n">
-        <v>-0.2949839291900899</v>
+        <v>1.585488481075622</v>
       </c>
     </row>
     <row r="997">
@@ -8404,7 +8404,7 @@
         <v>37521</v>
       </c>
       <c r="B997" t="n">
-        <v>0.7849217013437313</v>
+        <v>0.4307669583734393</v>
       </c>
     </row>
     <row r="998">
@@ -8412,7 +8412,7 @@
         <v>37522</v>
       </c>
       <c r="B998" t="n">
-        <v>1.57011914518905</v>
+        <v>-0.754170117412139</v>
       </c>
     </row>
     <row r="999">
@@ -8420,7 +8420,7 @@
         <v>37523</v>
       </c>
       <c r="B999" t="n">
-        <v>0.06478115239855521</v>
+        <v>0.3999649830690875</v>
       </c>
     </row>
     <row r="1000">
@@ -8428,7 +8428,7 @@
         <v>37524</v>
       </c>
       <c r="B1000" t="n">
-        <v>0.7808765719043905</v>
+        <v>-2.524303627748882</v>
       </c>
     </row>
     <row r="1001">
@@ -8436,7 +8436,7 @@
         <v>37525</v>
       </c>
       <c r="B1001" t="n">
-        <v>1.297339317115409</v>
+        <v>2.762838453903808</v>
       </c>
     </row>
   </sheetData>
